--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-14.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-12 01:32:45</t>
+          <t>2026-07-12 03:48:52</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-12 01:32:45</t>
+          <t>2026-07-12 03:48:52</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-14.xlsx
@@ -869,10 +869,10 @@
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K2" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-12 03:48:52</t>
+          <t>2026-07-12 06:05:18</t>
         </is>
       </c>
     </row>
@@ -1117,13 +1117,13 @@
         <v>2.4</v>
       </c>
       <c r="H3" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="I3" t="n">
         <v>4.2</v>
       </c>
       <c r="J3" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K3" t="n">
         <v>3.7</v>
@@ -1144,7 +1144,7 @@
         <v>1.71</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-12 03:48:52</t>
+          <t>2026-07-12 06:05:18</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-14.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-12 06:05:18</t>
+          <t>2026-07-12 08:21:30</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-12 06:05:18</t>
+          <t>2026-07-12 08:21:30</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-14.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-12 08:21:30</t>
+          <t>2026-07-12 10:37:00</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
         <v>2.4</v>
       </c>
       <c r="H3" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I3" t="n">
         <v>4.2</v>
@@ -1126,7 +1126,7 @@
         <v>3.15</v>
       </c>
       <c r="K3" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1144,7 +1144,7 @@
         <v>1.71</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-12 08:21:30</t>
+          <t>2026-07-12 10:37:00</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-14.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-12 10:37:00</t>
+          <t>2026-07-12 12:51:08</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-12 10:37:00</t>
+          <t>2026-07-12 12:51:08</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB3"/>
+  <dimension ref="A1:CB4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Chinese Super League</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,251 +843,251 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>08:35:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>HK Kopavogur</t>
+          <t>Zhejiang Greentown</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>Qingdao Hainiu</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.04</v>
+        <v>1.47</v>
       </c>
       <c r="G2" t="n">
-        <v>1000</v>
+        <v>1.56</v>
       </c>
       <c r="H2" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="I2" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="J2" t="n">
-        <v>1.02</v>
+        <v>5</v>
       </c>
       <c r="K2" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="P2" t="n">
-        <v>1.24</v>
+        <v>3</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BH2" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BK2" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BO2" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BP2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BR2" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BV2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BX2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="CA2" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-12 12:51:08</t>
+          <t>2026-07-12 15:04:14</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,244 +1097,498 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Macara</t>
+          <t>HK Kopavogur</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>IR Reykjavik</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.12</v>
+        <v>1.82</v>
       </c>
       <c r="G3" t="n">
-        <v>2.4</v>
+        <v>2.02</v>
       </c>
       <c r="H3" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="I3" t="n">
         <v>4.2</v>
       </c>
       <c r="J3" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>36</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>26</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>2026-07-12 15:04:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Macara</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J4" t="n">
         <v>3.15</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K4" t="n">
         <v>3.65</v>
       </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
         <v>1.71</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="Q4" t="n">
         <v>2.14</v>
       </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>2026-07-12 12:51:08</t>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>2026-07-12 15:04:14</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-14.xlsx
@@ -857,16 +857,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="G2" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="H2" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I2" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="J2" t="n">
         <v>5</v>
@@ -875,7 +875,7 @@
         <v>5.9</v>
       </c>
       <c r="L2" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="M2" t="n">
         <v>1.01</v>
@@ -890,25 +890,25 @@
         <v>3</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="R2" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="S2" t="n">
         <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="U2" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="V2" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W2" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="X2" t="n">
         <v>42</v>
@@ -920,10 +920,10 @@
         <v>75</v>
       </c>
       <c r="AA2" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AB2" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AC2" t="n">
         <v>15.5</v>
@@ -947,34 +947,34 @@
         <v>65</v>
       </c>
       <c r="AJ2" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK2" t="n">
         <v>16.5</v>
       </c>
-      <c r="AK2" t="n">
-        <v>15</v>
-      </c>
       <c r="AL2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM2" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AO2" t="n">
         <v>60</v>
       </c>
       <c r="AP2" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="AR2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS2" t="n">
         <v>6.2</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>6.6</v>
       </c>
       <c r="AT2" t="n">
         <v>12.5</v>
@@ -983,10 +983,10 @@
         <v>11.5</v>
       </c>
       <c r="AV2" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="AW2" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AX2" t="n">
         <v>11</v>
@@ -998,7 +998,7 @@
         <v>16</v>
       </c>
       <c r="BA2" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BB2" t="n">
         <v>13.5</v>
@@ -1010,13 +1010,13 @@
         <v>20</v>
       </c>
       <c r="BE2" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BF2" t="n">
         <v>3.85</v>
       </c>
       <c r="BG2" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BH2" t="n">
         <v>5.4</v>
@@ -1052,7 +1052,7 @@
         <v>18</v>
       </c>
       <c r="BS2" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BT2" t="n">
         <v>11</v>
@@ -1076,11 +1076,11 @@
         <v>10</v>
       </c>
       <c r="CA2" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-12 15:04:14</t>
+          <t>2026-07-12 17:15:06</t>
         </is>
       </c>
     </row>
@@ -1111,16 +1111,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="G3" t="n">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="H3" t="n">
         <v>3.4</v>
       </c>
       <c r="I3" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J3" t="n">
         <v>3.95</v>
@@ -1135,88 +1135,88 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.26</v>
+        <v>6.4</v>
       </c>
       <c r="O3" t="n">
         <v>1.12</v>
       </c>
       <c r="P3" t="n">
-        <v>2.92</v>
+        <v>3.15</v>
       </c>
       <c r="Q3" t="n">
         <v>1.37</v>
       </c>
       <c r="R3" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="S3" t="n">
         <v>1.9</v>
       </c>
       <c r="T3" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="U3" t="n">
         <v>2.84</v>
       </c>
       <c r="V3" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W3" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="Y3" t="n">
         <v>36</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AB3" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AC3" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AF3" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG3" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>19.5</v>
+        <v>16</v>
       </c>
       <c r="AI3" t="n">
         <v>42</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AK3" t="n">
-        <v>22</v>
+        <v>17.5</v>
       </c>
       <c r="AL3" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AP3" t="n">
         <v>1.03</v>
@@ -1267,10 +1267,10 @@
         <v>1.03</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BH3" t="n">
         <v>5.7</v>
@@ -1291,13 +1291,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BN3" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BO3" t="n">
         <v>3.6</v>
       </c>
       <c r="BP3" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BQ3" t="n">
         <v>7.2</v>
@@ -1309,32 +1309,32 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BT3" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BU3" t="n">
         <v>5.1</v>
       </c>
       <c r="BV3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BW3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BX3" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BY3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BZ3" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="CA3" t="n">
         <v>6.6</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-12 15:04:14</t>
+          <t>2026-07-12 17:15:06</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-12 15:04:14</t>
+          <t>2026-07-12 17:15:06</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-14.xlsx
@@ -1028,13 +1028,13 @@
         <v>9.6</v>
       </c>
       <c r="BK2" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BN2" t="n">
         <v>4.8</v>
@@ -1046,31 +1046,31 @@
         <v>9</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BR2" t="n">
         <v>18</v>
       </c>
       <c r="BS2" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BT2" t="n">
         <v>11</v>
       </c>
       <c r="BU2" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2" t="n">
         <v>10</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-12 17:15:06</t>
+          <t>2026-07-12 19:23:37</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="G3" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="H3" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="I3" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="J3" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="K3" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="L3" t="n">
         <v>1.18</v>
@@ -1135,22 +1135,22 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="O3" t="n">
         <v>1.12</v>
       </c>
       <c r="P3" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="R3" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="S3" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="T3" t="n">
         <v>1.43</v>
@@ -1159,22 +1159,22 @@
         <v>2.84</v>
       </c>
       <c r="V3" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="W3" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="X3" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="Y3" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Z3" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AA3" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AB3" t="n">
         <v>23</v>
@@ -1183,10 +1183,10 @@
         <v>15.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE3" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AF3" t="n">
         <v>22</v>
@@ -1201,10 +1201,10 @@
         <v>42</v>
       </c>
       <c r="AJ3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK3" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AL3" t="n">
         <v>27</v>
@@ -1213,128 +1213,128 @@
         <v>55</v>
       </c>
       <c r="AN3" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AO3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="BA3" t="n">
         <v>1.03</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BG3" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BH3" t="n">
         <v>5.7</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.55</v>
+        <v>4.8</v>
       </c>
       <c r="BJ3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BN3" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BO3" t="n">
         <v>3.6</v>
       </c>
       <c r="BP3" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BR3" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BS3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT3" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BT3" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BU3" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BV3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BW3" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BX3" t="n">
         <v>28</v>
       </c>
       <c r="BY3" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BZ3" t="n">
         <v>11</v>
       </c>
       <c r="CA3" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-12 17:15:06</t>
+          <t>2026-07-12 19:23:37</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
         <v>2.12</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="H4" t="n">
         <v>3.55</v>
@@ -1383,16 +1383,16 @@
         <v>3.65</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="P4" t="n">
         <v>1.71</v>
@@ -1401,194 +1401,194 @@
         <v>2.14</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BI4" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN4" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BO4" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BP4" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR4" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BU4" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BV4" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX4" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BY4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-12 17:15:06</t>
+          <t>2026-07-12 19:23:37</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-14.xlsx
@@ -857,58 +857,58 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="G2" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="H2" t="n">
         <v>6.2</v>
       </c>
       <c r="I2" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="J2" t="n">
         <v>5</v>
       </c>
       <c r="K2" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="L2" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="O2" t="n">
         <v>1.14</v>
       </c>
       <c r="P2" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="R2" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="T2" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="U2" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="V2" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="W2" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="X2" t="n">
         <v>42</v>
@@ -926,7 +926,7 @@
         <v>17</v>
       </c>
       <c r="AC2" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AD2" t="n">
         <v>28</v>
@@ -965,16 +965,16 @@
         <v>60</v>
       </c>
       <c r="AP2" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="AR2" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AT2" t="n">
         <v>12.5</v>
@@ -983,10 +983,10 @@
         <v>11.5</v>
       </c>
       <c r="AV2" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="AW2" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AX2" t="n">
         <v>11</v>
@@ -998,7 +998,7 @@
         <v>16</v>
       </c>
       <c r="BA2" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BB2" t="n">
         <v>13.5</v>
@@ -1010,16 +1010,16 @@
         <v>20</v>
       </c>
       <c r="BE2" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BF2" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="BG2" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="BH2" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BI2" t="n">
         <v>4.6</v>
@@ -1028,16 +1028,16 @@
         <v>9.6</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BN2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BO2" t="n">
         <v>3.75</v>
@@ -1046,31 +1046,31 @@
         <v>9</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BR2" t="n">
         <v>18</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BT2" t="n">
         <v>11</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ2" t="n">
         <v>10</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-12 19:23:37</t>
+          <t>2026-07-12 21:31:45</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
         <v>55</v>
       </c>
       <c r="AN3" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="AO3" t="n">
         <v>26</v>
@@ -1222,7 +1222,7 @@
         <v>1.01</v>
       </c>
       <c r="AQ3" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="AR3" t="n">
         <v>1.01</v>
@@ -1234,7 +1234,7 @@
         <v>13.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AV3" t="n">
         <v>13.5</v>
@@ -1249,7 +1249,7 @@
         <v>8.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA3" t="n">
         <v>1.03</v>
@@ -1258,7 +1258,7 @@
         <v>16</v>
       </c>
       <c r="BC3" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BD3" t="n">
         <v>16</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-12 19:23:37</t>
+          <t>2026-07-12 21:31:45</t>
         </is>
       </c>
     </row>
@@ -1536,13 +1536,13 @@
         <v>10.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BN4" t="n">
         <v>5.1</v>
@@ -1554,41 +1554,41 @@
         <v>18</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BR4" t="n">
         <v>36</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BT4" t="n">
         <v>7.2</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BV4" t="n">
         <v>34</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BX4" t="n">
         <v>50</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BZ4" t="n">
         <v>34</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-12 19:23:37</t>
+          <t>2026-07-12 21:31:45</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-14.xlsx
@@ -869,7 +869,7 @@
         <v>7</v>
       </c>
       <c r="J2" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="K2" t="n">
         <v>5.7</v>
@@ -881,7 +881,7 @@
         <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="O2" t="n">
         <v>1.14</v>
@@ -908,7 +908,7 @@
         <v>1.17</v>
       </c>
       <c r="W2" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="X2" t="n">
         <v>42</v>
@@ -923,10 +923,10 @@
         <v>170</v>
       </c>
       <c r="AB2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AC2" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AD2" t="n">
         <v>28</v>
@@ -947,7 +947,7 @@
         <v>65</v>
       </c>
       <c r="AJ2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AK2" t="n">
         <v>16.5</v>
@@ -965,16 +965,16 @@
         <v>60</v>
       </c>
       <c r="AP2" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AQ2" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AR2" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AT2" t="n">
         <v>12.5</v>
@@ -983,10 +983,10 @@
         <v>11.5</v>
       </c>
       <c r="AV2" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AW2" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AX2" t="n">
         <v>11</v>
@@ -998,7 +998,7 @@
         <v>16</v>
       </c>
       <c r="BA2" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BB2" t="n">
         <v>13.5</v>
@@ -1010,13 +1010,13 @@
         <v>20</v>
       </c>
       <c r="BE2" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BF2" t="n">
         <v>4.3</v>
       </c>
       <c r="BG2" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BH2" t="n">
         <v>5.3</v>
@@ -1028,13 +1028,13 @@
         <v>9.6</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BN2" t="n">
         <v>4.7</v>
@@ -1043,7 +1043,7 @@
         <v>3.75</v>
       </c>
       <c r="BP2" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BQ2" t="n">
         <v>5.3</v>
@@ -1058,7 +1058,7 @@
         <v>11</v>
       </c>
       <c r="BU2" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
@@ -1070,7 +1070,7 @@
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ2" t="n">
         <v>10</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-12 21:31:45</t>
+          <t>2026-07-12 23:39:28</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-12 21:31:45</t>
+          <t>2026-07-12 23:39:28</t>
         </is>
       </c>
     </row>
@@ -1365,67 +1365,67 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="G4" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="H4" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="I4" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J4" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K4" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L4" t="n">
         <v>1.45</v>
       </c>
       <c r="M4" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N4" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O4" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P4" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R4" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S4" t="n">
         <v>3.9</v>
       </c>
       <c r="T4" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="U4" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="V4" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W4" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="X4" t="n">
         <v>12</v>
       </c>
       <c r="Y4" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA4" t="n">
         <v>100</v>
@@ -1437,7 +1437,7 @@
         <v>8</v>
       </c>
       <c r="AD4" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AE4" t="n">
         <v>75</v>
@@ -1446,7 +1446,7 @@
         <v>14</v>
       </c>
       <c r="AG4" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH4" t="n">
         <v>21</v>
@@ -1455,19 +1455,19 @@
         <v>70</v>
       </c>
       <c r="AJ4" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL4" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM4" t="n">
         <v>150</v>
       </c>
       <c r="AN4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AO4" t="n">
         <v>75</v>
@@ -1482,7 +1482,7 @@
         <v>17.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AT4" t="n">
         <v>7.4</v>
@@ -1494,43 +1494,43 @@
         <v>13.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX4" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AY4" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ4" t="n">
         <v>16.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BB4" t="n">
-        <v>22</v>
+        <v>7.2</v>
       </c>
       <c r="BC4" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BD4" t="n">
         <v>32</v>
       </c>
       <c r="BE4" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BF4" t="n">
         <v>16.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BH4" t="n">
         <v>3.2</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="BJ4" t="n">
         <v>10.5</v>
@@ -1545,50 +1545,50 @@
         <v>10.5</v>
       </c>
       <c r="BN4" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BO4" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BP4" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BQ4" t="n">
         <v>6.8</v>
       </c>
       <c r="BR4" t="n">
+        <v>34</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV4" t="n">
         <v>36</v>
       </c>
-      <c r="BS4" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>34</v>
-      </c>
       <c r="BW4" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BX4" t="n">
         <v>50</v>
       </c>
       <c r="BY4" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ4" t="n">
         <v>34</v>
       </c>
       <c r="CA4" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-12 21:31:45</t>
+          <t>2026-07-12 23:39:28</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB4"/>
+  <dimension ref="A1:CB5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -905,10 +905,10 @@
         <v>2.44</v>
       </c>
       <c r="V2" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W2" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="X2" t="n">
         <v>42</v>
@@ -917,7 +917,7 @@
         <v>42</v>
       </c>
       <c r="Z2" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AA2" t="n">
         <v>170</v>
@@ -935,7 +935,7 @@
         <v>80</v>
       </c>
       <c r="AF2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AG2" t="n">
         <v>12.5</v>
@@ -956,7 +956,7 @@
         <v>25</v>
       </c>
       <c r="AM2" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN2" t="n">
         <v>4.8</v>
@@ -965,16 +965,16 @@
         <v>60</v>
       </c>
       <c r="AP2" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AR2" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT2" t="n">
         <v>12.5</v>
@@ -983,10 +983,10 @@
         <v>11.5</v>
       </c>
       <c r="AV2" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AW2" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AX2" t="n">
         <v>11</v>
@@ -998,7 +998,7 @@
         <v>16</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BB2" t="n">
         <v>13.5</v>
@@ -1007,16 +1007,16 @@
         <v>12</v>
       </c>
       <c r="BD2" t="n">
-        <v>20</v>
+        <v>6.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF2" t="n">
         <v>4.3</v>
       </c>
       <c r="BG2" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH2" t="n">
         <v>5.3</v>
@@ -1034,7 +1034,7 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BN2" t="n">
         <v>4.7</v>
@@ -1043,10 +1043,10 @@
         <v>3.75</v>
       </c>
       <c r="BP2" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="BR2" t="n">
         <v>18</v>
@@ -1058,7 +1058,7 @@
         <v>11</v>
       </c>
       <c r="BU2" t="n">
-        <v>8.199999999999999</v>
+        <v>6</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
@@ -1070,17 +1070,17 @@
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ2" t="n">
         <v>10</v>
       </c>
       <c r="CA2" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-12 23:39:28</t>
+          <t>2026-07-13 01:47:23</t>
         </is>
       </c>
     </row>
@@ -1111,19 +1111,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="G3" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="H3" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="I3" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J3" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="K3" t="n">
         <v>5.3</v>
@@ -1135,19 +1135,19 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="O3" t="n">
         <v>1.12</v>
       </c>
       <c r="P3" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="Q3" t="n">
         <v>1.36</v>
       </c>
       <c r="R3" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="S3" t="n">
         <v>1.89</v>
@@ -1159,7 +1159,7 @@
         <v>2.84</v>
       </c>
       <c r="V3" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="W3" t="n">
         <v>2.08</v>
@@ -1168,7 +1168,7 @@
         <v>50</v>
       </c>
       <c r="Y3" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Z3" t="n">
         <v>50</v>
@@ -1186,16 +1186,16 @@
         <v>23</v>
       </c>
       <c r="AE3" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF3" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AG3" t="n">
         <v>14.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AI3" t="n">
         <v>42</v>
@@ -1204,7 +1204,7 @@
         <v>27</v>
       </c>
       <c r="AK3" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AL3" t="n">
         <v>27</v>
@@ -1213,70 +1213,70 @@
         <v>55</v>
       </c>
       <c r="AN3" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AO3" t="n">
         <v>26</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AQ3" t="n">
-        <v>21</v>
+        <v>3.95</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AT3" t="n">
-        <v>13.5</v>
+        <v>3.7</v>
       </c>
       <c r="AU3" t="n">
-        <v>9.4</v>
+        <v>3.45</v>
       </c>
       <c r="AV3" t="n">
-        <v>13.5</v>
+        <v>3.7</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AX3" t="n">
-        <v>12.5</v>
+        <v>3.6</v>
       </c>
       <c r="AY3" t="n">
-        <v>8.6</v>
+        <v>3.4</v>
       </c>
       <c r="AZ3" t="n">
-        <v>11</v>
+        <v>3.6</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BB3" t="n">
-        <v>16</v>
+        <v>3.8</v>
       </c>
       <c r="BC3" t="n">
-        <v>12</v>
+        <v>3.65</v>
       </c>
       <c r="BD3" t="n">
-        <v>16</v>
+        <v>3.8</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>15.5</v>
+        <v>3.8</v>
       </c>
       <c r="BH3" t="n">
         <v>5.7</v>
       </c>
       <c r="BI3" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BJ3" t="n">
         <v>8.800000000000001</v>
@@ -1294,7 +1294,7 @@
         <v>5.6</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="BP3" t="n">
         <v>11.5</v>
@@ -1315,13 +1315,13 @@
         <v>1.01</v>
       </c>
       <c r="BV3" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BW3" t="n">
         <v>1.01</v>
       </c>
       <c r="BX3" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BY3" t="n">
         <v>1.01</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-12 23:39:28</t>
+          <t>2026-07-13 01:47:23</t>
         </is>
       </c>
     </row>
@@ -1365,37 +1365,37 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="G4" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="H4" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="I4" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="J4" t="n">
         <v>3.25</v>
       </c>
       <c r="K4" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L4" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M4" t="n">
         <v>1.08</v>
       </c>
       <c r="N4" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O4" t="n">
         <v>1.37</v>
       </c>
       <c r="P4" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q4" t="n">
         <v>2.12</v>
@@ -1404,31 +1404,31 @@
         <v>1.27</v>
       </c>
       <c r="S4" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="T4" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U4" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="V4" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W4" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="X4" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Y4" t="n">
         <v>13.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AA4" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AB4" t="n">
         <v>8.800000000000001</v>
@@ -1437,28 +1437,28 @@
         <v>8</v>
       </c>
       <c r="AD4" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AF4" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG4" t="n">
         <v>11.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI4" t="n">
         <v>70</v>
       </c>
       <c r="AJ4" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AK4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL4" t="n">
         <v>46</v>
@@ -1467,43 +1467,43 @@
         <v>150</v>
       </c>
       <c r="AN4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO4" t="n">
         <v>75</v>
       </c>
       <c r="AP4" t="n">
-        <v>9.800000000000001</v>
+        <v>5.4</v>
       </c>
       <c r="AQ4" t="n">
-        <v>10.5</v>
+        <v>5.6</v>
       </c>
       <c r="AR4" t="n">
-        <v>17.5</v>
+        <v>7.4</v>
       </c>
       <c r="AS4" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT4" t="n">
-        <v>7.4</v>
+        <v>4.6</v>
       </c>
       <c r="AU4" t="n">
-        <v>6.6</v>
+        <v>4.3</v>
       </c>
       <c r="AV4" t="n">
-        <v>13.5</v>
+        <v>6.2</v>
       </c>
       <c r="AW4" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AX4" t="n">
-        <v>11</v>
+        <v>5.6</v>
       </c>
       <c r="AY4" t="n">
-        <v>9.4</v>
+        <v>5.2</v>
       </c>
       <c r="AZ4" t="n">
-        <v>16.5</v>
+        <v>6.4</v>
       </c>
       <c r="BA4" t="n">
         <v>8.4</v>
@@ -1512,28 +1512,28 @@
         <v>7.2</v>
       </c>
       <c r="BC4" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="BD4" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="BE4" t="n">
         <v>9</v>
       </c>
       <c r="BF4" t="n">
-        <v>16.5</v>
+        <v>6.6</v>
       </c>
       <c r="BG4" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH4" t="n">
         <v>3.2</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="BJ4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK4" t="n">
         <v>6.2</v>
@@ -1542,53 +1542,307 @@
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN4" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BO4" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BP4" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BQ4" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BR4" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BS4" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT4" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BU4" t="n">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="BV4" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BW4" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX4" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BY4" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ4" t="n">
         <v>34</v>
       </c>
       <c r="CA4" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-12 23:39:28</t>
+          <t>2026-07-13 01:47:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Delfin</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="X5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>38</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>21</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>34</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>14</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>21</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>21</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>21</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>21</v>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>2026-07-13 01:47:23</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-14.xlsx
@@ -866,7 +866,7 @@
         <v>6.2</v>
       </c>
       <c r="I2" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J2" t="n">
         <v>5.1</v>
@@ -875,7 +875,7 @@
         <v>5.7</v>
       </c>
       <c r="L2" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="M2" t="n">
         <v>1.02</v>
@@ -971,7 +971,7 @@
         <v>7.6</v>
       </c>
       <c r="AR2" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS2" t="n">
         <v>8.199999999999999</v>
@@ -998,7 +998,7 @@
         <v>16</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BB2" t="n">
         <v>13.5</v>
@@ -1007,16 +1007,16 @@
         <v>12</v>
       </c>
       <c r="BD2" t="n">
-        <v>6.6</v>
+        <v>20</v>
       </c>
       <c r="BE2" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BF2" t="n">
         <v>4.3</v>
       </c>
       <c r="BG2" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BH2" t="n">
         <v>5.3</v>
@@ -1034,7 +1034,7 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BN2" t="n">
         <v>4.7</v>
@@ -1043,7 +1043,7 @@
         <v>3.75</v>
       </c>
       <c r="BP2" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BQ2" t="n">
         <v>6.8</v>
@@ -1052,7 +1052,7 @@
         <v>18</v>
       </c>
       <c r="BS2" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BT2" t="n">
         <v>11</v>
@@ -1064,23 +1064,23 @@
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
+        <v>10</v>
+      </c>
+      <c r="BZ2" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="BZ2" t="n">
-        <v>10</v>
-      </c>
       <c r="CA2" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-13 01:47:23</t>
+          <t>2026-07-13 03:55:13</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
         <v>4.5</v>
       </c>
       <c r="J3" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="K3" t="n">
         <v>5.3</v>
@@ -1135,22 +1135,22 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="O3" t="n">
         <v>1.12</v>
       </c>
       <c r="P3" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="R3" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="S3" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="T3" t="n">
         <v>1.43</v>
@@ -1195,7 +1195,7 @@
         <v>14.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AI3" t="n">
         <v>42</v>
@@ -1213,7 +1213,7 @@
         <v>55</v>
       </c>
       <c r="AN3" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AO3" t="n">
         <v>26</v>
@@ -1222,119 +1222,119 @@
         <v>4.1</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3.95</v>
+        <v>21</v>
       </c>
       <c r="AR3" t="n">
         <v>4.1</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.7</v>
+        <v>13.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.45</v>
+        <v>10.5</v>
       </c>
       <c r="AV3" t="n">
-        <v>3.7</v>
+        <v>13.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AX3" t="n">
-        <v>3.6</v>
+        <v>12.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>3.4</v>
+        <v>10</v>
       </c>
       <c r="AZ3" t="n">
-        <v>3.6</v>
+        <v>11</v>
       </c>
       <c r="BA3" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BB3" t="n">
-        <v>3.8</v>
+        <v>18.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.65</v>
+        <v>12</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.8</v>
+        <v>18.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.1</v>
+        <v>34</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.8</v>
+        <v>15</v>
       </c>
       <c r="BH3" t="n">
         <v>5.7</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BJ3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BN3" t="n">
         <v>5.6</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BP3" t="n">
         <v>11.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BR3" t="n">
         <v>18</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BT3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BV3" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BZ3" t="n">
         <v>11</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-13 01:47:23</t>
+          <t>2026-07-13 03:55:13</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
         <v>2.24</v>
       </c>
       <c r="H4" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="I4" t="n">
         <v>4.5</v>
@@ -1380,16 +1380,16 @@
         <v>3.25</v>
       </c>
       <c r="K4" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L4" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="M4" t="n">
         <v>1.08</v>
       </c>
       <c r="N4" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O4" t="n">
         <v>1.37</v>
@@ -1398,7 +1398,7 @@
         <v>1.73</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R4" t="n">
         <v>1.27</v>
@@ -1410,10 +1410,10 @@
         <v>1.87</v>
       </c>
       <c r="U4" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="V4" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="W4" t="n">
         <v>1.81</v>
@@ -1425,13 +1425,13 @@
         <v>13.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA4" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AB4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC4" t="n">
         <v>8</v>
@@ -1449,7 +1449,7 @@
         <v>11.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI4" t="n">
         <v>70</v>
@@ -1470,67 +1470,67 @@
         <v>21</v>
       </c>
       <c r="AO4" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AP4" t="n">
-        <v>5.4</v>
+        <v>10</v>
       </c>
       <c r="AQ4" t="n">
-        <v>5.6</v>
+        <v>11</v>
       </c>
       <c r="AR4" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AS4" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT4" t="n">
-        <v>4.6</v>
+        <v>7.2</v>
       </c>
       <c r="AU4" t="n">
-        <v>4.3</v>
+        <v>6.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>6.2</v>
+        <v>14.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>8.199999999999999</v>
+        <v>44</v>
       </c>
       <c r="AX4" t="n">
-        <v>5.6</v>
+        <v>10.5</v>
       </c>
       <c r="AY4" t="n">
-        <v>5.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ4" t="n">
-        <v>6.4</v>
+        <v>16.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB4" t="n">
-        <v>7.2</v>
+        <v>22</v>
       </c>
       <c r="BC4" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="BD4" t="n">
         <v>8</v>
       </c>
       <c r="BE4" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF4" t="n">
-        <v>6.6</v>
+        <v>17</v>
       </c>
       <c r="BG4" t="n">
         <v>8.6</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="BJ4" t="n">
         <v>11</v>
@@ -1542,10 +1542,10 @@
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BN4" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BO4" t="n">
         <v>4.1</v>
@@ -1554,41 +1554,41 @@
         <v>17</v>
       </c>
       <c r="BQ4" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BR4" t="n">
         <v>36</v>
       </c>
       <c r="BS4" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BT4" t="n">
         <v>7.6</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="BV4" t="n">
         <v>38</v>
       </c>
       <c r="BW4" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BX4" t="n">
         <v>55</v>
       </c>
       <c r="BY4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ4" t="n">
         <v>34</v>
       </c>
       <c r="CA4" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-13 01:47:23</t>
+          <t>2026-07-13 03:55:13</t>
         </is>
       </c>
     </row>
@@ -1619,13 +1619,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="G5" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="H5" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="I5" t="n">
         <v>4.1</v>
@@ -1640,166 +1640,166 @@
         <v>1.59</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="N5" t="n">
-        <v>1.43</v>
+        <v>2.36</v>
       </c>
       <c r="O5" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="P5" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="R5" t="n">
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="T5" t="n">
-        <v>1.88</v>
+        <v>2.2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="V5" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W5" t="n">
         <v>1.61</v>
       </c>
       <c r="X5" t="n">
-        <v>10.5</v>
+        <v>7.8</v>
       </c>
       <c r="Y5" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG5" t="n">
         <v>13.5</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AH5" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>290</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>60</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>140</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF5" t="n">
         <v>34</v>
       </c>
-      <c r="AA5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>25</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>100</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>38</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>55</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>100</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>2.66</v>
-      </c>
       <c r="BG5" t="n">
-        <v>2.66</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH5" t="n">
         <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="BJ5" t="n">
         <v>17.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>7.4</v>
+        <v>1.5</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>21</v>
+        <v>1.63</v>
       </c>
       <c r="BN5" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BO5" t="n">
         <v>3.4</v>
@@ -1808,41 +1808,41 @@
         <v>34</v>
       </c>
       <c r="BQ5" t="n">
-        <v>14</v>
+        <v>1.56</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>21</v>
+        <v>1.6</v>
       </c>
       <c r="BT5" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BU5" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>21</v>
+        <v>1.6</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>21</v>
+        <v>1.61</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>21</v>
+        <v>1.61</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-13 01:47:23</t>
+          <t>2026-07-13 03:55:13</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB5"/>
+  <dimension ref="A1:CB6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,109 +857,109 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="G2" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="H2" t="n">
         <v>6.2</v>
       </c>
       <c r="I2" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J2" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="K2" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="L2" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="M2" t="n">
         <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="O2" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="P2" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="R2" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="S2" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="T2" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="U2" t="n">
-        <v>2.44</v>
+        <v>2.66</v>
       </c>
       <c r="V2" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W2" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="X2" t="n">
         <v>42</v>
       </c>
       <c r="Y2" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="Z2" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AA2" t="n">
         <v>170</v>
       </c>
       <c r="AB2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AC2" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AD2" t="n">
         <v>28</v>
       </c>
       <c r="AE2" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AF2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG2" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH2" t="n">
         <v>22</v>
       </c>
       <c r="AI2" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AJ2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AK2" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AL2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AM2" t="n">
         <v>65</v>
       </c>
       <c r="AN2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AO2" t="n">
         <v>60</v>
@@ -968,40 +968,40 @@
         <v>7.6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AR2" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AS2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AT2" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX2" t="n">
         <v>11.5</v>
       </c>
-      <c r="AV2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>11</v>
-      </c>
       <c r="AY2" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AZ2" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BB2" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BC2" t="n">
         <v>12</v>
@@ -1010,7 +1010,7 @@
         <v>20</v>
       </c>
       <c r="BE2" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BF2" t="n">
         <v>4.3</v>
@@ -1034,13 +1034,13 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BN2" t="n">
         <v>4.7</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BP2" t="n">
         <v>8.800000000000001</v>
@@ -1052,35 +1052,35 @@
         <v>18</v>
       </c>
       <c r="BS2" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BT2" t="n">
         <v>11</v>
       </c>
       <c r="BU2" t="n">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BZ2" t="n">
         <v>10</v>
       </c>
-      <c r="BZ2" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="CA2" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-13 03:55:13</t>
+          <t>2026-07-13 06:03:21</t>
         </is>
       </c>
     </row>
@@ -1168,13 +1168,13 @@
         <v>50</v>
       </c>
       <c r="Y3" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="Z3" t="n">
         <v>50</v>
       </c>
       <c r="AA3" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AB3" t="n">
         <v>23</v>
@@ -1204,7 +1204,7 @@
         <v>27</v>
       </c>
       <c r="AK3" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AL3" t="n">
         <v>27</v>
@@ -1219,16 +1219,16 @@
         <v>26</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AQ3" t="n">
         <v>21</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AT3" t="n">
         <v>13.5</v>
@@ -1240,7 +1240,7 @@
         <v>13.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AX3" t="n">
         <v>12.5</v>
@@ -1252,19 +1252,19 @@
         <v>11</v>
       </c>
       <c r="BA3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB3" t="n">
         <v>4.1</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>18.5</v>
       </c>
       <c r="BC3" t="n">
         <v>12</v>
       </c>
       <c r="BD3" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="BE3" t="n">
-        <v>34</v>
+        <v>4.4</v>
       </c>
       <c r="BF3" t="n">
         <v>5.1</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-13 03:55:13</t>
+          <t>2026-07-13 06:03:21</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="G4" t="n">
         <v>2.24</v>
@@ -1377,10 +1377,10 @@
         <v>4.5</v>
       </c>
       <c r="J4" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K4" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L4" t="n">
         <v>1.38</v>
@@ -1566,7 +1566,7 @@
         <v>7.6</v>
       </c>
       <c r="BU4" t="n">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="BV4" t="n">
         <v>38</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-13 03:55:13</t>
+          <t>2026-07-13 06:03:21</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
         <v>27</v>
       </c>
       <c r="AA5" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AB5" t="n">
         <v>7.2</v>
@@ -1772,7 +1772,7 @@
         <v>8.4</v>
       </c>
       <c r="BE5" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF5" t="n">
         <v>34</v>
@@ -1842,7 +1842,261 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-13 03:55:13</t>
+          <t>2026-07-13 06:03:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Bolivian Liga de Futbol Profesional</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Blooming Santa Cruz</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>CD Gualberto Villarroel</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>2026-07-13 06:03:21</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB6"/>
+  <dimension ref="A1:CB18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="G2" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="H2" t="n">
         <v>6.2</v>
@@ -869,64 +869,64 @@
         <v>7</v>
       </c>
       <c r="J2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="K2" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="M2" t="n">
         <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="O2" t="n">
         <v>1.13</v>
       </c>
       <c r="P2" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="Q2" t="n">
         <v>1.41</v>
       </c>
       <c r="R2" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="S2" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="T2" t="n">
         <v>1.53</v>
       </c>
       <c r="U2" t="n">
-        <v>2.66</v>
+        <v>2.56</v>
       </c>
       <c r="V2" t="n">
         <v>1.17</v>
       </c>
       <c r="W2" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="X2" t="n">
+        <v>44</v>
+      </c>
+      <c r="Y2" t="n">
         <v>42</v>
       </c>
-      <c r="Y2" t="n">
-        <v>40</v>
-      </c>
       <c r="Z2" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AA2" t="n">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="AB2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AC2" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AD2" t="n">
         <v>28</v>
@@ -935,58 +935,58 @@
         <v>75</v>
       </c>
       <c r="AF2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AG2" t="n">
         <v>10.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AJ2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AK2" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AL2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AM2" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AN2" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AO2" t="n">
         <v>60</v>
       </c>
       <c r="AP2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR2" t="n">
         <v>7.6</v>
       </c>
-      <c r="AQ2" t="n">
+      <c r="AS2" t="n">
         <v>7.4</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>8.4</v>
       </c>
       <c r="AT2" t="n">
         <v>13</v>
       </c>
       <c r="AU2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AV2" t="n">
-        <v>18.5</v>
+        <v>6.4</v>
       </c>
       <c r="AW2" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AX2" t="n">
         <v>11.5</v>
@@ -998,67 +998,67 @@
         <v>15.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BB2" t="n">
         <v>14.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>20</v>
+        <v>6.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BF2" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BG2" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BH2" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BI2" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BJ2" t="n">
         <v>9.6</v>
       </c>
       <c r="BK2" t="n">
-        <v>7.2</v>
+        <v>5.6</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BN2" t="n">
         <v>4.7</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="BP2" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.8</v>
+        <v>5.4</v>
       </c>
       <c r="BR2" t="n">
         <v>18</v>
       </c>
       <c r="BS2" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BT2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BU2" t="n">
-        <v>8.4</v>
+        <v>5.9</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
@@ -1070,17 +1070,17 @@
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="CA2" t="n">
-        <v>7.8</v>
+        <v>5.9</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-13 06:03:21</t>
+          <t>2026-07-13 08:12:39</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="G3" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="H3" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="I3" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="J3" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K3" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L3" t="n">
         <v>1.18</v>
@@ -1147,34 +1147,34 @@
         <v>1.37</v>
       </c>
       <c r="R3" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="S3" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="T3" t="n">
         <v>1.43</v>
       </c>
       <c r="U3" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="V3" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="W3" t="n">
         <v>2.08</v>
       </c>
       <c r="X3" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="Y3" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="Z3" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AA3" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AB3" t="n">
         <v>23</v>
@@ -1183,28 +1183,28 @@
         <v>15.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE3" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF3" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AG3" t="n">
         <v>14.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AJ3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AK3" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AL3" t="n">
         <v>27</v>
@@ -1213,64 +1213,64 @@
         <v>55</v>
       </c>
       <c r="AN3" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AO3" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AQ3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="AT3" t="n">
         <v>13.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV3" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="AX3" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AY3" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="AZ3" t="n">
         <v>11</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.1</v>
+        <v>19.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.4</v>
+        <v>34</v>
       </c>
       <c r="BF3" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="BG3" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BH3" t="n">
         <v>5.7</v>
@@ -1288,43 +1288,43 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BN3" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BO3" t="n">
         <v>4.7</v>
       </c>
       <c r="BP3" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BQ3" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BR3" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BS3" t="n">
         <v>6.4</v>
       </c>
       <c r="BT3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BU3" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BV3" t="n">
+        <v>27</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BX3" t="n">
         <v>28</v>
       </c>
-      <c r="BW3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BX3" t="n">
-        <v>1000</v>
-      </c>
       <c r="BY3" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BZ3" t="n">
         <v>11</v>
@@ -1334,14 +1334,14 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-13 06:03:21</t>
+          <t>2026-07-13 08:12:39</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1351,251 +1351,251 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Macara</t>
+          <t>CS Dock Sud</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Uai Urquiza</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.02</v>
+        <v>1.04</v>
       </c>
       <c r="G4" t="n">
-        <v>2.24</v>
+        <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>3.85</v>
+        <v>1.04</v>
       </c>
       <c r="I4" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>3.3</v>
+        <v>1.02</v>
       </c>
       <c r="K4" t="n">
-        <v>3.75</v>
+        <v>1000</v>
       </c>
       <c r="L4" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>3.1</v>
+        <v>1.05</v>
       </c>
       <c r="O4" t="n">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="P4" t="n">
-        <v>1.73</v>
+        <v>1.05</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="R4" t="n">
-        <v>1.27</v>
+        <v>1.05</v>
       </c>
       <c r="S4" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="T4" t="n">
-        <v>1.87</v>
+        <v>1.01</v>
       </c>
       <c r="U4" t="n">
-        <v>1.94</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>1.81</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AR4" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AU4" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV4" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW4" t="n">
-        <v>44</v>
+        <v>1.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY4" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA4" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BB4" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BC4" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BD4" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BE4" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.25</v>
+        <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.78</v>
+        <v>1.01</v>
       </c>
       <c r="BJ4" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BN4" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BP4" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BR4" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BT4" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BV4" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BX4" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-13 06:03:21</t>
+          <t>2026-07-13 08:12:39</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,251 +1605,251 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Flandria</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Delfin</t>
+          <t>Argentino de Merlo</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.36</v>
+        <v>1.04</v>
       </c>
       <c r="G5" t="n">
-        <v>2.64</v>
+        <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>3.65</v>
+        <v>1.04</v>
       </c>
       <c r="I5" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>2.82</v>
+        <v>1.02</v>
       </c>
       <c r="K5" t="n">
-        <v>3.1</v>
+        <v>1000</v>
       </c>
       <c r="L5" t="n">
-        <v>1.59</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>2.36</v>
+        <v>1.05</v>
       </c>
       <c r="O5" t="n">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="P5" t="n">
-        <v>1.44</v>
+        <v>1.05</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.86</v>
+        <v>1.01</v>
       </c>
       <c r="R5" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="S5" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="T5" t="n">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>290</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AR5" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AS5" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AT5" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AU5" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AV5" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AW5" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AX5" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY5" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BA5" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BB5" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BC5" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BD5" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BE5" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BF5" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="n">
         <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.63</v>
+        <v>1.01</v>
       </c>
       <c r="BJ5" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.63</v>
+        <v>1.01</v>
       </c>
       <c r="BN5" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="BP5" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="BT5" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-13 06:03:21</t>
+          <t>2026-07-13 08:12:39</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,24 +1859,24 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Blooming Santa Cruz</t>
+          <t>Sportivo Italiano</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CD Gualberto Villarroel</t>
+          <t>Villa San Carlos</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.21</v>
+        <v>1.04</v>
       </c>
       <c r="G6" t="n">
-        <v>1.72</v>
+        <v>1000</v>
       </c>
       <c r="H6" t="n">
         <v>1.04</v>
@@ -1897,206 +1897,3254 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>2026-07-13 08:12:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Argentinian Primera B Metropolitana</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Defensores Unidos</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Excursionistas</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>2026-07-13 08:12:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Argentinian Primera B Metropolitana</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Argentino de Quilmes</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Arsenal de Sarandi</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>2026-07-13 08:12:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Icelandic 1 Deild</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Grotta</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Grindavik</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>2026-07-13 08:12:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Argentinian Primera B Metropolitana</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>15:30:00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Deportivo Armenio</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Talleres (RE)</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>2026-07-13 08:12:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Macara</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="V11" t="n">
         <v>1.31</v>
       </c>
-      <c r="O6" t="n">
+      <c r="W11" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="X11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>7</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>34</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>38</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>10</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>32</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>9</v>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>2026-07-13 08:12:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Argentinian Primera B Metropolitana</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Brown de Adrogue</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Deportivo Laferrere</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>2026-07-13 08:12:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Argentinian Primera B Metropolitana</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Deportivo Merlo</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Real Pilar FC</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB13" t="inlineStr">
+        <is>
+          <t>2026-07-13 08:12:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Argentinian Primera B Metropolitana</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Comunicaciones B Aires</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Villa Dalmine</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB14" t="inlineStr">
+        <is>
+          <t>2026-07-13 08:12:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Argentinian Primera B Metropolitana</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>CA Ituzaingo</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>San Martin de Burzaco</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB15" t="inlineStr">
+        <is>
+          <t>2026-07-13 08:12:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Bolivian Liga de Futbol Profesional</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>CDT Real Oruro</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Always Ready</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K16" t="n">
+        <v>950</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB16" t="inlineStr">
+        <is>
+          <t>2026-07-13 08:12:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Delfin</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X17" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>95</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>260</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>85</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>44</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>42</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>50</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>50</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>28</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>8</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="CB17" t="inlineStr">
+        <is>
+          <t>2026-07-13 08:12:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Bolivian Liga de Futbol Profesional</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Blooming Santa Cruz</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>CD Gualberto Villarroel</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="O18" t="n">
         <v>1.14</v>
       </c>
-      <c r="P6" t="n">
+      <c r="P18" t="n">
         <v>1.31</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="Q18" t="n">
         <v>1.14</v>
       </c>
-      <c r="R6" t="n">
+      <c r="R18" t="n">
         <v>1.28</v>
       </c>
-      <c r="S6" t="n">
+      <c r="S18" t="n">
         <v>1.14</v>
       </c>
-      <c r="T6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BZ6" t="n">
+      <c r="T18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ18" t="n">
         <v>0</v>
       </c>
-      <c r="CA6" t="n">
+      <c r="CA18" t="n">
         <v>0</v>
       </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>2026-07-13 06:03:21</t>
+      <c r="CB18" t="inlineStr">
+        <is>
+          <t>2026-07-13 08:12:39</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB18"/>
+  <dimension ref="A1:CB19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,61 +857,61 @@
         </is>
       </c>
       <c r="F2" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="G2" t="n">
         <v>1.51</v>
       </c>
-      <c r="G2" t="n">
-        <v>1.55</v>
-      </c>
       <c r="H2" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="I2" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="J2" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="K2" t="n">
         <v>5.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="M2" t="n">
         <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="O2" t="n">
         <v>1.13</v>
       </c>
       <c r="P2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="Q2" t="n">
         <v>1.41</v>
       </c>
       <c r="R2" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="S2" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="T2" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="U2" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="V2" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W2" t="n">
-        <v>2.82</v>
+        <v>2.96</v>
       </c>
       <c r="X2" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Y2" t="n">
         <v>42</v>
@@ -923,10 +923,10 @@
         <v>190</v>
       </c>
       <c r="AB2" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AD2" t="n">
         <v>28</v>
@@ -935,58 +935,58 @@
         <v>75</v>
       </c>
       <c r="AF2" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH2" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AI2" t="n">
         <v>65</v>
       </c>
       <c r="AJ2" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AK2" t="n">
         <v>14.5</v>
       </c>
       <c r="AL2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AM2" t="n">
         <v>75</v>
       </c>
       <c r="AN2" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="AO2" t="n">
         <v>60</v>
       </c>
       <c r="AP2" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ2" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR2" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AV2" t="n">
-        <v>6.4</v>
+        <v>18.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX2" t="n">
         <v>11.5</v>
@@ -995,40 +995,40 @@
         <v>9</v>
       </c>
       <c r="AZ2" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB2" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BC2" t="n">
         <v>11.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BE2" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF2" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="BG2" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH2" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BI2" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BJ2" t="n">
         <v>9.6</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
@@ -1043,7 +1043,7 @@
         <v>4.1</v>
       </c>
       <c r="BP2" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BQ2" t="n">
         <v>5.4</v>
@@ -1052,19 +1052,19 @@
         <v>18</v>
       </c>
       <c r="BS2" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BT2" t="n">
+        <v>11</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW2" t="n">
         <v>10.5</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>10</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
@@ -1073,14 +1073,14 @@
         <v>10</v>
       </c>
       <c r="BZ2" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CA2" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-13 08:12:39</t>
+          <t>2026-07-13 10:21:51</t>
         </is>
       </c>
     </row>
@@ -1120,13 +1120,13 @@
         <v>3.7</v>
       </c>
       <c r="I3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J3" t="n">
         <v>4.3</v>
       </c>
       <c r="K3" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L3" t="n">
         <v>1.18</v>
@@ -1159,7 +1159,7 @@
         <v>2.86</v>
       </c>
       <c r="V3" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W3" t="n">
         <v>2.08</v>
@@ -1186,7 +1186,7 @@
         <v>22</v>
       </c>
       <c r="AE3" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AF3" t="n">
         <v>22</v>
@@ -1216,16 +1216,16 @@
         <v>7.4</v>
       </c>
       <c r="AO3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AP3" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AQ3" t="n">
         <v>20</v>
       </c>
       <c r="AR3" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AS3" t="n">
         <v>4.1</v>
@@ -1234,7 +1234,7 @@
         <v>13.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AV3" t="n">
         <v>13</v>
@@ -1252,13 +1252,13 @@
         <v>11</v>
       </c>
       <c r="BA3" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BB3" t="n">
         <v>19.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BD3" t="n">
         <v>18.5</v>
@@ -1267,16 +1267,16 @@
         <v>34</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BG3" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="BH3" t="n">
         <v>5.7</v>
       </c>
       <c r="BI3" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BJ3" t="n">
         <v>8.800000000000001</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-13 08:12:39</t>
+          <t>2026-07-13 10:21:51</t>
         </is>
       </c>
     </row>
@@ -1356,31 +1356,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CS Dock Sud</t>
+          <t>Camioneros</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Uai Urquiza</t>
+          <t>CSD Liniers de Ciudad Evita</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.04</v>
+        <v>1.5</v>
       </c>
       <c r="G4" t="n">
         <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>1.04</v>
+        <v>2.2</v>
       </c>
       <c r="I4" t="n">
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="K4" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
@@ -1389,19 +1389,19 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.05</v>
+        <v>1.24</v>
       </c>
       <c r="O4" t="n">
         <v>1.01</v>
       </c>
       <c r="P4" t="n">
-        <v>1.05</v>
+        <v>1.24</v>
       </c>
       <c r="Q4" t="n">
         <v>1.01</v>
       </c>
       <c r="R4" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="S4" t="n">
         <v>1.01</v>
@@ -1473,52 +1473,52 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF4" t="n">
         <v>1.01</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-13 08:12:39</t>
+          <t>2026-07-13 10:21:51</t>
         </is>
       </c>
     </row>
@@ -1610,22 +1610,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Flandria</t>
+          <t>Argentino de Quilmes</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Argentino de Merlo</t>
+          <t>Arsenal de Sarandi</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.04</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
         <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>1.04</v>
+        <v>1.65</v>
       </c>
       <c r="I5" t="n">
         <v>1000</v>
@@ -1634,7 +1634,7 @@
         <v>1.02</v>
       </c>
       <c r="K5" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1643,22 +1643,22 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="O5" t="n">
         <v>1.01</v>
       </c>
       <c r="P5" t="n">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R5" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="S5" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1727,52 +1727,52 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF5" t="n">
         <v>1.01</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-13 08:12:39</t>
+          <t>2026-07-13 10:21:51</t>
         </is>
       </c>
     </row>
@@ -1864,67 +1864,67 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Sportivo Italiano</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Villa San Carlos</t>
+          <t>Excursionistas</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.04</v>
+        <v>2.1</v>
       </c>
       <c r="G6" t="n">
         <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>1.04</v>
+        <v>1.5</v>
       </c>
       <c r="I6" t="n">
         <v>1000</v>
       </c>
       <c r="J6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K6" t="n">
+        <v>950</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V6" t="n">
         <v>1.02</v>
       </c>
-      <c r="K6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.01</v>
-      </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -1981,52 +1981,52 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF6" t="n">
         <v>1.01</v>
@@ -2096,14 +2096,14 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-13 08:12:39</t>
+          <t>2026-07-13 10:21:51</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2118,121 +2118,121 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Grotta</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Excursionistas</t>
+          <t>Grindavik</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.04</v>
+        <v>1.92</v>
       </c>
       <c r="G7" t="n">
-        <v>1000</v>
+        <v>2.1</v>
       </c>
       <c r="H7" t="n">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="I7" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="J7" t="n">
-        <v>1.02</v>
+        <v>3.75</v>
       </c>
       <c r="K7" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="M7" t="n">
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.08</v>
+        <v>5.7</v>
       </c>
       <c r="O7" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="P7" t="n">
-        <v>1.08</v>
+        <v>2.94</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="R7" t="n">
-        <v>1.08</v>
+        <v>1.78</v>
       </c>
       <c r="S7" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AP7" t="n">
         <v>1.01</v>
@@ -2289,68 +2289,68 @@
         <v>1.01</v>
       </c>
       <c r="BH7" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BI7" t="n">
         <v>1.01</v>
       </c>
       <c r="BJ7" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BK7" t="n">
         <v>1.01</v>
       </c>
       <c r="BL7" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BM7" t="n">
         <v>1.01</v>
       </c>
       <c r="BN7" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BO7" t="n">
         <v>1.01</v>
       </c>
       <c r="BP7" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BQ7" t="n">
         <v>1.01</v>
       </c>
       <c r="BR7" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BS7" t="n">
         <v>1.01</v>
       </c>
       <c r="BT7" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU7" t="n">
         <v>1.01</v>
       </c>
       <c r="BV7" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BW7" t="n">
         <v>1.01</v>
       </c>
       <c r="BX7" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BY7" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="CA7" t="n">
         <v>1.01</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-13 08:12:39</t>
+          <t>2026-07-13 10:21:51</t>
         </is>
       </c>
     </row>
@@ -2372,67 +2372,67 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Argentino de Quilmes</t>
+          <t>Flandria</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandi</t>
+          <t>Argentino de Merlo</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.04</v>
+        <v>1.7</v>
       </c>
       <c r="G8" t="n">
         <v>1000</v>
       </c>
       <c r="H8" t="n">
-        <v>1.04</v>
+        <v>1.7</v>
       </c>
       <c r="I8" t="n">
         <v>1000</v>
       </c>
       <c r="J8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K8" t="n">
+        <v>950</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V8" t="n">
         <v>1.02</v>
       </c>
-      <c r="K8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.01</v>
-      </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2489,52 +2489,52 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF8" t="n">
         <v>1.01</v>
@@ -2604,14 +2604,14 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-13 08:12:39</t>
+          <t>2026-07-13 10:21:51</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2626,31 +2626,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Grotta</t>
+          <t>CS Dock Sud</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Grindavik</t>
+          <t>Uai Urquiza</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.04</v>
+        <v>1.5</v>
       </c>
       <c r="G9" t="n">
         <v>1000</v>
       </c>
       <c r="H9" t="n">
-        <v>1.04</v>
+        <v>2.2</v>
       </c>
       <c r="I9" t="n">
         <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="K9" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
@@ -2662,19 +2662,19 @@
         <v>1.25</v>
       </c>
       <c r="O9" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="P9" t="n">
         <v>1.25</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.13</v>
+        <v>1.53</v>
       </c>
       <c r="R9" t="n">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="S9" t="n">
-        <v>1.13</v>
+        <v>1.55</v>
       </c>
       <c r="T9" t="n">
         <v>1.01</v>
@@ -2683,10 +2683,10 @@
         <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2743,52 +2743,52 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF9" t="n">
         <v>1.01</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-13 08:12:39</t>
+          <t>2026-07-13 10:21:51</t>
         </is>
       </c>
     </row>
@@ -2875,27 +2875,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Deportivo Armenio</t>
+          <t>Sportivo Italiano</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Talleres (RE)</t>
+          <t>Villa San Carlos</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G10" t="n">
         <v>1000</v>
       </c>
       <c r="H10" t="n">
-        <v>1.04</v>
+        <v>2.4</v>
       </c>
       <c r="I10" t="n">
         <v>1000</v>
@@ -2904,7 +2904,7 @@
         <v>1.02</v>
       </c>
       <c r="K10" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2913,22 +2913,22 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="O10" t="n">
         <v>1.01</v>
       </c>
       <c r="P10" t="n">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="Q10" t="n">
         <v>1.01</v>
       </c>
       <c r="R10" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="S10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="T10" t="n">
         <v>1.01</v>
@@ -2997,52 +2997,52 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF10" t="n">
         <v>1.01</v>
@@ -3112,14 +3112,14 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-13 08:12:39</t>
+          <t>2026-07-13 10:21:51</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3129,251 +3129,251 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Macara</t>
+          <t>Deportivo Armenio</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Talleres (RE)</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>2.2</v>
+        <v>1000</v>
       </c>
       <c r="H11" t="n">
-        <v>3.9</v>
+        <v>1.7</v>
       </c>
       <c r="I11" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>3.35</v>
+        <v>1.03</v>
       </c>
       <c r="K11" t="n">
-        <v>3.7</v>
+        <v>950</v>
       </c>
       <c r="L11" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>3.3</v>
+        <v>1.24</v>
       </c>
       <c r="O11" t="n">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="P11" t="n">
-        <v>1.75</v>
+        <v>1.24</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="R11" t="n">
-        <v>1.28</v>
+        <v>1.12</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>1.57</v>
       </c>
       <c r="T11" t="n">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="U11" t="n">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>1.31</v>
+        <v>1.02</v>
       </c>
       <c r="W11" t="n">
-        <v>1.83</v>
+        <v>1.02</v>
       </c>
       <c r="X11" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Y11" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Z11" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA11" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AC11" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD11" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AE11" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH11" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI11" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AL11" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM11" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AQ11" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR11" t="n">
-        <v>5.2</v>
+        <v>1.03</v>
       </c>
       <c r="AS11" t="n">
-        <v>5.9</v>
+        <v>1.03</v>
       </c>
       <c r="AT11" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AU11" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AV11" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AW11" t="n">
-        <v>5.6</v>
+        <v>1.03</v>
       </c>
       <c r="AX11" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AY11" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AZ11" t="n">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA11" t="n">
-        <v>5.7</v>
+        <v>1.03</v>
       </c>
       <c r="BB11" t="n">
-        <v>19.5</v>
+        <v>1.03</v>
       </c>
       <c r="BC11" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="BD11" t="n">
-        <v>5.5</v>
+        <v>1.03</v>
       </c>
       <c r="BE11" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="BF11" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG11" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH11" t="n">
-        <v>3.2</v>
+        <v>1000</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.82</v>
+        <v>1.01</v>
       </c>
       <c r="BJ11" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK11" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN11" t="n">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="BO11" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BP11" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BR11" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BT11" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BU11" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BV11" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BZ11" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-13 08:12:39</t>
+          <t>2026-07-13 10:21:51</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3383,244 +3383,244 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Brown de Adrogue</t>
+          <t>Macara</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Deportivo Laferrere</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.04</v>
+        <v>2.04</v>
       </c>
       <c r="G12" t="n">
-        <v>1000</v>
+        <v>2.18</v>
       </c>
       <c r="H12" t="n">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="I12" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="J12" t="n">
-        <v>1.02</v>
+        <v>3.3</v>
       </c>
       <c r="K12" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M12" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N12" t="n">
-        <v>1.08</v>
+        <v>3.3</v>
       </c>
       <c r="O12" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="P12" t="n">
-        <v>1.04</v>
+        <v>1.76</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="R12" t="n">
-        <v>1.04</v>
+        <v>1.28</v>
       </c>
       <c r="S12" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="T12" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="U12" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="W12" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="X12" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB12" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AE12" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF12" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI12" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK12" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AL12" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM12" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH12" t="n">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.01</v>
+        <v>2.82</v>
       </c>
       <c r="BJ12" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK12" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BN12" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BP12" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BR12" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT12" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BU12" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BV12" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BZ12" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="CA12" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-13 08:12:39</t>
+          <t>2026-07-13 10:21:51</t>
         </is>
       </c>
     </row>
@@ -3642,67 +3642,67 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Deportivo Merlo</t>
+          <t>Brown de Adrogue</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Real Pilar FC</t>
+          <t>Deportivo Laferrere</t>
         </is>
       </c>
       <c r="F13" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J13" t="n">
         <v>1.04</v>
       </c>
-      <c r="G13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V13" t="n">
         <v>1.02</v>
       </c>
-      <c r="K13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N13" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.01</v>
-      </c>
       <c r="W13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -3759,52 +3759,52 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF13" t="n">
         <v>1.01</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-13 08:12:39</t>
+          <t>2026-07-13 10:21:51</t>
         </is>
       </c>
     </row>
@@ -3896,12 +3896,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Comunicaciones B Aires</t>
+          <t>Deportivo Merlo</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Villa Dalmine</t>
+          <t>Real Pilar FC</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -3917,46 +3917,46 @@
         <v>1000</v>
       </c>
       <c r="J14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="K14" t="n">
+        <v>950</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V14" t="n">
         <v>1.02</v>
       </c>
-      <c r="K14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.01</v>
-      </c>
       <c r="W14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -4013,52 +4013,52 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF14" t="n">
         <v>1.01</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-13 08:12:39</t>
+          <t>2026-07-13 10:21:51</t>
         </is>
       </c>
     </row>
@@ -4150,12 +4150,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CA Ituzaingo</t>
+          <t>Comunicaciones B Aires</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>San Martin de Burzaco</t>
+          <t>Villa Dalmine</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -4171,46 +4171,46 @@
         <v>1000</v>
       </c>
       <c r="J15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="K15" t="n">
+        <v>950</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V15" t="n">
         <v>1.02</v>
       </c>
-      <c r="K15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N15" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.01</v>
-      </c>
       <c r="W15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -4267,52 +4267,52 @@
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF15" t="n">
         <v>1.01</v>
@@ -4382,14 +4382,14 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-13 08:12:39</t>
+          <t>2026-07-13 10:21:51</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4404,12 +4404,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CDT Real Oruro</t>
+          <t>CA Ituzaingo</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Always Ready</t>
+          <t>San Martin de Burzaco</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -4425,7 +4425,7 @@
         <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K16" t="n">
         <v>950</v>
@@ -4437,22 +4437,22 @@
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="O16" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="P16" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="R16" t="n">
-        <v>1.31</v>
+        <v>1.12</v>
       </c>
       <c r="S16" t="n">
-        <v>1.13</v>
+        <v>1.51</v>
       </c>
       <c r="T16" t="n">
         <v>1.01</v>
@@ -4461,7 +4461,7 @@
         <v>1.01</v>
       </c>
       <c r="V16" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W16" t="n">
         <v>1.02</v>
@@ -4521,52 +4521,52 @@
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF16" t="n">
         <v>1.01</v>
@@ -4629,21 +4629,21 @@
         <v>1.01</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-13 08:12:39</t>
+          <t>2026-07-13 10:21:51</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4653,498 +4653,752 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>CDT Real Oruro</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Delfin</t>
+          <t>Always Ready</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.82</v>
+        <v>2.2</v>
       </c>
       <c r="G17" t="n">
-        <v>3.05</v>
+        <v>110</v>
       </c>
       <c r="H17" t="n">
-        <v>3.25</v>
+        <v>1.34</v>
       </c>
       <c r="I17" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="J17" t="n">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="K17" t="n">
-        <v>2.94</v>
+        <v>4.6</v>
       </c>
       <c r="L17" t="n">
-        <v>1.66</v>
+        <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>2.32</v>
+        <v>1.32</v>
       </c>
       <c r="O17" t="n">
-        <v>1.64</v>
+        <v>1.12</v>
       </c>
       <c r="P17" t="n">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.1</v>
+        <v>1.19</v>
       </c>
       <c r="R17" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="S17" t="n">
-        <v>6.4</v>
+        <v>1.19</v>
       </c>
       <c r="T17" t="n">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="U17" t="n">
-        <v>1.69</v>
+        <v>1.01</v>
       </c>
       <c r="V17" t="n">
-        <v>1.43</v>
+        <v>1.26</v>
       </c>
       <c r="W17" t="n">
-        <v>1.5</v>
+        <v>1.02</v>
       </c>
       <c r="X17" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="Y17" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="Z17" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AA17" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AC17" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="AD17" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AE17" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AG17" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AH17" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AI17" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AK17" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AL17" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AM17" t="n">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AQ17" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AR17" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AS17" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AT17" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AU17" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV17" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AW17" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AX17" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY17" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ17" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BA17" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BB17" t="n">
-        <v>44</v>
+        <v>1.01</v>
       </c>
       <c r="BC17" t="n">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BD17" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BE17" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BF17" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BG17" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BH17" t="n">
-        <v>2.6</v>
+        <v>1000</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="BJ17" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK17" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN17" t="n">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="BO17" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BP17" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BT17" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BU17" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BZ17" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA17" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-13 08:12:39</t>
+          <t>2026-07-13 10:21:51</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Delfin</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="H18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S18" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="X18" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>95</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>260</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>70</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>50</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>70</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>44</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>42</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>60</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>11</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="CB18" t="inlineStr">
+        <is>
+          <t>2026-07-13 10:21:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>21:30:00</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>Blooming Santa Cruz</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>CD Gualberto Villarroel</t>
         </is>
       </c>
-      <c r="F18" t="n">
+      <c r="F19" t="n">
         <v>1.21</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G19" t="n">
         <v>1.72</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H19" t="n">
         <v>1.04</v>
       </c>
-      <c r="I18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J18" t="n">
+      <c r="I19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J19" t="n">
         <v>1.02</v>
       </c>
-      <c r="K18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N18" t="n">
+      <c r="K19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N19" t="n">
         <v>1.31</v>
       </c>
-      <c r="O18" t="n">
+      <c r="O19" t="n">
         <v>1.14</v>
       </c>
-      <c r="P18" t="n">
+      <c r="P19" t="n">
         <v>1.31</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="Q19" t="n">
         <v>1.14</v>
       </c>
-      <c r="R18" t="n">
+      <c r="R19" t="n">
         <v>1.28</v>
       </c>
-      <c r="S18" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BZ18" t="n">
+      <c r="S19" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ19" t="n">
         <v>0</v>
       </c>
-      <c r="CA18" t="n">
+      <c r="CA19" t="n">
         <v>0</v>
       </c>
-      <c r="CB18" t="inlineStr">
-        <is>
-          <t>2026-07-13 08:12:39</t>
+      <c r="CB19" t="inlineStr">
+        <is>
+          <t>2026-07-13 10:21:51</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-14.xlsx
@@ -863,19 +863,19 @@
         <v>1.51</v>
       </c>
       <c r="H2" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="I2" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J2" t="n">
         <v>5.2</v>
       </c>
       <c r="K2" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="L2" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="M2" t="n">
         <v>1.02</v>
@@ -902,7 +902,7 @@
         <v>1.56</v>
       </c>
       <c r="U2" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="V2" t="n">
         <v>1.16</v>
@@ -935,7 +935,7 @@
         <v>75</v>
       </c>
       <c r="AF2" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AG2" t="n">
         <v>11</v>
@@ -947,10 +947,10 @@
         <v>65</v>
       </c>
       <c r="AJ2" t="n">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="AK2" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AL2" t="n">
         <v>26</v>
@@ -965,16 +965,16 @@
         <v>60</v>
       </c>
       <c r="AP2" t="n">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="AQ2" t="n">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="AR2" t="n">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="AS2" t="n">
-        <v>8.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="AT2" t="n">
         <v>13.5</v>
@@ -986,37 +986,37 @@
         <v>18.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>8.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="AX2" t="n">
         <v>11.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AZ2" t="n">
         <v>16</v>
       </c>
       <c r="BA2" t="n">
-        <v>8.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="BB2" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BC2" t="n">
         <v>11.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="BE2" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BF2" t="n">
         <v>4.1</v>
       </c>
       <c r="BG2" t="n">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="BH2" t="n">
         <v>5.3</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-13 10:21:51</t>
+          <t>2026-07-13 12:31:07</t>
         </is>
       </c>
     </row>
@@ -1120,13 +1120,13 @@
         <v>3.7</v>
       </c>
       <c r="I3" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J3" t="n">
         <v>4.3</v>
       </c>
       <c r="K3" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L3" t="n">
         <v>1.18</v>
@@ -1198,7 +1198,7 @@
         <v>18.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AJ3" t="n">
         <v>28</v>
@@ -1234,13 +1234,13 @@
         <v>13.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AV3" t="n">
         <v>13</v>
       </c>
       <c r="AW3" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AX3" t="n">
         <v>13</v>
@@ -1255,22 +1255,22 @@
         <v>3.85</v>
       </c>
       <c r="BB3" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BC3" t="n">
         <v>12</v>
       </c>
       <c r="BD3" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="BF3" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BG3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BH3" t="n">
         <v>5.7</v>
@@ -1282,7 +1282,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK3" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
@@ -1294,13 +1294,13 @@
         <v>5.7</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="BP3" t="n">
         <v>12</v>
       </c>
       <c r="BQ3" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BR3" t="n">
         <v>18.5</v>
@@ -1312,7 +1312,7 @@
         <v>8.6</v>
       </c>
       <c r="BU3" t="n">
-        <v>6.4</v>
+        <v>4.5</v>
       </c>
       <c r="BV3" t="n">
         <v>27</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-13 10:21:51</t>
+          <t>2026-07-13 12:31:07</t>
         </is>
       </c>
     </row>
@@ -1368,16 +1368,16 @@
         <v>1.5</v>
       </c>
       <c r="G4" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H4" t="n">
         <v>2.2</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="K4" t="n">
         <v>950</v>
@@ -1389,7 +1389,7 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O4" t="n">
         <v>1.01</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-13 10:21:51</t>
+          <t>2026-07-13 12:31:07</t>
         </is>
       </c>
     </row>
@@ -1622,16 +1622,16 @@
         <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="H5" t="n">
         <v>1.65</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>870</v>
       </c>
       <c r="J5" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K5" t="n">
         <v>950</v>
@@ -1643,22 +1643,22 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="O5" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="P5" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.02</v>
+        <v>1.3</v>
       </c>
       <c r="R5" t="n">
         <v>1.12</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1667,7 +1667,7 @@
         <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W5" t="n">
         <v>1.01</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-13 10:21:51</t>
+          <t>2026-07-13 12:31:07</t>
         </is>
       </c>
     </row>
@@ -1876,16 +1876,16 @@
         <v>2.1</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="H6" t="n">
         <v>1.5</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>870</v>
       </c>
       <c r="J6" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="K6" t="n">
         <v>950</v>
@@ -1897,22 +1897,22 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="O6" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="P6" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.34</v>
+        <v>1.5</v>
       </c>
       <c r="R6" t="n">
         <v>1.12</v>
       </c>
       <c r="S6" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="T6" t="n">
         <v>1.01</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-13 10:21:51</t>
+          <t>2026-07-13 12:31:07</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="G7" t="n">
         <v>2.1</v>
@@ -2136,13 +2136,13 @@
         <v>3.35</v>
       </c>
       <c r="I7" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="J7" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="K7" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L7" t="n">
         <v>1.2</v>
@@ -2151,88 +2151,88 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>5.7</v>
+        <v>1.1</v>
       </c>
       <c r="O7" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="P7" t="n">
-        <v>2.94</v>
+        <v>2.86</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="R7" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="S7" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="T7" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="U7" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="V7" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W7" t="n">
         <v>1.91</v>
       </c>
       <c r="X7" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="Y7" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="Z7" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AA7" t="n">
         <v>75</v>
       </c>
       <c r="AB7" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AD7" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AE7" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AF7" t="n">
         <v>22</v>
       </c>
       <c r="AG7" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AH7" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AJ7" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AK7" t="n">
         <v>19</v>
       </c>
       <c r="AL7" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AM7" t="n">
         <v>60</v>
       </c>
       <c r="AN7" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO7" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AP7" t="n">
         <v>1.01</v>
@@ -2289,13 +2289,13 @@
         <v>1.01</v>
       </c>
       <c r="BH7" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BI7" t="n">
         <v>1.01</v>
       </c>
       <c r="BJ7" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK7" t="n">
         <v>1.01</v>
@@ -2319,7 +2319,7 @@
         <v>1.01</v>
       </c>
       <c r="BR7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BS7" t="n">
         <v>1.01</v>
@@ -2331,26 +2331,26 @@
         <v>1.01</v>
       </c>
       <c r="BV7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BW7" t="n">
         <v>1.01</v>
       </c>
       <c r="BX7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BY7" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ7" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="CA7" t="n">
         <v>1.01</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-13 10:21:51</t>
+          <t>2026-07-13 12:31:07</t>
         </is>
       </c>
     </row>
@@ -2384,13 +2384,13 @@
         <v>1.7</v>
       </c>
       <c r="G8" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H8" t="n">
         <v>1.7</v>
       </c>
       <c r="I8" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J8" t="n">
         <v>1.03</v>
@@ -2405,16 +2405,16 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="O8" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="P8" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="R8" t="n">
         <v>1.12</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-13 10:21:51</t>
+          <t>2026-07-13 12:31:07</t>
         </is>
       </c>
     </row>
@@ -2638,16 +2638,16 @@
         <v>1.5</v>
       </c>
       <c r="G9" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H9" t="n">
         <v>2.2</v>
       </c>
       <c r="I9" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J9" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="K9" t="n">
         <v>950</v>
@@ -2674,13 +2674,13 @@
         <v>1.12</v>
       </c>
       <c r="S9" t="n">
-        <v>1.55</v>
+        <v>1.05</v>
       </c>
       <c r="T9" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U9" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V9" t="n">
         <v>1.02</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-13 10:21:51</t>
+          <t>2026-07-13 12:31:07</t>
         </is>
       </c>
     </row>
@@ -2892,16 +2892,16 @@
         <v>1.09</v>
       </c>
       <c r="G10" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="H10" t="n">
         <v>2.4</v>
       </c>
       <c r="I10" t="n">
-        <v>1000</v>
+        <v>870</v>
       </c>
       <c r="J10" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K10" t="n">
         <v>950</v>
@@ -2913,13 +2913,13 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O10" t="n">
         <v>1.01</v>
       </c>
       <c r="P10" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q10" t="n">
         <v>1.01</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-13 10:21:51</t>
+          <t>2026-07-13 12:31:07</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3146,7 @@
         <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H11" t="n">
         <v>1.7</v>
@@ -3155,7 +3155,7 @@
         <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="K11" t="n">
         <v>950</v>
@@ -3167,28 +3167,28 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O11" t="n">
         <v>1.01</v>
       </c>
       <c r="P11" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R11" t="n">
         <v>1.12</v>
       </c>
       <c r="S11" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="T11" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U11" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V11" t="n">
         <v>1.02</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-13 10:21:51</t>
+          <t>2026-07-13 12:31:07</t>
         </is>
       </c>
     </row>
@@ -3397,10 +3397,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="G12" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="H12" t="n">
         <v>3.9</v>
@@ -3409,10 +3409,10 @@
         <v>4.4</v>
       </c>
       <c r="J12" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K12" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="L12" t="n">
         <v>1.44</v>
@@ -3442,13 +3442,13 @@
         <v>1.86</v>
       </c>
       <c r="U12" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="V12" t="n">
         <v>1.31</v>
       </c>
       <c r="W12" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="X12" t="n">
         <v>14.5</v>
@@ -3478,13 +3478,13 @@
         <v>15.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI12" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ12" t="n">
         <v>32</v>
@@ -3511,13 +3511,13 @@
         <v>11.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AT12" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU12" t="n">
         <v>6.8</v>
@@ -3526,7 +3526,7 @@
         <v>14</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AX12" t="n">
         <v>11</v>
@@ -3538,25 +3538,25 @@
         <v>16.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BB12" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="BC12" t="n">
         <v>20</v>
       </c>
       <c r="BD12" t="n">
-        <v>32</v>
+        <v>4.3</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BF12" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BH12" t="n">
         <v>3.2</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-13 10:21:51</t>
+          <t>2026-07-13 12:31:07</t>
         </is>
       </c>
     </row>
@@ -3651,19 +3651,19 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.47</v>
+        <v>1.04</v>
       </c>
       <c r="G13" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="H13" t="n">
-        <v>1.47</v>
+        <v>1.04</v>
       </c>
       <c r="I13" t="n">
-        <v>1000</v>
+        <v>870</v>
       </c>
       <c r="J13" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="K13" t="n">
         <v>3.2</v>
@@ -3675,16 +3675,16 @@
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O13" t="n">
         <v>1.01</v>
       </c>
       <c r="P13" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R13" t="n">
         <v>1.12</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-13 10:21:51</t>
+          <t>2026-07-13 12:31:07</t>
         </is>
       </c>
     </row>
@@ -3908,13 +3908,13 @@
         <v>1.04</v>
       </c>
       <c r="G14" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="H14" t="n">
         <v>1.04</v>
       </c>
       <c r="I14" t="n">
-        <v>1000</v>
+        <v>870</v>
       </c>
       <c r="J14" t="n">
         <v>1.04</v>
@@ -3929,16 +3929,16 @@
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O14" t="n">
         <v>1.01</v>
       </c>
       <c r="P14" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R14" t="n">
         <v>1.12</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-13 10:21:51</t>
+          <t>2026-07-13 12:31:07</t>
         </is>
       </c>
     </row>
@@ -4162,16 +4162,16 @@
         <v>1.04</v>
       </c>
       <c r="G15" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H15" t="n">
         <v>1.04</v>
       </c>
       <c r="I15" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J15" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="K15" t="n">
         <v>950</v>
@@ -4189,16 +4189,16 @@
         <v>1.01</v>
       </c>
       <c r="P15" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R15" t="n">
         <v>1.12</v>
       </c>
       <c r="S15" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="T15" t="n">
         <v>1.01</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-13 10:21:51</t>
+          <t>2026-07-13 12:31:07</t>
         </is>
       </c>
     </row>
@@ -4416,16 +4416,16 @@
         <v>1.04</v>
       </c>
       <c r="G16" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H16" t="n">
         <v>1.04</v>
       </c>
       <c r="I16" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J16" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="K16" t="n">
         <v>950</v>
@@ -4437,22 +4437,22 @@
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O16" t="n">
         <v>1.01</v>
       </c>
       <c r="P16" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R16" t="n">
         <v>1.12</v>
       </c>
       <c r="S16" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="T16" t="n">
         <v>1.01</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-13 10:21:51</t>
+          <t>2026-07-13 12:31:07</t>
         </is>
       </c>
     </row>
@@ -4670,10 +4670,10 @@
         <v>2.2</v>
       </c>
       <c r="G17" t="n">
-        <v>110</v>
+        <v>600</v>
       </c>
       <c r="H17" t="n">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="I17" t="n">
         <v>4.8</v>
@@ -4682,7 +4682,7 @@
         <v>3</v>
       </c>
       <c r="K17" t="n">
-        <v>4.6</v>
+        <v>950</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
@@ -4691,22 +4691,22 @@
         <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="O17" t="n">
         <v>1.12</v>
       </c>
       <c r="P17" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="R17" t="n">
         <v>1.31</v>
       </c>
       <c r="S17" t="n">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="T17" t="n">
         <v>1.01</v>
@@ -4718,7 +4718,7 @@
         <v>1.26</v>
       </c>
       <c r="W17" t="n">
-        <v>1.02</v>
+        <v>1.16</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-13 10:21:51</t>
+          <t>2026-07-13 12:31:07</t>
         </is>
       </c>
     </row>
@@ -4921,19 +4921,19 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="G18" t="n">
-        <v>2.94</v>
+        <v>3.3</v>
       </c>
       <c r="H18" t="n">
-        <v>3.1</v>
+        <v>2.84</v>
       </c>
       <c r="I18" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="J18" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="K18" t="n">
         <v>2.96</v>
@@ -4957,52 +4957,52 @@
         <v>3.1</v>
       </c>
       <c r="R18" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="S18" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="T18" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="U18" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="V18" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="X18" t="n">
         <v>7.2</v>
       </c>
       <c r="Y18" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Z18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AA18" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AB18" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC18" t="n">
         <v>6.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AF18" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AH18" t="n">
         <v>32</v>
@@ -5011,22 +5011,22 @@
         <v>120</v>
       </c>
       <c r="AJ18" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AK18" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AL18" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AM18" t="n">
         <v>260</v>
       </c>
       <c r="AN18" t="n">
+        <v>85</v>
+      </c>
+      <c r="AO18" t="n">
         <v>70</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>85</v>
       </c>
       <c r="AP18" t="n">
         <v>6.2</v>
@@ -5035,13 +5035,13 @@
         <v>7</v>
       </c>
       <c r="AR18" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AS18" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="AT18" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AU18" t="n">
         <v>6.2</v>
@@ -5050,22 +5050,22 @@
         <v>13</v>
       </c>
       <c r="AW18" t="n">
-        <v>11.5</v>
+        <v>42</v>
       </c>
       <c r="AX18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY18" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AZ18" t="n">
         <v>22</v>
       </c>
       <c r="BA18" t="n">
-        <v>70</v>
+        <v>12</v>
       </c>
       <c r="BB18" t="n">
-        <v>44</v>
+        <v>11.5</v>
       </c>
       <c r="BC18" t="n">
         <v>42</v>
@@ -5074,19 +5074,19 @@
         <v>12.5</v>
       </c>
       <c r="BE18" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BF18" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BG18" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BH18" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="BJ18" t="n">
         <v>12.5</v>
@@ -5101,40 +5101,40 @@
         <v>11</v>
       </c>
       <c r="BN18" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BO18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BU18" t="n">
         <v>4.3</v>
       </c>
-      <c r="BP18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ18" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BR18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS18" t="n">
+      <c r="BV18" t="n">
+        <v>32</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY18" t="n">
         <v>9.6</v>
-      </c>
-      <c r="BT18" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BU18" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BV18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW18" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BX18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY18" t="n">
-        <v>9.800000000000001</v>
       </c>
       <c r="BZ18" t="n">
         <v>1000</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-13 10:21:51</t>
+          <t>2026-07-13 12:31:07</t>
         </is>
       </c>
     </row>
@@ -5199,13 +5199,13 @@
         <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>1.31</v>
+        <v>1.59</v>
       </c>
       <c r="O19" t="n">
         <v>1.14</v>
       </c>
       <c r="P19" t="n">
-        <v>1.31</v>
+        <v>1.59</v>
       </c>
       <c r="Q19" t="n">
         <v>1.14</v>
@@ -5214,7 +5214,7 @@
         <v>1.28</v>
       </c>
       <c r="S19" t="n">
-        <v>1.89</v>
+        <v>1.14</v>
       </c>
       <c r="T19" t="n">
         <v>1.01</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-13 10:21:51</t>
+          <t>2026-07-13 12:31:07</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-14.xlsx
@@ -866,7 +866,7 @@
         <v>6.6</v>
       </c>
       <c r="I2" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J2" t="n">
         <v>5.2</v>
@@ -887,10 +887,10 @@
         <v>1.13</v>
       </c>
       <c r="P2" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="R2" t="n">
         <v>1.9</v>
@@ -965,13 +965,13 @@
         <v>60</v>
       </c>
       <c r="AP2" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AR2" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AS2" t="n">
         <v>7.2</v>
@@ -998,7 +998,7 @@
         <v>16</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BB2" t="n">
         <v>14</v>
@@ -1007,10 +1007,10 @@
         <v>11.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BE2" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BF2" t="n">
         <v>4.1</v>
@@ -1022,13 +1022,13 @@
         <v>5.3</v>
       </c>
       <c r="BI2" t="n">
-        <v>4.6</v>
+        <v>3.85</v>
       </c>
       <c r="BJ2" t="n">
         <v>9.6</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
@@ -1046,13 +1046,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BR2" t="n">
         <v>18</v>
       </c>
       <c r="BS2" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BT2" t="n">
         <v>11</v>
@@ -1064,7 +1064,7 @@
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
@@ -1076,11 +1076,11 @@
         <v>9.800000000000001</v>
       </c>
       <c r="CA2" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-13 12:31:07</t>
+          <t>2026-07-13 14:40:34</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="G3" t="n">
         <v>1.93</v>
@@ -1120,13 +1120,13 @@
         <v>3.7</v>
       </c>
       <c r="I3" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J3" t="n">
         <v>4.3</v>
       </c>
       <c r="K3" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L3" t="n">
         <v>1.18</v>
@@ -1171,7 +1171,7 @@
         <v>36</v>
       </c>
       <c r="Z3" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AA3" t="n">
         <v>90</v>
@@ -1198,7 +1198,7 @@
         <v>18.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AJ3" t="n">
         <v>28</v>
@@ -1219,7 +1219,7 @@
         <v>25</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AQ3" t="n">
         <v>20</v>
@@ -1234,13 +1234,13 @@
         <v>13.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV3" t="n">
         <v>13</v>
       </c>
       <c r="AW3" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AX3" t="n">
         <v>13</v>
@@ -1252,25 +1252,25 @@
         <v>11</v>
       </c>
       <c r="BA3" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BB3" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BC3" t="n">
         <v>12</v>
       </c>
       <c r="BD3" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="BE3" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BF3" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BG3" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BH3" t="n">
         <v>5.7</v>
@@ -1294,7 +1294,7 @@
         <v>5.7</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BP3" t="n">
         <v>12</v>
@@ -1312,7 +1312,7 @@
         <v>8.6</v>
       </c>
       <c r="BU3" t="n">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="BV3" t="n">
         <v>27</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-13 12:31:07</t>
+          <t>2026-07-13 14:40:34</t>
         </is>
       </c>
     </row>
@@ -1368,19 +1368,19 @@
         <v>1.5</v>
       </c>
       <c r="G4" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="H4" t="n">
         <v>2.2</v>
       </c>
       <c r="I4" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="J4" t="n">
         <v>1.03</v>
       </c>
       <c r="K4" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
@@ -1395,7 +1395,7 @@
         <v>1.01</v>
       </c>
       <c r="P4" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q4" t="n">
         <v>1.01</v>
@@ -1404,7 +1404,7 @@
         <v>1.12</v>
       </c>
       <c r="S4" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="T4" t="n">
         <v>1.01</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-13 12:31:07</t>
+          <t>2026-07-13 14:40:34</t>
         </is>
       </c>
     </row>
@@ -1622,19 +1622,19 @@
         <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="H5" t="n">
         <v>1.65</v>
       </c>
       <c r="I5" t="n">
-        <v>870</v>
+        <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="K5" t="n">
-        <v>950</v>
+        <v>3.35</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1643,16 +1643,16 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="O5" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="P5" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.3</v>
+        <v>1.51</v>
       </c>
       <c r="R5" t="n">
         <v>1.12</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-13 12:31:07</t>
+          <t>2026-07-13 14:40:34</t>
         </is>
       </c>
     </row>
@@ -1876,19 +1876,19 @@
         <v>2.1</v>
       </c>
       <c r="G6" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="H6" t="n">
         <v>1.5</v>
       </c>
       <c r="I6" t="n">
-        <v>870</v>
+        <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="K6" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
@@ -1897,22 +1897,22 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="O6" t="n">
         <v>1.01</v>
       </c>
       <c r="P6" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="R6" t="n">
         <v>1.12</v>
       </c>
       <c r="S6" t="n">
-        <v>4.2</v>
+        <v>1.51</v>
       </c>
       <c r="T6" t="n">
         <v>1.01</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-13 12:31:07</t>
+          <t>2026-07-13 14:40:34</t>
         </is>
       </c>
     </row>
@@ -2136,10 +2136,10 @@
         <v>3.35</v>
       </c>
       <c r="I7" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="J7" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="K7" t="n">
         <v>4.8</v>
@@ -2154,7 +2154,7 @@
         <v>1.1</v>
       </c>
       <c r="O7" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="P7" t="n">
         <v>2.86</v>
@@ -2169,13 +2169,13 @@
         <v>2.14</v>
       </c>
       <c r="T7" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="U7" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="V7" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W7" t="n">
         <v>1.91</v>
@@ -2184,7 +2184,7 @@
         <v>40</v>
       </c>
       <c r="Y7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Z7" t="n">
         <v>34</v>
@@ -2196,16 +2196,16 @@
         <v>17.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AE7" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AF7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG7" t="n">
         <v>12</v>
@@ -2220,19 +2220,19 @@
         <v>26</v>
       </c>
       <c r="AK7" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AL7" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AM7" t="n">
         <v>60</v>
       </c>
       <c r="AN7" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AO7" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AP7" t="n">
         <v>1.01</v>
@@ -2250,7 +2250,7 @@
         <v>1.01</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AV7" t="n">
         <v>1.01</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-13 12:31:07</t>
+          <t>2026-07-13 14:40:34</t>
         </is>
       </c>
     </row>
@@ -2384,19 +2384,19 @@
         <v>1.7</v>
       </c>
       <c r="G8" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="H8" t="n">
         <v>1.7</v>
       </c>
       <c r="I8" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K8" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
@@ -2420,7 +2420,7 @@
         <v>1.12</v>
       </c>
       <c r="S8" t="n">
-        <v>1.55</v>
+        <v>1.01</v>
       </c>
       <c r="T8" t="n">
         <v>1.01</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-13 12:31:07</t>
+          <t>2026-07-13 14:40:34</t>
         </is>
       </c>
     </row>
@@ -2638,19 +2638,19 @@
         <v>1.5</v>
       </c>
       <c r="G9" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="H9" t="n">
         <v>2.2</v>
       </c>
       <c r="I9" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="K9" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
@@ -2659,13 +2659,13 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="O9" t="n">
         <v>1.01</v>
       </c>
       <c r="P9" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q9" t="n">
         <v>1.53</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-13 12:31:07</t>
+          <t>2026-07-13 14:40:34</t>
         </is>
       </c>
     </row>
@@ -2892,19 +2892,19 @@
         <v>1.09</v>
       </c>
       <c r="G10" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="H10" t="n">
         <v>2.4</v>
       </c>
       <c r="I10" t="n">
-        <v>870</v>
+        <v>1000</v>
       </c>
       <c r="J10" t="n">
         <v>1.04</v>
       </c>
       <c r="K10" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2922,7 +2922,7 @@
         <v>1.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R10" t="n">
         <v>1.12</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-13 12:31:07</t>
+          <t>2026-07-13 14:40:34</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3146,7 @@
         <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="H11" t="n">
         <v>1.7</v>
@@ -3155,10 +3155,10 @@
         <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="K11" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
@@ -3182,7 +3182,7 @@
         <v>1.12</v>
       </c>
       <c r="S11" t="n">
-        <v>1.65</v>
+        <v>1.05</v>
       </c>
       <c r="T11" t="n">
         <v>1.11</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-13 12:31:07</t>
+          <t>2026-07-13 14:40:34</t>
         </is>
       </c>
     </row>
@@ -3409,7 +3409,7 @@
         <v>4.4</v>
       </c>
       <c r="J12" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K12" t="n">
         <v>3.7</v>
@@ -3466,10 +3466,10 @@
         <v>10.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE12" t="n">
         <v>60</v>
@@ -3484,7 +3484,7 @@
         <v>24</v>
       </c>
       <c r="AI12" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AJ12" t="n">
         <v>32</v>
@@ -3499,19 +3499,19 @@
         <v>150</v>
       </c>
       <c r="AN12" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AO12" t="n">
         <v>85</v>
       </c>
       <c r="AP12" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ12" t="n">
         <v>11.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="AS12" t="n">
         <v>4.4</v>
@@ -3523,10 +3523,10 @@
         <v>6.8</v>
       </c>
       <c r="AV12" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.3</v>
+        <v>40</v>
       </c>
       <c r="AX12" t="n">
         <v>11</v>
@@ -3541,22 +3541,22 @@
         <v>4.3</v>
       </c>
       <c r="BB12" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="BC12" t="n">
         <v>20</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.3</v>
+        <v>30</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BF12" t="n">
         <v>16</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BH12" t="n">
         <v>3.2</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-13 12:31:07</t>
+          <t>2026-07-13 14:40:34</t>
         </is>
       </c>
     </row>
@@ -3651,19 +3651,19 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.04</v>
+        <v>1.57</v>
       </c>
       <c r="G13" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>1.04</v>
+        <v>1.57</v>
       </c>
       <c r="I13" t="n">
-        <v>870</v>
+        <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="K13" t="n">
         <v>3.2</v>
@@ -3675,13 +3675,13 @@
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="O13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P13" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Q13" t="n">
         <v>1.02</v>
@@ -3690,7 +3690,7 @@
         <v>1.12</v>
       </c>
       <c r="S13" t="n">
-        <v>1.52</v>
+        <v>1.37</v>
       </c>
       <c r="T13" t="n">
         <v>1.01</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-13 12:31:07</t>
+          <t>2026-07-13 14:40:34</t>
         </is>
       </c>
     </row>
@@ -3905,22 +3905,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="G14" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="H14" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="I14" t="n">
-        <v>870</v>
+        <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="K14" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-13 12:31:07</t>
+          <t>2026-07-13 14:40:34</t>
         </is>
       </c>
     </row>
@@ -4162,19 +4162,19 @@
         <v>1.04</v>
       </c>
       <c r="G15" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="H15" t="n">
         <v>1.04</v>
       </c>
       <c r="I15" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="J15" t="n">
         <v>1.03</v>
       </c>
       <c r="K15" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L15" t="n">
         <v>1.01</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-13 12:31:07</t>
+          <t>2026-07-13 14:40:34</t>
         </is>
       </c>
     </row>
@@ -4416,19 +4416,19 @@
         <v>1.04</v>
       </c>
       <c r="G16" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="H16" t="n">
         <v>1.04</v>
       </c>
       <c r="I16" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="J16" t="n">
         <v>1.03</v>
       </c>
       <c r="K16" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-13 12:31:07</t>
+          <t>2026-07-13 14:40:34</t>
         </is>
       </c>
     </row>
@@ -4670,10 +4670,10 @@
         <v>2.2</v>
       </c>
       <c r="G17" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="H17" t="n">
-        <v>1.18</v>
+        <v>1.6</v>
       </c>
       <c r="I17" t="n">
         <v>4.8</v>
@@ -4682,7 +4682,7 @@
         <v>3</v>
       </c>
       <c r="K17" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
@@ -4706,7 +4706,7 @@
         <v>1.31</v>
       </c>
       <c r="S17" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="T17" t="n">
         <v>1.01</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-13 12:31:07</t>
+          <t>2026-07-13 14:40:34</t>
         </is>
       </c>
     </row>
@@ -4924,19 +4924,19 @@
         <v>3.15</v>
       </c>
       <c r="G18" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H18" t="n">
         <v>2.84</v>
       </c>
       <c r="I18" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K18" t="n">
         <v>3</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="K18" t="n">
-        <v>2.96</v>
       </c>
       <c r="L18" t="n">
         <v>1.66</v>
@@ -4972,7 +4972,7 @@
         <v>1.5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X18" t="n">
         <v>7.2</v>
@@ -4987,10 +4987,10 @@
         <v>55</v>
       </c>
       <c r="AB18" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC18" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="AD18" t="n">
         <v>14.5</v>
@@ -5023,7 +5023,7 @@
         <v>260</v>
       </c>
       <c r="AN18" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AO18" t="n">
         <v>70</v>
@@ -5038,7 +5038,7 @@
         <v>15</v>
       </c>
       <c r="AS18" t="n">
-        <v>38</v>
+        <v>8.4</v>
       </c>
       <c r="AT18" t="n">
         <v>7.6</v>
@@ -5062,25 +5062,25 @@
         <v>22</v>
       </c>
       <c r="BA18" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BB18" t="n">
-        <v>11.5</v>
+        <v>8.6</v>
       </c>
       <c r="BC18" t="n">
         <v>42</v>
       </c>
       <c r="BD18" t="n">
-        <v>12.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE18" t="n">
-        <v>13</v>
+        <v>9.6</v>
       </c>
       <c r="BF18" t="n">
-        <v>12</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG18" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BH18" t="n">
         <v>2.56</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-13 12:31:07</t>
+          <t>2026-07-13 14:40:34</t>
         </is>
       </c>
     </row>
@@ -5199,13 +5199,13 @@
         <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>1.59</v>
+        <v>1.33</v>
       </c>
       <c r="O19" t="n">
         <v>1.14</v>
       </c>
       <c r="P19" t="n">
-        <v>1.59</v>
+        <v>1.33</v>
       </c>
       <c r="Q19" t="n">
         <v>1.14</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-13 12:31:07</t>
+          <t>2026-07-13 14:40:34</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-14.xlsx
@@ -887,10 +887,10 @@
         <v>1.13</v>
       </c>
       <c r="P2" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="R2" t="n">
         <v>1.9</v>
@@ -1001,7 +1001,7 @@
         <v>7</v>
       </c>
       <c r="BB2" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BC2" t="n">
         <v>11.5</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-13 14:40:34</t>
+          <t>2026-07-13 16:49:34</t>
         </is>
       </c>
     </row>
@@ -1114,13 +1114,13 @@
         <v>1.78</v>
       </c>
       <c r="G3" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="H3" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I3" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="J3" t="n">
         <v>4.3</v>
@@ -1135,34 +1135,34 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="O3" t="n">
         <v>1.12</v>
       </c>
       <c r="P3" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="Q3" t="n">
         <v>1.37</v>
       </c>
       <c r="R3" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="S3" t="n">
         <v>1.91</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.93</v>
       </c>
       <c r="T3" t="n">
         <v>1.43</v>
       </c>
       <c r="U3" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="V3" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W3" t="n">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="X3" t="n">
         <v>48</v>
@@ -1213,22 +1213,22 @@
         <v>55</v>
       </c>
       <c r="AN3" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="AO3" t="n">
         <v>25</v>
       </c>
       <c r="AP3" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AQ3" t="n">
         <v>20</v>
       </c>
       <c r="AR3" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AT3" t="n">
         <v>13.5</v>
@@ -1240,7 +1240,7 @@
         <v>13</v>
       </c>
       <c r="AW3" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AX3" t="n">
         <v>13</v>
@@ -1252,7 +1252,7 @@
         <v>11</v>
       </c>
       <c r="BA3" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="BB3" t="n">
         <v>19.5</v>
@@ -1276,7 +1276,7 @@
         <v>5.7</v>
       </c>
       <c r="BI3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BJ3" t="n">
         <v>8.800000000000001</v>
@@ -1288,7 +1288,7 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN3" t="n">
         <v>5.7</v>
@@ -1303,13 +1303,13 @@
         <v>8.4</v>
       </c>
       <c r="BR3" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BS3" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BT3" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU3" t="n">
         <v>6.2</v>
@@ -1318,7 +1318,7 @@
         <v>27</v>
       </c>
       <c r="BW3" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BX3" t="n">
         <v>28</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-13 14:40:34</t>
+          <t>2026-07-13 16:49:34</t>
         </is>
       </c>
     </row>
@@ -1365,46 +1365,46 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.5</v>
+        <v>1.97</v>
       </c>
       <c r="G4" t="n">
-        <v>1000</v>
+        <v>2.16</v>
       </c>
       <c r="H4" t="n">
-        <v>2.2</v>
+        <v>4.1</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="J4" t="n">
-        <v>1.03</v>
+        <v>2.94</v>
       </c>
       <c r="K4" t="n">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N4" t="n">
-        <v>1.25</v>
+        <v>2.5</v>
       </c>
       <c r="O4" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="P4" t="n">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.01</v>
+        <v>2.82</v>
       </c>
       <c r="R4" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="S4" t="n">
-        <v>1.58</v>
+        <v>3.1</v>
       </c>
       <c r="T4" t="n">
         <v>1.01</v>
@@ -1413,13 +1413,13 @@
         <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="Y4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-13 14:40:34</t>
+          <t>2026-07-13 16:49:34</t>
         </is>
       </c>
     </row>
@@ -1619,160 +1619,160 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="H5" t="n">
-        <v>1.65</v>
+        <v>2.14</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>2.38</v>
       </c>
       <c r="J5" t="n">
-        <v>1.05</v>
+        <v>2.92</v>
       </c>
       <c r="K5" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="N5" t="n">
-        <v>1.32</v>
+        <v>2.46</v>
       </c>
       <c r="O5" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="P5" t="n">
-        <v>1.32</v>
+        <v>1.46</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.51</v>
+        <v>2.88</v>
       </c>
       <c r="R5" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="S5" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="V5" t="n">
-        <v>1.02</v>
+        <v>1.83</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF5" t="n">
         <v>1.01</v>
@@ -1781,68 +1781,68 @@
         <v>1.01</v>
       </c>
       <c r="BH5" t="n">
-        <v>1000</v>
+        <v>2.68</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="BN5" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BP5" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="BT5" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BV5" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-13 14:40:34</t>
+          <t>2026-07-13 16:49:34</t>
         </is>
       </c>
     </row>
@@ -1873,175 +1873,175 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.1</v>
+        <v>3.6</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="H6" t="n">
-        <v>1.5</v>
+        <v>2.24</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>2.48</v>
       </c>
       <c r="J6" t="n">
-        <v>1.08</v>
+        <v>2.86</v>
       </c>
       <c r="K6" t="n">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N6" t="n">
-        <v>1.25</v>
+        <v>2.72</v>
       </c>
       <c r="O6" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="P6" t="n">
-        <v>1.25</v>
+        <v>1.52</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="R6" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="S6" t="n">
-        <v>1.51</v>
+        <v>4.1</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="V6" t="n">
-        <v>1.02</v>
+        <v>1.68</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>1.3</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BH6" t="n">
-        <v>1000</v>
+        <v>2.88</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK6" t="n">
         <v>1.01</v>
@@ -2053,50 +2053,50 @@
         <v>1.01</v>
       </c>
       <c r="BN6" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BO6" t="n">
         <v>1.01</v>
       </c>
       <c r="BP6" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BQ6" t="n">
         <v>1.01</v>
       </c>
       <c r="BR6" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BS6" t="n">
         <v>1.01</v>
       </c>
       <c r="BT6" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BU6" t="n">
         <v>1.01</v>
       </c>
       <c r="BV6" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BW6" t="n">
         <v>1.01</v>
       </c>
       <c r="BX6" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BY6" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="CA6" t="n">
         <v>1.01</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-13 14:40:34</t>
+          <t>2026-07-13 16:49:34</t>
         </is>
       </c>
     </row>
@@ -2133,13 +2133,13 @@
         <v>2.1</v>
       </c>
       <c r="H7" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I7" t="n">
         <v>3.85</v>
       </c>
       <c r="J7" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="K7" t="n">
         <v>4.8</v>
@@ -2151,7 +2151,7 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.1</v>
+        <v>2.84</v>
       </c>
       <c r="O7" t="n">
         <v>1.12</v>
@@ -2172,7 +2172,7 @@
         <v>1.46</v>
       </c>
       <c r="U7" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="V7" t="n">
         <v>1.35</v>
@@ -2184,43 +2184,43 @@
         <v>40</v>
       </c>
       <c r="Y7" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="Z7" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AA7" t="n">
         <v>75</v>
       </c>
       <c r="AB7" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AC7" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG7" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AH7" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AI7" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AJ7" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AK7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL7" t="n">
         <v>29</v>
@@ -2232,125 +2232,125 @@
         <v>9.6</v>
       </c>
       <c r="AO7" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS7" t="n">
         <v>1.01</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AU7" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BE7" t="n">
         <v>1.01</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BH7" t="n">
         <v>5.1</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BJ7" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BL7" t="n">
         <v>65</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN7" t="n">
         <v>5.7</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BP7" t="n">
         <v>13</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BR7" t="n">
         <v>21</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BT7" t="n">
         <v>7.8</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BV7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BX7" t="n">
         <v>28</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BZ7" t="n">
         <v>13</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-13 14:40:34</t>
+          <t>2026-07-13 16:49:34</t>
         </is>
       </c>
     </row>
@@ -2381,58 +2381,58 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.7</v>
+        <v>2.56</v>
       </c>
       <c r="G8" t="n">
-        <v>1000</v>
+        <v>2.9</v>
       </c>
       <c r="H8" t="n">
-        <v>1.7</v>
+        <v>3.25</v>
       </c>
       <c r="I8" t="n">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="J8" t="n">
-        <v>1.04</v>
+        <v>2.78</v>
       </c>
       <c r="K8" t="n">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="M8" t="n">
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.28</v>
+        <v>2.24</v>
       </c>
       <c r="O8" t="n">
-        <v>1.3</v>
+        <v>1.67</v>
       </c>
       <c r="P8" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.46</v>
+        <v>3.25</v>
       </c>
       <c r="R8" t="n">
         <v>1.12</v>
       </c>
       <c r="S8" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="T8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="U8" t="n">
         <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>1.02</v>
+        <v>1.37</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>1.6</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-13 14:40:34</t>
+          <t>2026-07-13 16:49:34</t>
         </is>
       </c>
     </row>
@@ -2635,175 +2635,175 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.5</v>
+        <v>2.08</v>
       </c>
       <c r="G9" t="n">
-        <v>1000</v>
+        <v>2.28</v>
       </c>
       <c r="H9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="T9" t="n">
         <v>2.2</v>
       </c>
-      <c r="I9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.11</v>
-      </c>
       <c r="U9" t="n">
-        <v>1.11</v>
+        <v>1.67</v>
       </c>
       <c r="V9" t="n">
-        <v>1.02</v>
+        <v>1.25</v>
       </c>
       <c r="W9" t="n">
-        <v>1.02</v>
+        <v>1.78</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="Y9" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB9" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AC9" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE9" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF9" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AG9" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI9" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AK9" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL9" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM9" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BH9" t="n">
-        <v>1000</v>
+        <v>2.68</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK9" t="n">
         <v>1.01</v>
@@ -2815,31 +2815,31 @@
         <v>1.01</v>
       </c>
       <c r="BN9" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BP9" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BQ9" t="n">
         <v>1.01</v>
       </c>
       <c r="BR9" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS9" t="n">
         <v>1.01</v>
       </c>
       <c r="BT9" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BV9" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW9" t="n">
         <v>1.01</v>
@@ -2851,14 +2851,14 @@
         <v>1.01</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA9" t="n">
         <v>1.01</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-13 14:40:34</t>
+          <t>2026-07-13 16:49:34</t>
         </is>
       </c>
     </row>
@@ -2889,230 +2889,230 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.09</v>
+        <v>1.89</v>
       </c>
       <c r="G10" t="n">
-        <v>1000</v>
+        <v>2.08</v>
       </c>
       <c r="H10" t="n">
-        <v>2.4</v>
+        <v>4.9</v>
       </c>
       <c r="I10" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="J10" t="n">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="M10" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N10" t="n">
-        <v>1.25</v>
+        <v>2.48</v>
       </c>
       <c r="O10" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="P10" t="n">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.02</v>
+        <v>2.86</v>
       </c>
       <c r="R10" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="S10" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="T10" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="U10" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="V10" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="X10" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AB10" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD10" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AF10" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH10" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.03</v>
+        <v>3.05</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.03</v>
+        <v>2.76</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.03</v>
+        <v>3</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BH10" t="n">
-        <v>1000</v>
+        <v>2.68</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="BN10" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BP10" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="BR10" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="BT10" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-13 14:40:34</t>
+          <t>2026-07-13 16:49:34</t>
         </is>
       </c>
     </row>
@@ -3143,175 +3143,175 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>3.05</v>
       </c>
       <c r="G11" t="n">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="H11" t="n">
-        <v>1.7</v>
+        <v>2.74</v>
       </c>
       <c r="I11" t="n">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="J11" t="n">
-        <v>1.12</v>
+        <v>2.68</v>
       </c>
       <c r="K11" t="n">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="M11" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="N11" t="n">
-        <v>1.25</v>
+        <v>2.4</v>
       </c>
       <c r="O11" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="P11" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.02</v>
+        <v>3.05</v>
       </c>
       <c r="R11" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="S11" t="n">
-        <v>1.05</v>
+        <v>2.6</v>
       </c>
       <c r="T11" t="n">
-        <v>1.11</v>
+        <v>2.14</v>
       </c>
       <c r="U11" t="n">
-        <v>1.11</v>
+        <v>1.66</v>
       </c>
       <c r="V11" t="n">
-        <v>1.02</v>
+        <v>1.47</v>
       </c>
       <c r="W11" t="n">
-        <v>1.02</v>
+        <v>1.39</v>
       </c>
       <c r="X11" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="Y11" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z11" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB11" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF11" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AG11" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.03</v>
+        <v>2.92</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.03</v>
+        <v>2.94</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.03</v>
+        <v>3.05</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.03</v>
+        <v>2.86</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH11" t="n">
-        <v>1000</v>
+        <v>2.66</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="BJ11" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK11" t="n">
         <v>1.01</v>
@@ -3323,37 +3323,37 @@
         <v>1.01</v>
       </c>
       <c r="BN11" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO11" t="n">
         <v>1.01</v>
       </c>
       <c r="BP11" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BQ11" t="n">
         <v>1.01</v>
       </c>
       <c r="BR11" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BS11" t="n">
         <v>1.01</v>
       </c>
       <c r="BT11" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BU11" t="n">
         <v>1.01</v>
       </c>
       <c r="BV11" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BW11" t="n">
         <v>1.01</v>
       </c>
       <c r="BX11" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY11" t="n">
         <v>1.01</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-13 14:40:34</t>
+          <t>2026-07-13 16:49:34</t>
         </is>
       </c>
     </row>
@@ -3397,10 +3397,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="G12" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="H12" t="n">
         <v>3.9</v>
@@ -3412,7 +3412,7 @@
         <v>3.3</v>
       </c>
       <c r="K12" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L12" t="n">
         <v>1.44</v>
@@ -3442,7 +3442,7 @@
         <v>1.86</v>
       </c>
       <c r="U12" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="V12" t="n">
         <v>1.31</v>
@@ -3454,7 +3454,7 @@
         <v>14.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z12" t="n">
         <v>32</v>
@@ -3499,7 +3499,7 @@
         <v>150</v>
       </c>
       <c r="AN12" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AO12" t="n">
         <v>85</v>
@@ -3514,7 +3514,7 @@
         <v>22</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AT12" t="n">
         <v>7.4</v>
@@ -3538,7 +3538,7 @@
         <v>16.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BB12" t="n">
         <v>19</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-13 14:40:34</t>
+          <t>2026-07-13 16:49:34</t>
         </is>
       </c>
     </row>
@@ -3651,19 +3651,19 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="G13" t="n">
         <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="I13" t="n">
         <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="K13" t="n">
         <v>3.2</v>
@@ -3675,13 +3675,13 @@
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="O13" t="n">
         <v>1.02</v>
       </c>
       <c r="P13" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Q13" t="n">
         <v>1.02</v>
@@ -3690,7 +3690,7 @@
         <v>1.12</v>
       </c>
       <c r="S13" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T13" t="n">
         <v>1.01</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-13 14:40:34</t>
+          <t>2026-07-13 16:49:34</t>
         </is>
       </c>
     </row>
@@ -3905,19 +3905,19 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="G14" t="n">
         <v>1000</v>
       </c>
       <c r="H14" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="I14" t="n">
         <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="K14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-13 14:40:34</t>
+          <t>2026-07-13 16:49:34</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-13 14:40:34</t>
+          <t>2026-07-13 16:49:34</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-13 14:40:34</t>
+          <t>2026-07-13 16:49:34</t>
         </is>
       </c>
     </row>
@@ -4673,7 +4673,7 @@
         <v>1000</v>
       </c>
       <c r="H17" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="I17" t="n">
         <v>4.8</v>
@@ -4715,10 +4715,10 @@
         <v>1.01</v>
       </c>
       <c r="V17" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="W17" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-13 14:40:34</t>
+          <t>2026-07-13 16:49:34</t>
         </is>
       </c>
     </row>
@@ -4921,22 +4921,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="G18" t="n">
         <v>3.25</v>
       </c>
       <c r="H18" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="I18" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="J18" t="n">
         <v>2.88</v>
       </c>
       <c r="K18" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="L18" t="n">
         <v>1.66</v>
@@ -4966,7 +4966,7 @@
         <v>2.22</v>
       </c>
       <c r="U18" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="V18" t="n">
         <v>1.5</v>
@@ -4987,7 +4987,7 @@
         <v>55</v>
       </c>
       <c r="AB18" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC18" t="n">
         <v>8.4</v>
@@ -4996,7 +4996,7 @@
         <v>14.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AF18" t="n">
         <v>19.5</v>
@@ -5038,7 +5038,7 @@
         <v>15</v>
       </c>
       <c r="AS18" t="n">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="AT18" t="n">
         <v>7.6</v>
@@ -5080,7 +5080,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BG18" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BH18" t="n">
         <v>2.56</v>
@@ -5092,13 +5092,13 @@
         <v>12.5</v>
       </c>
       <c r="BK18" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BN18" t="n">
         <v>6.2</v>
@@ -5110,41 +5110,41 @@
         <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BT18" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BU18" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BV18" t="n">
         <v>32</v>
       </c>
       <c r="BW18" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA18" t="n">
         <v>9.6</v>
       </c>
-      <c r="BZ18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA18" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-13 14:40:34</t>
+          <t>2026-07-13 16:49:34</t>
         </is>
       </c>
     </row>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-13 14:40:34</t>
+          <t>2026-07-13 16:49:34</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-14.xlsx
@@ -860,7 +860,7 @@
         <v>1.47</v>
       </c>
       <c r="G2" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="H2" t="n">
         <v>6.6</v>
@@ -869,10 +869,10 @@
         <v>7.4</v>
       </c>
       <c r="J2" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="K2" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="L2" t="n">
         <v>1.23</v>
@@ -887,28 +887,28 @@
         <v>1.13</v>
       </c>
       <c r="P2" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="R2" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="S2" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="T2" t="n">
         <v>1.56</v>
       </c>
       <c r="U2" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="V2" t="n">
         <v>1.16</v>
       </c>
       <c r="W2" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="X2" t="n">
         <v>42</v>
@@ -926,7 +926,7 @@
         <v>17.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AD2" t="n">
         <v>28</v>
@@ -935,7 +935,7 @@
         <v>75</v>
       </c>
       <c r="AF2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AG2" t="n">
         <v>11</v>
@@ -965,28 +965,28 @@
         <v>60</v>
       </c>
       <c r="AP2" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AQ2" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AR2" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="AT2" t="n">
         <v>13.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AV2" t="n">
         <v>18.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AX2" t="n">
         <v>11.5</v>
@@ -995,28 +995,28 @@
         <v>9.6</v>
       </c>
       <c r="AZ2" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB2" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BC2" t="n">
         <v>11.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF2" t="n">
         <v>4.1</v>
       </c>
       <c r="BG2" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BH2" t="n">
         <v>5.3</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-13 16:49:34</t>
+          <t>2026-07-13 18:58:03</t>
         </is>
       </c>
     </row>
@@ -1114,25 +1114,25 @@
         <v>1.78</v>
       </c>
       <c r="G3" t="n">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="H3" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="I3" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K3" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L3" t="n">
         <v>1.18</v>
       </c>
       <c r="M3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N3" t="n">
         <v>7.6</v>
@@ -1147,7 +1147,7 @@
         <v>1.37</v>
       </c>
       <c r="R3" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="S3" t="n">
         <v>1.91</v>
@@ -1156,13 +1156,13 @@
         <v>1.43</v>
       </c>
       <c r="U3" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="V3" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W3" t="n">
-        <v>2.24</v>
+        <v>2.06</v>
       </c>
       <c r="X3" t="n">
         <v>48</v>
@@ -1174,7 +1174,7 @@
         <v>44</v>
       </c>
       <c r="AA3" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AB3" t="n">
         <v>23</v>
@@ -1213,34 +1213,34 @@
         <v>55</v>
       </c>
       <c r="AN3" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AO3" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AQ3" t="n">
         <v>20</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AT3" t="n">
         <v>13.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AV3" t="n">
         <v>13</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AX3" t="n">
         <v>13</v>
@@ -1252,7 +1252,7 @@
         <v>11</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BB3" t="n">
         <v>19.5</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-13 16:49:34</t>
+          <t>2026-07-13 18:58:03</t>
         </is>
       </c>
     </row>
@@ -1365,166 +1365,166 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="G4" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="H4" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="I4" t="n">
-        <v>6.4</v>
+        <v>5.4</v>
       </c>
       <c r="J4" t="n">
         <v>2.94</v>
       </c>
       <c r="K4" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="L4" t="n">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N4" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="O4" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="P4" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.82</v>
+        <v>2.72</v>
       </c>
       <c r="R4" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="S4" t="n">
-        <v>3.1</v>
+        <v>5.8</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="V4" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W4" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="X4" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BH4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-13 16:49:34</t>
+          <t>2026-07-13 18:58:03</t>
         </is>
       </c>
     </row>
@@ -1619,61 +1619,61 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="G5" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="H5" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="I5" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="J5" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="K5" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L5" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="M5" t="n">
         <v>1.14</v>
       </c>
       <c r="N5" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="O5" t="n">
         <v>1.58</v>
       </c>
       <c r="P5" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.88</v>
+        <v>2.72</v>
       </c>
       <c r="R5" t="n">
         <v>1.16</v>
       </c>
       <c r="S5" t="n">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="T5" t="n">
         <v>2.2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="V5" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="W5" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="X5" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="Y5" t="n">
         <v>7</v>
@@ -1685,7 +1685,7 @@
         <v>42</v>
       </c>
       <c r="AB5" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC5" t="n">
         <v>7.6</v>
@@ -1694,91 +1694,91 @@
         <v>13</v>
       </c>
       <c r="AE5" t="n">
-        <v>46</v>
+        <v>500</v>
       </c>
       <c r="AF5" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="AG5" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AH5" t="n">
         <v>38</v>
       </c>
       <c r="AI5" t="n">
-        <v>85</v>
+        <v>460</v>
       </c>
       <c r="AJ5" t="n">
-        <v>140</v>
+        <v>500</v>
       </c>
       <c r="AK5" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AL5" t="n">
-        <v>130</v>
+        <v>540</v>
       </c>
       <c r="AM5" t="n">
-        <v>280</v>
+        <v>500</v>
       </c>
       <c r="AN5" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AO5" t="n">
         <v>44</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AQ5" t="n">
         <v>4.3</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AU5" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BH5" t="n">
         <v>2.68</v>
@@ -1790,13 +1790,13 @@
         <v>12.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="BN5" t="n">
         <v>7.6</v>
@@ -1808,7 +1808,7 @@
         <v>65</v>
       </c>
       <c r="BQ5" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
@@ -1817,22 +1817,22 @@
         <v>2.1</v>
       </c>
       <c r="BT5" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BV5" t="n">
         <v>21</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.97</v>
+        <v>7.2</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-13 16:49:34</t>
+          <t>2026-07-13 18:58:03</t>
         </is>
       </c>
     </row>
@@ -1876,28 +1876,28 @@
         <v>3.6</v>
       </c>
       <c r="G6" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="H6" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="I6" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="J6" t="n">
         <v>2.86</v>
       </c>
       <c r="K6" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L6" t="n">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="M6" t="n">
         <v>1.11</v>
       </c>
       <c r="N6" t="n">
-        <v>2.72</v>
+        <v>2.56</v>
       </c>
       <c r="O6" t="n">
         <v>1.49</v>
@@ -1906,22 +1906,22 @@
         <v>1.52</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="R6" t="n">
         <v>1.19</v>
       </c>
       <c r="S6" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="T6" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U6" t="n">
         <v>1.75</v>
       </c>
       <c r="V6" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="W6" t="n">
         <v>1.3</v>
@@ -1954,85 +1954,85 @@
         <v>28</v>
       </c>
       <c r="AG6" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AH6" t="n">
         <v>25</v>
       </c>
       <c r="AI6" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AJ6" t="n">
         <v>110</v>
       </c>
       <c r="AK6" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AL6" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AM6" t="n">
-        <v>220</v>
+        <v>500</v>
       </c>
       <c r="AN6" t="n">
         <v>110</v>
       </c>
       <c r="AO6" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AP6" t="n">
-        <v>4</v>
+        <v>7.4</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.75</v>
+        <v>6.2</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.7</v>
+        <v>11</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.9</v>
+        <v>22</v>
       </c>
       <c r="AT6" t="n">
-        <v>4.4</v>
+        <v>7.8</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.7</v>
+        <v>6</v>
       </c>
       <c r="AV6" t="n">
-        <v>4.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW6" t="n">
-        <v>5.8</v>
+        <v>20</v>
       </c>
       <c r="AX6" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AY6" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AZ6" t="n">
-        <v>5.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BB6" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BC6" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BD6" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BE6" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BF6" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BG6" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="BH6" t="n">
         <v>2.88</v>
@@ -2044,59 +2044,59 @@
         <v>12</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="BN6" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BP6" t="n">
         <v>40</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="BR6" t="n">
         <v>65</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="BT6" t="n">
         <v>5.2</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BV6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BX6" t="n">
         <v>46</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="BZ6" t="n">
         <v>50</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-13 16:49:34</t>
+          <t>2026-07-13 18:58:03</t>
         </is>
       </c>
     </row>
@@ -2127,13 +2127,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="G7" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="H7" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="I7" t="n">
         <v>3.85</v>
@@ -2148,25 +2148,25 @@
         <v>1.2</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N7" t="n">
-        <v>2.84</v>
+        <v>5.5</v>
       </c>
       <c r="O7" t="n">
         <v>1.12</v>
       </c>
       <c r="P7" t="n">
-        <v>2.86</v>
+        <v>2.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="R7" t="n">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="S7" t="n">
-        <v>2.14</v>
+        <v>1.94</v>
       </c>
       <c r="T7" t="n">
         <v>1.46</v>
@@ -2178,7 +2178,7 @@
         <v>1.35</v>
       </c>
       <c r="W7" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="X7" t="n">
         <v>40</v>
@@ -2235,16 +2235,16 @@
         <v>24</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AQ7" t="n">
         <v>17</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AT7" t="n">
         <v>12</v>
@@ -2256,19 +2256,19 @@
         <v>11.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AX7" t="n">
         <v>13</v>
       </c>
       <c r="AY7" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ7" t="n">
         <v>10.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="BB7" t="n">
         <v>18.5</v>
@@ -2280,7 +2280,7 @@
         <v>17.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BF7" t="n">
         <v>6</v>
@@ -2292,7 +2292,7 @@
         <v>5.1</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="BJ7" t="n">
         <v>8.800000000000001</v>
@@ -2319,7 +2319,7 @@
         <v>5.9</v>
       </c>
       <c r="BR7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BS7" t="n">
         <v>7</v>
@@ -2331,7 +2331,7 @@
         <v>5.7</v>
       </c>
       <c r="BV7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BW7" t="n">
         <v>7.4</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-13 16:49:34</t>
+          <t>2026-07-13 18:58:03</t>
         </is>
       </c>
     </row>
@@ -2381,16 +2381,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="G8" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="H8" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="I8" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="J8" t="n">
         <v>2.78</v>
@@ -2399,148 +2399,148 @@
         <v>3.05</v>
       </c>
       <c r="L8" t="n">
-        <v>1.69</v>
+        <v>1.56</v>
       </c>
       <c r="M8" t="n">
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="O8" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="P8" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="R8" t="n">
         <v>1.12</v>
       </c>
       <c r="S8" t="n">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="T8" t="n">
-        <v>1.04</v>
+        <v>1.83</v>
       </c>
       <c r="U8" t="n">
         <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W8" t="n">
         <v>1.6</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y8" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z8" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE8" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI8" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK8" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.03</v>
+        <v>1.55</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.03</v>
+        <v>1.59</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.03</v>
+        <v>1.53</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.03</v>
+        <v>1.59</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.03</v>
+        <v>1.55</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.03</v>
+        <v>1.54</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.03</v>
+        <v>1.57</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.03</v>
+        <v>1.59</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.03</v>
+        <v>1.59</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.03</v>
+        <v>1.59</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.03</v>
+        <v>1.59</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.03</v>
+        <v>1.6</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="BH8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-13 16:49:34</t>
+          <t>2026-07-13 18:58:03</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="G9" t="n">
         <v>2.28</v>
@@ -2650,25 +2650,25 @@
         <v>2.92</v>
       </c>
       <c r="K9" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L9" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="M9" t="n">
         <v>1.13</v>
       </c>
       <c r="N9" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="O9" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="P9" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
       <c r="R9" t="n">
         <v>1.17</v>
@@ -2677,7 +2677,7 @@
         <v>5.7</v>
       </c>
       <c r="T9" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="U9" t="n">
         <v>1.67</v>
@@ -2689,7 +2689,7 @@
         <v>1.78</v>
       </c>
       <c r="X9" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="Y9" t="n">
         <v>12</v>
@@ -2698,7 +2698,7 @@
         <v>34</v>
       </c>
       <c r="AA9" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AB9" t="n">
         <v>6.8</v>
@@ -2719,10 +2719,10 @@
         <v>12.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AI9" t="n">
-        <v>140</v>
+        <v>540</v>
       </c>
       <c r="AJ9" t="n">
         <v>30</v>
@@ -2731,70 +2731,70 @@
         <v>34</v>
       </c>
       <c r="AL9" t="n">
-        <v>80</v>
+        <v>450</v>
       </c>
       <c r="AM9" t="n">
-        <v>270</v>
+        <v>500</v>
       </c>
       <c r="AN9" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AO9" t="n">
-        <v>180</v>
+        <v>500</v>
       </c>
       <c r="AP9" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="AQ9" t="n">
-        <v>4.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AU9" t="n">
         <v>6.4</v>
       </c>
-      <c r="AS9" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>3.85</v>
-      </c>
       <c r="AV9" t="n">
-        <v>5.7</v>
+        <v>17</v>
       </c>
       <c r="AW9" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="AX9" t="n">
-        <v>4.7</v>
+        <v>10</v>
       </c>
       <c r="AY9" t="n">
-        <v>4.8</v>
+        <v>10</v>
       </c>
       <c r="AZ9" t="n">
-        <v>6.2</v>
+        <v>14.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="BB9" t="n">
-        <v>6.2</v>
+        <v>11.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>6.4</v>
+        <v>14.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="BE9" t="n">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="BF9" t="n">
-        <v>6.4</v>
+        <v>21</v>
       </c>
       <c r="BG9" t="n">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH9" t="n">
         <v>2.68</v>
@@ -2806,13 +2806,13 @@
         <v>12.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BN9" t="n">
         <v>4.7</v>
@@ -2824,13 +2824,13 @@
         <v>19</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BR9" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT9" t="n">
         <v>8</v>
@@ -2839,26 +2839,26 @@
         <v>6</v>
       </c>
       <c r="BV9" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BZ9" t="n">
         <v>55</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-13 16:49:34</t>
+          <t>2026-07-13 18:58:03</t>
         </is>
       </c>
     </row>
@@ -2892,28 +2892,28 @@
         <v>1.89</v>
       </c>
       <c r="G10" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="H10" t="n">
         <v>4.9</v>
       </c>
       <c r="I10" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="J10" t="n">
         <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L10" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="M10" t="n">
         <v>1.13</v>
       </c>
       <c r="N10" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="O10" t="n">
         <v>1.58</v>
@@ -2922,25 +2922,25 @@
         <v>1.46</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.86</v>
+        <v>2.74</v>
       </c>
       <c r="R10" t="n">
         <v>1.16</v>
       </c>
       <c r="S10" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="T10" t="n">
         <v>2.3</v>
       </c>
       <c r="U10" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="V10" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W10" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="X10" t="n">
         <v>9.6</v>
@@ -2949,19 +2949,19 @@
         <v>15.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AA10" t="n">
-        <v>220</v>
+        <v>700</v>
       </c>
       <c r="AB10" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="AC10" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AD10" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AE10" t="n">
         <v>140</v>
@@ -2973,85 +2973,85 @@
         <v>14</v>
       </c>
       <c r="AH10" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AI10" t="n">
-        <v>170</v>
+        <v>540</v>
       </c>
       <c r="AJ10" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AK10" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AL10" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AM10" t="n">
-        <v>330</v>
+        <v>500</v>
       </c>
       <c r="AN10" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AO10" t="n">
-        <v>260</v>
+        <v>700</v>
       </c>
       <c r="AP10" t="n">
-        <v>3.05</v>
+        <v>6.8</v>
       </c>
       <c r="AQ10" t="n">
-        <v>3.45</v>
+        <v>6.2</v>
       </c>
       <c r="AR10" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="AT10" t="n">
-        <v>2.76</v>
+        <v>5.2</v>
       </c>
       <c r="AU10" t="n">
-        <v>3</v>
+        <v>5.8</v>
       </c>
       <c r="AV10" t="n">
-        <v>3.85</v>
+        <v>17</v>
       </c>
       <c r="AW10" t="n">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="AX10" t="n">
-        <v>3.25</v>
+        <v>7.6</v>
       </c>
       <c r="AY10" t="n">
-        <v>3.35</v>
+        <v>7</v>
       </c>
       <c r="AZ10" t="n">
-        <v>3.95</v>
+        <v>4.8</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="BB10" t="n">
-        <v>3.85</v>
+        <v>18</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.95</v>
+        <v>21</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
       <c r="BF10" t="n">
-        <v>3.95</v>
+        <v>19.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
       <c r="BH10" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="BI10" t="n">
         <v>2.18</v>
@@ -3060,31 +3060,31 @@
         <v>13</v>
       </c>
       <c r="BK10" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>2.16</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN10" t="n">
         <v>4.5</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BP10" t="n">
         <v>17</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.94</v>
+        <v>6.8</v>
       </c>
       <c r="BR10" t="n">
         <v>46</v>
       </c>
       <c r="BS10" t="n">
-        <v>2.08</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT10" t="n">
         <v>8.800000000000001</v>
@@ -3096,23 +3096,23 @@
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>2.12</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.14</v>
+        <v>10</v>
       </c>
       <c r="BZ10" t="n">
         <v>50</v>
       </c>
       <c r="CA10" t="n">
-        <v>2.1</v>
+        <v>9.4</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-13 16:49:34</t>
+          <t>2026-07-13 18:58:03</t>
         </is>
       </c>
     </row>
@@ -3143,13 +3143,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="G11" t="n">
         <v>3.55</v>
       </c>
       <c r="H11" t="n">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="I11" t="n">
         <v>3.15</v>
@@ -3161,13 +3161,13 @@
         <v>3.1</v>
       </c>
       <c r="L11" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="M11" t="n">
         <v>1.14</v>
       </c>
       <c r="N11" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="O11" t="n">
         <v>1.6</v>
@@ -3176,13 +3176,13 @@
         <v>1.42</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="R11" t="n">
         <v>1.15</v>
       </c>
       <c r="S11" t="n">
-        <v>2.6</v>
+        <v>6</v>
       </c>
       <c r="T11" t="n">
         <v>2.14</v>
@@ -3194,19 +3194,19 @@
         <v>1.47</v>
       </c>
       <c r="W11" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="X11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y11" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Z11" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB11" t="n">
         <v>10.5</v>
@@ -3218,91 +3218,91 @@
         <v>17</v>
       </c>
       <c r="AE11" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AF11" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AG11" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AI11" t="n">
-        <v>100</v>
+        <v>540</v>
       </c>
       <c r="AJ11" t="n">
         <v>80</v>
       </c>
       <c r="AK11" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AL11" t="n">
-        <v>110</v>
+        <v>540</v>
       </c>
       <c r="AM11" t="n">
-        <v>280</v>
+        <v>500</v>
       </c>
       <c r="AN11" t="n">
         <v>95</v>
       </c>
       <c r="AO11" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.92</v>
+        <v>6.2</v>
       </c>
       <c r="AQ11" t="n">
-        <v>2.94</v>
+        <v>6.4</v>
       </c>
       <c r="AR11" t="n">
-        <v>3.55</v>
+        <v>12.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="AT11" t="n">
-        <v>3.05</v>
+        <v>7</v>
       </c>
       <c r="AU11" t="n">
-        <v>2.86</v>
+        <v>5.8</v>
       </c>
       <c r="AV11" t="n">
-        <v>3.45</v>
+        <v>10</v>
       </c>
       <c r="AW11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AX11" t="n">
-        <v>3.7</v>
+        <v>14.5</v>
       </c>
       <c r="AY11" t="n">
-        <v>3.5</v>
+        <v>11</v>
       </c>
       <c r="AZ11" t="n">
-        <v>3.8</v>
+        <v>18</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="BB11" t="n">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="BC11" t="n">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="BE11" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="BF11" t="n">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="BH11" t="n">
         <v>2.66</v>
@@ -3314,59 +3314,59 @@
         <v>12.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="BN11" t="n">
         <v>6.4</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BP11" t="n">
         <v>34</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BR11" t="n">
         <v>65</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="BT11" t="n">
         <v>5.9</v>
       </c>
       <c r="BU11" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BV11" t="n">
         <v>29</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="BX11" t="n">
         <v>60</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="BZ11" t="n">
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-13 16:49:34</t>
+          <t>2026-07-13 18:58:03</t>
         </is>
       </c>
     </row>
@@ -3400,46 +3400,46 @@
         <v>2.06</v>
       </c>
       <c r="G12" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="H12" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="I12" t="n">
         <v>4.4</v>
       </c>
       <c r="J12" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K12" t="n">
         <v>3.65</v>
       </c>
       <c r="L12" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M12" t="n">
         <v>1.08</v>
       </c>
       <c r="N12" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="O12" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P12" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="R12" t="n">
         <v>1.28</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="T12" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U12" t="n">
         <v>1.96</v>
@@ -3448,22 +3448,22 @@
         <v>1.31</v>
       </c>
       <c r="W12" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="X12" t="n">
         <v>14.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Z12" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA12" t="n">
         <v>110</v>
       </c>
       <c r="AB12" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC12" t="n">
         <v>9.6</v>
@@ -3475,13 +3475,13 @@
         <v>60</v>
       </c>
       <c r="AF12" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI12" t="n">
         <v>75</v>
@@ -3496,10 +3496,10 @@
         <v>55</v>
       </c>
       <c r="AM12" t="n">
-        <v>150</v>
+        <v>450</v>
       </c>
       <c r="AN12" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AO12" t="n">
         <v>85</v>
@@ -3514,7 +3514,7 @@
         <v>22</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="AT12" t="n">
         <v>7.4</v>
@@ -3538,7 +3538,7 @@
         <v>16.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="BB12" t="n">
         <v>19</v>
@@ -3550,19 +3550,19 @@
         <v>30</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="BF12" t="n">
         <v>16</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BH12" t="n">
         <v>3.2</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="BJ12" t="n">
         <v>10.5</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-13 16:49:34</t>
+          <t>2026-07-13 18:58:03</t>
         </is>
       </c>
     </row>
@@ -3651,175 +3651,175 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.49</v>
+        <v>2.6</v>
       </c>
       <c r="G13" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="H13" t="n">
-        <v>1.49</v>
+        <v>2.76</v>
       </c>
       <c r="I13" t="n">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="J13" t="n">
-        <v>1.17</v>
+        <v>2.72</v>
       </c>
       <c r="K13" t="n">
         <v>3.2</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="M13" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N13" t="n">
-        <v>1.25</v>
+        <v>2.44</v>
       </c>
       <c r="O13" t="n">
-        <v>1.02</v>
+        <v>1.49</v>
       </c>
       <c r="P13" t="n">
-        <v>1.25</v>
+        <v>1.48</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.02</v>
+        <v>2.46</v>
       </c>
       <c r="R13" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="S13" t="n">
-        <v>1.36</v>
+        <v>4.4</v>
       </c>
       <c r="T13" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="U13" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="V13" t="n">
-        <v>1.02</v>
+        <v>1.4</v>
       </c>
       <c r="W13" t="n">
-        <v>1.02</v>
+        <v>1.44</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="Y13" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z13" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB13" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AC13" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE13" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF13" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH13" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI13" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK13" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AL13" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM13" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BH13" t="n">
-        <v>1000</v>
+        <v>2.86</v>
       </c>
       <c r="BI13" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="BJ13" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK13" t="n">
         <v>1.01</v>
@@ -3831,50 +3831,50 @@
         <v>1.01</v>
       </c>
       <c r="BN13" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BO13" t="n">
         <v>1.01</v>
       </c>
       <c r="BP13" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BQ13" t="n">
         <v>1.01</v>
       </c>
       <c r="BR13" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS13" t="n">
         <v>1.01</v>
       </c>
       <c r="BT13" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU13" t="n">
         <v>1.01</v>
       </c>
       <c r="BV13" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW13" t="n">
         <v>1.01</v>
       </c>
       <c r="BX13" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY13" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ13" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="CA13" t="n">
         <v>1.01</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-13 16:49:34</t>
+          <t>2026-07-13 18:58:03</t>
         </is>
       </c>
     </row>
@@ -3905,175 +3905,175 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.1</v>
+        <v>2.72</v>
       </c>
       <c r="G14" t="n">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="H14" t="n">
-        <v>1.1</v>
+        <v>2.68</v>
       </c>
       <c r="I14" t="n">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="J14" t="n">
-        <v>1.19</v>
+        <v>2.66</v>
       </c>
       <c r="K14" t="n">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="M14" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N14" t="n">
-        <v>1.25</v>
+        <v>2.24</v>
       </c>
       <c r="O14" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="P14" t="n">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.02</v>
+        <v>2.6</v>
       </c>
       <c r="R14" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="S14" t="n">
-        <v>1.53</v>
+        <v>5.3</v>
       </c>
       <c r="T14" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="V14" t="n">
-        <v>1.02</v>
+        <v>1.41</v>
       </c>
       <c r="W14" t="n">
-        <v>1.02</v>
+        <v>1.41</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="Z14" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AA14" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB14" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC14" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE14" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF14" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG14" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI14" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK14" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AM14" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BH14" t="n">
-        <v>1000</v>
+        <v>2.76</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="BJ14" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK14" t="n">
         <v>1.01</v>
@@ -4085,50 +4085,50 @@
         <v>1.01</v>
       </c>
       <c r="BN14" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO14" t="n">
         <v>1.01</v>
       </c>
       <c r="BP14" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BQ14" t="n">
         <v>1.01</v>
       </c>
       <c r="BR14" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS14" t="n">
         <v>1.01</v>
       </c>
       <c r="BT14" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU14" t="n">
         <v>1.01</v>
       </c>
       <c r="BV14" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW14" t="n">
         <v>1.01</v>
       </c>
       <c r="BX14" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY14" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="CA14" t="n">
         <v>1.01</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-13 16:49:34</t>
+          <t>2026-07-13 18:58:03</t>
         </is>
       </c>
     </row>
@@ -4159,175 +4159,175 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.04</v>
+        <v>2.94</v>
       </c>
       <c r="G15" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="H15" t="n">
-        <v>1.04</v>
+        <v>2.74</v>
       </c>
       <c r="I15" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="J15" t="n">
-        <v>1.03</v>
+        <v>2.64</v>
       </c>
       <c r="K15" t="n">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="L15" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="M15" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="N15" t="n">
-        <v>1.24</v>
+        <v>2.02</v>
       </c>
       <c r="O15" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="P15" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.02</v>
+        <v>2.78</v>
       </c>
       <c r="R15" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S15" t="n">
-        <v>1.6</v>
+        <v>5.3</v>
       </c>
       <c r="T15" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="U15" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="V15" t="n">
-        <v>1.02</v>
+        <v>1.45</v>
       </c>
       <c r="W15" t="n">
-        <v>1.02</v>
+        <v>1.4</v>
       </c>
       <c r="X15" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="Y15" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="Z15" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB15" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AC15" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE15" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF15" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG15" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH15" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AI15" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK15" t="n">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AL15" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM15" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN15" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO15" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH15" t="n">
-        <v>1000</v>
+        <v>2.52</v>
       </c>
       <c r="BI15" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="BJ15" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK15" t="n">
         <v>1.01</v>
@@ -4339,13 +4339,13 @@
         <v>1.01</v>
       </c>
       <c r="BN15" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO15" t="n">
         <v>1.01</v>
       </c>
       <c r="BP15" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BQ15" t="n">
         <v>1.01</v>
@@ -4357,7 +4357,7 @@
         <v>1.01</v>
       </c>
       <c r="BT15" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BU15" t="n">
         <v>1.01</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-13 16:49:34</t>
+          <t>2026-07-13 18:58:03</t>
         </is>
       </c>
     </row>
@@ -4413,175 +4413,175 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.04</v>
+        <v>2.76</v>
       </c>
       <c r="G16" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="H16" t="n">
-        <v>1.04</v>
+        <v>2.6</v>
       </c>
       <c r="I16" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="J16" t="n">
-        <v>1.03</v>
+        <v>2.7</v>
       </c>
       <c r="K16" t="n">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="M16" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N16" t="n">
-        <v>1.25</v>
+        <v>2.26</v>
       </c>
       <c r="O16" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="P16" t="n">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.02</v>
+        <v>2.5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="S16" t="n">
-        <v>1.52</v>
+        <v>4.4</v>
       </c>
       <c r="T16" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="U16" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="V16" t="n">
-        <v>1.02</v>
+        <v>1.44</v>
       </c>
       <c r="W16" t="n">
-        <v>1.02</v>
+        <v>1.4</v>
       </c>
       <c r="X16" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="Y16" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z16" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB16" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AC16" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF16" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG16" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AH16" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI16" t="n">
-        <v>1000</v>
+        <v>540</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1000</v>
+        <v>420</v>
       </c>
       <c r="AK16" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL16" t="n">
-        <v>1000</v>
+        <v>540</v>
       </c>
       <c r="AM16" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AN16" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AO16" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BH16" t="n">
-        <v>1000</v>
+        <v>2.84</v>
       </c>
       <c r="BI16" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="BJ16" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK16" t="n">
         <v>1.01</v>
@@ -4593,13 +4593,13 @@
         <v>1.01</v>
       </c>
       <c r="BN16" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO16" t="n">
         <v>1.01</v>
       </c>
       <c r="BP16" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BQ16" t="n">
         <v>1.01</v>
@@ -4611,13 +4611,13 @@
         <v>1.01</v>
       </c>
       <c r="BT16" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU16" t="n">
         <v>1.01</v>
       </c>
       <c r="BV16" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BW16" t="n">
         <v>1.01</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-13 16:49:34</t>
+          <t>2026-07-13 18:58:03</t>
         </is>
       </c>
     </row>
@@ -4673,16 +4673,16 @@
         <v>1000</v>
       </c>
       <c r="H17" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="I17" t="n">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="J17" t="n">
         <v>3</v>
       </c>
       <c r="K17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
@@ -4715,118 +4715,118 @@
         <v>1.01</v>
       </c>
       <c r="V17" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="X17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Y17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AD17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BH17" t="n">
         <v>1000</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-13 16:49:34</t>
+          <t>2026-07-13 18:58:03</t>
         </is>
       </c>
     </row>
@@ -4924,10 +4924,10 @@
         <v>3.1</v>
       </c>
       <c r="G18" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="H18" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="I18" t="n">
         <v>3</v>
@@ -4936,7 +4936,7 @@
         <v>2.88</v>
       </c>
       <c r="K18" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="L18" t="n">
         <v>1.66</v>
@@ -4945,7 +4945,7 @@
         <v>1.15</v>
       </c>
       <c r="N18" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="O18" t="n">
         <v>1.64</v>
@@ -4954,7 +4954,7 @@
         <v>1.43</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="R18" t="n">
         <v>1.16</v>
@@ -4963,7 +4963,7 @@
         <v>6.8</v>
       </c>
       <c r="T18" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="U18" t="n">
         <v>1.68</v>
@@ -4978,7 +4978,7 @@
         <v>7.2</v>
       </c>
       <c r="Y18" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="Z18" t="n">
         <v>18</v>
@@ -4987,7 +4987,7 @@
         <v>55</v>
       </c>
       <c r="AB18" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC18" t="n">
         <v>8.4</v>
@@ -4996,7 +4996,7 @@
         <v>14.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF18" t="n">
         <v>19.5</v>
@@ -5005,10 +5005,10 @@
         <v>17</v>
       </c>
       <c r="AH18" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AI18" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="AJ18" t="n">
         <v>65</v>
@@ -5020,7 +5020,7 @@
         <v>100</v>
       </c>
       <c r="AM18" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AN18" t="n">
         <v>80</v>
@@ -5038,7 +5038,7 @@
         <v>15</v>
       </c>
       <c r="AS18" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AT18" t="n">
         <v>7.6</v>
@@ -5062,10 +5062,10 @@
         <v>22</v>
       </c>
       <c r="BA18" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB18" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC18" t="n">
         <v>42</v>
@@ -5074,16 +5074,16 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BE18" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF18" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BG18" t="n">
         <v>50</v>
       </c>
       <c r="BH18" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="BI18" t="n">
         <v>2.08</v>
@@ -5104,7 +5104,7 @@
         <v>6.2</v>
       </c>
       <c r="BO18" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BP18" t="n">
         <v>1000</v>
@@ -5119,10 +5119,10 @@
         <v>9.4</v>
       </c>
       <c r="BT18" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BU18" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BV18" t="n">
         <v>32</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-13 16:49:34</t>
+          <t>2026-07-13 18:58:03</t>
         </is>
       </c>
     </row>
@@ -5178,7 +5178,7 @@
         <v>1.21</v>
       </c>
       <c r="G19" t="n">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="H19" t="n">
         <v>1.04</v>
@@ -5187,7 +5187,7 @@
         <v>1000</v>
       </c>
       <c r="J19" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K19" t="n">
         <v>1000</v>
@@ -5199,13 +5199,13 @@
         <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="O19" t="n">
         <v>1.14</v>
       </c>
       <c r="P19" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Q19" t="n">
         <v>1.14</v>
@@ -5214,7 +5214,7 @@
         <v>1.28</v>
       </c>
       <c r="S19" t="n">
-        <v>1.14</v>
+        <v>2.12</v>
       </c>
       <c r="T19" t="n">
         <v>1.01</v>
@@ -5223,10 +5223,10 @@
         <v>1.01</v>
       </c>
       <c r="V19" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="W19" t="n">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="X19" t="n">
         <v>1000</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-13 16:49:34</t>
+          <t>2026-07-13 18:58:03</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-14.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,402 +417,402 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>League</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Home</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Away</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Odd_H_Back</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Odd_H_Lay</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Odd_A_Back</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Odd_A_Lay</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Odd_D_Back</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Odd_D_Lay</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Odd_Over05_HT_Back</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Odd_Over05_FT_Back</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Odd_Under15_FT_Back</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Odd_Over15_FT_Back</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Odd_Under25_FT_Back</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Odd_Over25_FT_Back</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Odd_Under35_FT_Back</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Odd_Over35_FT_Back</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Odd_BTTS_Yes_Back</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Odd_BTTS_No_Back</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Double_Chance_Home_or_Draw_Back</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Double_Chance_Draw_or_Away_Back</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Odd_CS_0x0_Lay</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Odd_CS_0x1_Lay</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Odd_CS_0x2_Lay</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Odd_CS_0x3_Lay</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Odd_CS_1x0_Lay</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Odd_CS_1x1_Lay</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Odd_CS_1x2_Lay</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Odd_CS_1x3_Lay</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Odd_CS_2x0_Lay</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Odd_CS_2x1_Lay</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Odd_CS_2x2_Lay</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Odd_CS_2x3_Lay</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Odd_CS_3x0_Lay</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Odd_CS_3x1_Lay</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>Odd_CS_3x2_Lay</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>Odd_CS_3x3_Lay</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>Odd_CS_Goleada_H_Lay</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>Odd_CS_Goleada_A_Lay</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>Odd_CS_0x0_Back</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>Odd_CS_0x1_Back</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>Odd_CS_0x2_Back</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>Odd_CS_0x3_Back</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>Odd_CS_1x0_Back</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Odd_CS_1x1_Back</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>Odd_CS_1x2_Back</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>Odd_CS_1x3_Back</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>Odd_CS_2x0_Back</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>Odd_CS_2x1_Back</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>Odd_CS_2x2_Back</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>Odd_CS_2x3_Back</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>Odd_CS_3x0_Back</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>Odd_CS_3x1_Back</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>Odd_CS_3x2_Back</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>Odd_CS_3x3_Back</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>Odd_CS_Goleada_H_Back</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>Odd_CS_Goleada_A_Back</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>Odd_HTS_0x0_Lay</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>Odd_HTS_0x0_Back</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>Odd_HTS_1x1_Lay</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>Odd_HTS_1x1_Back</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>Odd_HTS_2x2_Lay</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>Odd_HTS_2x2_Back</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>Odd_HTS_1x0_Lay</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>Odd_HTS_1x0_Back</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>Odd_HTS_2x0_Lay</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>Odd_HTS_2x0_Back</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>Odd_HTS_2x1_Lay</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>Odd_HTS_2x1_Back</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>Odd_HTS_0x1_Lay</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>Odd_HTS_0x1_Back</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>Odd_HTS_0x2_Lay</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>Odd_HTS_0x2_Back</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>Odd_HTS_1x2_Lay</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>Odd_HTS_1x2_Back</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>Odd_HTS_Outros_Lay</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>Odd_HTS_Outros_Back</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>SnapshotTS</t>
         </is>
@@ -857,22 +845,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="G2" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="H2" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="I2" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="J2" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="K2" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="L2" t="n">
         <v>1.23</v>
@@ -887,22 +875,22 @@
         <v>1.13</v>
       </c>
       <c r="P2" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="R2" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="S2" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="T2" t="n">
         <v>1.56</v>
       </c>
       <c r="U2" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="V2" t="n">
         <v>1.16</v>
@@ -911,130 +899,130 @@
         <v>2.92</v>
       </c>
       <c r="X2" t="n">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="Y2" t="n">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="Z2" t="n">
-        <v>75</v>
+        <v>450</v>
       </c>
       <c r="AA2" t="n">
         <v>190</v>
       </c>
       <c r="AB2" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AC2" t="n">
         <v>13</v>
       </c>
       <c r="AD2" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AE2" t="n">
-        <v>75</v>
+        <v>400</v>
       </c>
       <c r="AF2" t="n">
         <v>13</v>
       </c>
       <c r="AG2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>65</v>
+        <v>200</v>
       </c>
       <c r="AJ2" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AK2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AL2" t="n">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="AM2" t="n">
-        <v>75</v>
+        <v>260</v>
       </c>
       <c r="AN2" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AO2" t="n">
-        <v>60</v>
+        <v>170</v>
       </c>
       <c r="AP2" t="n">
-        <v>7.4</v>
+        <v>18.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>7.4</v>
+        <v>36</v>
       </c>
       <c r="AR2" t="n">
-        <v>7.8</v>
+        <v>12</v>
       </c>
       <c r="AS2" t="n">
-        <v>8.4</v>
+        <v>13</v>
       </c>
       <c r="AT2" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AU2" t="n">
         <v>11</v>
       </c>
       <c r="AV2" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AW2" t="n">
-        <v>7.8</v>
+        <v>28</v>
       </c>
       <c r="AX2" t="n">
         <v>11.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AZ2" t="n">
         <v>15.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="BB2" t="n">
         <v>14</v>
       </c>
       <c r="BC2" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BD2" t="n">
-        <v>6.8</v>
+        <v>21</v>
       </c>
       <c r="BE2" t="n">
-        <v>8.199999999999999</v>
+        <v>28</v>
       </c>
       <c r="BF2" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BG2" t="n">
-        <v>7.8</v>
+        <v>11</v>
       </c>
       <c r="BH2" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.85</v>
+        <v>4.6</v>
       </c>
       <c r="BJ2" t="n">
         <v>9.6</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BN2" t="n">
         <v>4.7</v>
@@ -1046,41 +1034,41 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BR2" t="n">
         <v>18</v>
       </c>
       <c r="BS2" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BT2" t="n">
         <v>11</v>
       </c>
       <c r="BU2" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ2" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="CA2" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-13 18:58:03</t>
+          <t>2026-07-13 22:40:56</t>
         </is>
       </c>
     </row>
@@ -1114,13 +1102,13 @@
         <v>1.78</v>
       </c>
       <c r="G3" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="H3" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J3" t="n">
         <v>4.4</v>
@@ -1129,7 +1117,7 @@
         <v>5.2</v>
       </c>
       <c r="L3" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="M3" t="n">
         <v>1.02</v>
@@ -1144,10 +1132,10 @@
         <v>3.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="R3" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="S3" t="n">
         <v>1.91</v>
@@ -1156,133 +1144,133 @@
         <v>1.43</v>
       </c>
       <c r="U3" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="V3" t="n">
         <v>1.3</v>
       </c>
       <c r="W3" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="X3" t="n">
-        <v>48</v>
+        <v>130</v>
       </c>
       <c r="Y3" t="n">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="Z3" t="n">
-        <v>44</v>
+        <v>140</v>
       </c>
       <c r="AA3" t="n">
         <v>500</v>
       </c>
       <c r="AB3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AL3" t="n">
         <v>23</v>
       </c>
-      <c r="AC3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>46</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>38</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>28</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>27</v>
-      </c>
       <c r="AM3" t="n">
-        <v>55</v>
+        <v>200</v>
       </c>
       <c r="AN3" t="n">
         <v>6.2</v>
       </c>
       <c r="AO3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.6</v>
+        <v>7.6</v>
       </c>
       <c r="AQ3" t="n">
-        <v>20</v>
+        <v>14.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.5</v>
+        <v>7.6</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV3" t="n">
         <v>13.5</v>
       </c>
-      <c r="AU3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>13</v>
-      </c>
       <c r="AW3" t="n">
-        <v>4.6</v>
+        <v>7.4</v>
       </c>
       <c r="AX3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AY3" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AZ3" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.4</v>
+        <v>16</v>
       </c>
       <c r="BB3" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BC3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BD3" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BE3" t="n">
-        <v>34</v>
+        <v>7.6</v>
       </c>
       <c r="BF3" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BG3" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="BH3" t="n">
         <v>5.7</v>
       </c>
       <c r="BI3" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="BJ3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BK3" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
@@ -1294,7 +1282,7 @@
         <v>5.7</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="BP3" t="n">
         <v>12</v>
@@ -1315,7 +1303,7 @@
         <v>6.2</v>
       </c>
       <c r="BV3" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="BW3" t="n">
         <v>7</v>
@@ -1330,11 +1318,11 @@
         <v>11</v>
       </c>
       <c r="CA3" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-13 18:58:03</t>
+          <t>2026-07-13 22:40:56</t>
         </is>
       </c>
     </row>
@@ -1356,239 +1344,239 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Camioneros</t>
+          <t>CS Dock Sud</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CSD Liniers de Ciudad Evita</t>
+          <t>Uai Urquiza</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="G4" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="H4" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="I4" t="n">
         <v>5.4</v>
       </c>
       <c r="J4" t="n">
-        <v>2.94</v>
+        <v>2.58</v>
       </c>
       <c r="K4" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="M4" t="n">
         <v>1.13</v>
       </c>
       <c r="N4" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="O4" t="n">
         <v>1.57</v>
       </c>
       <c r="P4" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.72</v>
+        <v>2.86</v>
       </c>
       <c r="R4" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="S4" t="n">
-        <v>5.8</v>
+        <v>2.92</v>
       </c>
       <c r="T4" t="n">
-        <v>2.24</v>
+        <v>1.11</v>
       </c>
       <c r="U4" t="n">
-        <v>1.65</v>
+        <v>1.11</v>
       </c>
       <c r="V4" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="W4" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="X4" t="n">
-        <v>8.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="Y4" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="Z4" t="n">
+        <v>120</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC4" t="n">
         <v>42</v>
       </c>
-      <c r="AA4" t="n">
-        <v>700</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>7.8</v>
-      </c>
       <c r="AD4" t="n">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="AE4" t="n">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="AF4" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AG4" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AH4" t="n">
-        <v>32</v>
+        <v>85</v>
       </c>
       <c r="AI4" t="n">
-        <v>700</v>
+        <v>540</v>
       </c>
       <c r="AJ4" t="n">
-        <v>32</v>
+        <v>900</v>
       </c>
       <c r="AK4" t="n">
-        <v>36</v>
+        <v>110</v>
       </c>
       <c r="AL4" t="n">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="AM4" t="n">
         <v>500</v>
       </c>
       <c r="AN4" t="n">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="AO4" t="n">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="AP4" t="n">
-        <v>6.2</v>
+        <v>4.2</v>
       </c>
       <c r="AQ4" t="n">
-        <v>9.199999999999999</v>
+        <v>1.56</v>
       </c>
       <c r="AR4" t="n">
-        <v>5.8</v>
+        <v>1.67</v>
       </c>
       <c r="AS4" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BQ4" t="n">
         <v>6.4</v>
       </c>
-      <c r="AT4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AX4" t="n">
+      <c r="BR4" t="n">
+        <v>48</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>8</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY4" t="n">
         <v>8.6</v>
       </c>
-      <c r="AY4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BZ4" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-13 18:58:03</t>
+          <t>2026-07-13 22:40:56</t>
         </is>
       </c>
     </row>
@@ -1610,239 +1598,239 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Argentino de Quilmes</t>
+          <t>Flandria</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandi</t>
+          <t>Argentino de Merlo</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.95</v>
+        <v>2.56</v>
       </c>
       <c r="G5" t="n">
-        <v>4.6</v>
+        <v>2.86</v>
       </c>
       <c r="H5" t="n">
-        <v>2.16</v>
+        <v>3.25</v>
       </c>
       <c r="I5" t="n">
-        <v>2.42</v>
+        <v>3.65</v>
       </c>
       <c r="J5" t="n">
-        <v>2.86</v>
+        <v>2.66</v>
       </c>
       <c r="K5" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L5" t="n">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="M5" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="R5" t="n">
         <v>1.14</v>
       </c>
-      <c r="N5" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.16</v>
-      </c>
       <c r="S5" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="T5" t="n">
         <v>2.2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.69</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.7</v>
+        <v>1.38</v>
       </c>
       <c r="W5" t="n">
-        <v>1.28</v>
+        <v>1.54</v>
       </c>
       <c r="X5" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="Y5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z5" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="AA5" t="n">
-        <v>42</v>
+        <v>250</v>
       </c>
       <c r="AB5" t="n">
-        <v>11</v>
+        <v>7.4</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>13</v>
+        <v>17.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AF5" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>340</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>120</v>
+      </c>
+      <c r="AK5" t="n">
         <v>48</v>
       </c>
-      <c r="AG5" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>38</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>460</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>500</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>500</v>
-      </c>
       <c r="AL5" t="n">
-        <v>540</v>
+        <v>210</v>
       </c>
       <c r="AM5" t="n">
         <v>500</v>
       </c>
       <c r="AN5" t="n">
+        <v>390</v>
+      </c>
+      <c r="AO5" t="n">
         <v>500</v>
       </c>
-      <c r="AO5" t="n">
-        <v>44</v>
-      </c>
       <c r="AP5" t="n">
-        <v>6.8</v>
+        <v>4.2</v>
       </c>
       <c r="AQ5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AU5" t="n">
         <v>4.3</v>
       </c>
-      <c r="AR5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>21</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU5" t="n">
+      <c r="AV5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AX5" t="n">
         <v>6.2</v>
       </c>
-      <c r="AV5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>21</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>21</v>
-      </c>
       <c r="AY5" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AZ5" t="n">
-        <v>21</v>
+        <v>7.4</v>
       </c>
       <c r="BA5" t="n">
-        <v>28</v>
+        <v>9.4</v>
       </c>
       <c r="BB5" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BC5" t="n">
         <v>8.4</v>
       </c>
       <c r="BD5" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE5" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF5" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BG5" t="n">
-        <v>23</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.68</v>
+        <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="BJ5" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="BN5" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BP5" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="BT5" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="BV5" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-13 18:58:03</t>
+          <t>2026-07-13 22:40:56</t>
         </is>
       </c>
     </row>
@@ -1864,246 +1852,246 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Sportivo Italiano</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Excursionistas</t>
+          <t>Villa San Carlos</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.6</v>
+        <v>1.89</v>
       </c>
       <c r="G6" t="n">
-        <v>4.3</v>
+        <v>2.08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.2</v>
+        <v>4.9</v>
       </c>
       <c r="I6" t="n">
-        <v>2.52</v>
+        <v>5.9</v>
       </c>
       <c r="J6" t="n">
+        <v>3</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Q6" t="n">
         <v>2.86</v>
       </c>
-      <c r="K6" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N6" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.46</v>
-      </c>
       <c r="R6" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="T6" t="n">
-        <v>2</v>
+        <v>2.28</v>
       </c>
       <c r="U6" t="n">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="V6" t="n">
-        <v>1.65</v>
+        <v>1.2</v>
       </c>
       <c r="W6" t="n">
-        <v>1.3</v>
+        <v>1.94</v>
       </c>
       <c r="X6" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="Y6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AC6" t="n">
         <v>8</v>
       </c>
-      <c r="Z6" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>36</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>7.8</v>
-      </c>
       <c r="AD6" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="AE6" t="n">
-        <v>34</v>
+        <v>140</v>
       </c>
       <c r="AF6" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="AG6" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="AH6" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AI6" t="n">
-        <v>65</v>
+        <v>700</v>
       </c>
       <c r="AJ6" t="n">
-        <v>110</v>
+        <v>26</v>
       </c>
       <c r="AK6" t="n">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="AL6" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AM6" t="n">
         <v>500</v>
       </c>
       <c r="AN6" t="n">
-        <v>110</v>
+        <v>29</v>
       </c>
       <c r="AO6" t="n">
-        <v>36</v>
+        <v>700</v>
       </c>
       <c r="AP6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR6" t="n">
         <v>7.4</v>
       </c>
-      <c r="AQ6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AR6" t="n">
+      <c r="AS6" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>13</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
         <v>11</v>
       </c>
-      <c r="AS6" t="n">
-        <v>22</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV6" t="n">
+      <c r="BN6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>17</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>46</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BT6" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AW6" t="n">
-        <v>20</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>7</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>21</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>12</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>4</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>40</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BR6" t="n">
+      <c r="BU6" t="n">
+        <v>5</v>
+      </c>
+      <c r="BV6" t="n">
         <v>65</v>
       </c>
-      <c r="BS6" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>22</v>
-      </c>
       <c r="BW6" t="n">
-        <v>6.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX6" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.1</v>
+        <v>10</v>
       </c>
       <c r="BZ6" t="n">
         <v>50</v>
       </c>
       <c r="CA6" t="n">
-        <v>2.1</v>
+        <v>9.4</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-13 18:58:03</t>
+          <t>2026-07-13 22:40:56</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2118,239 +2106,239 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Grotta</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Grindavik</t>
+          <t>Excursionistas</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.92</v>
+        <v>3.6</v>
       </c>
       <c r="G7" t="n">
-        <v>2.14</v>
+        <v>4.3</v>
       </c>
       <c r="H7" t="n">
-        <v>3.3</v>
+        <v>2.24</v>
       </c>
       <c r="I7" t="n">
-        <v>3.85</v>
+        <v>2.5</v>
       </c>
       <c r="J7" t="n">
-        <v>4.1</v>
+        <v>2.86</v>
       </c>
       <c r="K7" t="n">
-        <v>4.8</v>
+        <v>3.35</v>
       </c>
       <c r="L7" t="n">
-        <v>1.2</v>
+        <v>1.55</v>
       </c>
       <c r="M7" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="N7" t="n">
-        <v>5.5</v>
+        <v>2.72</v>
       </c>
       <c r="O7" t="n">
-        <v>1.12</v>
+        <v>1.49</v>
       </c>
       <c r="P7" t="n">
-        <v>2.7</v>
+        <v>1.52</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.29</v>
+        <v>2.6</v>
       </c>
       <c r="R7" t="n">
-        <v>1.62</v>
+        <v>1.19</v>
       </c>
       <c r="S7" t="n">
-        <v>1.94</v>
+        <v>5</v>
       </c>
       <c r="T7" t="n">
-        <v>1.46</v>
+        <v>2</v>
       </c>
       <c r="U7" t="n">
-        <v>2.76</v>
+        <v>1.75</v>
       </c>
       <c r="V7" t="n">
-        <v>1.35</v>
+        <v>1.67</v>
       </c>
       <c r="W7" t="n">
-        <v>1.88</v>
+        <v>1.31</v>
       </c>
       <c r="X7" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>38</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>250</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>70</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>200</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>110</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>36</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>24</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>23</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>28</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>9</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BP7" t="n">
         <v>40</v>
       </c>
-      <c r="Y7" t="n">
-        <v>29</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>40</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>75</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>21</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF7" t="n">
+      <c r="BQ7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>65</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BV7" t="n">
         <v>22</v>
       </c>
-      <c r="AG7" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>40</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>29</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>60</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>24</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>17</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>4</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>6</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>65</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>13</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>20</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>7</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>25</v>
-      </c>
       <c r="BW7" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="BX7" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="BY7" t="n">
         <v>7.8</v>
       </c>
       <c r="BZ7" t="n">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="CA7" t="n">
-        <v>5.9</v>
+        <v>7.8</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-13 18:58:03</t>
+          <t>2026-07-13 22:40:56</t>
         </is>
       </c>
     </row>
@@ -2372,112 +2360,112 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Flandria</t>
+          <t>Argentino de Quilmes</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Argentino de Merlo</t>
+          <t>Arsenal de Sarandi</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.5</v>
+        <v>3.85</v>
       </c>
       <c r="G8" t="n">
-        <v>2.92</v>
+        <v>4.6</v>
       </c>
       <c r="H8" t="n">
-        <v>3.05</v>
+        <v>2.18</v>
       </c>
       <c r="I8" t="n">
-        <v>3.8</v>
+        <v>2.4</v>
       </c>
       <c r="J8" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="K8" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="L8" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N8" t="n">
-        <v>2.22</v>
+        <v>2.56</v>
       </c>
       <c r="O8" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="P8" t="n">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.96</v>
+        <v>2.68</v>
       </c>
       <c r="R8" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="S8" t="n">
-        <v>2.96</v>
+        <v>5.7</v>
       </c>
       <c r="T8" t="n">
-        <v>1.83</v>
+        <v>2.18</v>
       </c>
       <c r="U8" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="V8" t="n">
-        <v>1.35</v>
+        <v>1.72</v>
       </c>
       <c r="W8" t="n">
-        <v>1.6</v>
+        <v>1.28</v>
       </c>
       <c r="X8" t="n">
-        <v>970</v>
+        <v>8.4</v>
       </c>
       <c r="Y8" t="n">
-        <v>970</v>
+        <v>7.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>500</v>
+        <v>13.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>500</v>
+        <v>38</v>
       </c>
       <c r="AB8" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AC8" t="n">
-        <v>970</v>
+        <v>7.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>500</v>
+        <v>12.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>500</v>
+        <v>42</v>
       </c>
       <c r="AF8" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AG8" t="n">
-        <v>500</v>
+        <v>19.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>500</v>
+        <v>30</v>
       </c>
       <c r="AI8" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AJ8" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK8" t="n">
-        <v>500</v>
+        <v>440</v>
       </c>
       <c r="AL8" t="n">
-        <v>500</v>
+        <v>540</v>
       </c>
       <c r="AM8" t="n">
         <v>500</v>
@@ -2486,125 +2474,125 @@
         <v>500</v>
       </c>
       <c r="AO8" t="n">
-        <v>500</v>
+        <v>44</v>
       </c>
       <c r="AP8" t="n">
-        <v>3.85</v>
+        <v>7</v>
       </c>
       <c r="AQ8" t="n">
-        <v>4.4</v>
+        <v>5.9</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.55</v>
+        <v>10.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.59</v>
+        <v>24</v>
       </c>
       <c r="AT8" t="n">
-        <v>4.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU8" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.53</v>
+        <v>10</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.59</v>
+        <v>24</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.55</v>
+        <v>21</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.54</v>
+        <v>15.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.57</v>
+        <v>20</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.59</v>
+        <v>28</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.59</v>
+        <v>9</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.59</v>
+        <v>8.6</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.59</v>
+        <v>9</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.6</v>
+        <v>9.4</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.59</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.59</v>
+        <v>24</v>
       </c>
       <c r="BH8" t="n">
-        <v>1000</v>
+        <v>2.72</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BN8" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BP8" t="n">
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT8" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BV8" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-13 18:58:03</t>
+          <t>2026-07-13 22:40:56</t>
         </is>
       </c>
     </row>
@@ -2626,79 +2614,79 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CS Dock Sud</t>
+          <t>Camioneros</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Uai Urquiza</t>
+          <t>CSD Liniers de Ciudad Evita</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="G9" t="n">
         <v>2.28</v>
       </c>
       <c r="H9" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I9" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="J9" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="K9" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="L9" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="O9" t="n">
         <v>1.59</v>
       </c>
-      <c r="M9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="N9" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.57</v>
-      </c>
       <c r="P9" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="R9" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="S9" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="T9" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="U9" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="V9" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W9" t="n">
         <v>1.78</v>
       </c>
       <c r="X9" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="Y9" t="n">
         <v>12</v>
       </c>
       <c r="Z9" t="n">
-        <v>34</v>
+        <v>95</v>
       </c>
       <c r="AA9" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB9" t="n">
         <v>6.8</v>
@@ -2707,10 +2695,10 @@
         <v>7.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE9" t="n">
-        <v>110</v>
+        <v>700</v>
       </c>
       <c r="AF9" t="n">
         <v>12</v>
@@ -2719,70 +2707,70 @@
         <v>12.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>27</v>
+        <v>75</v>
       </c>
       <c r="AI9" t="n">
-        <v>540</v>
+        <v>700</v>
       </c>
       <c r="AJ9" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AK9" t="n">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AL9" t="n">
-        <v>450</v>
+        <v>170</v>
       </c>
       <c r="AM9" t="n">
         <v>500</v>
       </c>
       <c r="AN9" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AO9" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="AP9" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AQ9" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AR9" t="n">
-        <v>13</v>
+        <v>7.6</v>
       </c>
       <c r="AS9" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AT9" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="AU9" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV9" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AW9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AX9" t="n">
         <v>9</v>
       </c>
-      <c r="AX9" t="n">
-        <v>10</v>
-      </c>
       <c r="AY9" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ9" t="n">
-        <v>14.5</v>
+        <v>7.2</v>
       </c>
       <c r="BA9" t="n">
         <v>9</v>
       </c>
       <c r="BB9" t="n">
-        <v>11.5</v>
+        <v>7.4</v>
       </c>
       <c r="BC9" t="n">
-        <v>14.5</v>
+        <v>7.6</v>
       </c>
       <c r="BD9" t="n">
         <v>8.6</v>
@@ -2791,52 +2779,52 @@
         <v>9.4</v>
       </c>
       <c r="BF9" t="n">
-        <v>21</v>
+        <v>7.6</v>
       </c>
       <c r="BG9" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BH9" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="BJ9" t="n">
         <v>12.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BN9" t="n">
         <v>4.7</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="BP9" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BQ9" t="n">
         <v>7.4</v>
       </c>
       <c r="BR9" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BS9" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BT9" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU9" t="n">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
@@ -2851,21 +2839,21 @@
         <v>10.5</v>
       </c>
       <c r="BZ9" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="CA9" t="n">
         <v>10</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-13 18:58:03</t>
+          <t>2026-07-13 22:40:56</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2880,184 +2868,184 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Sportivo Italiano</t>
+          <t>Grotta</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Villa San Carlos</t>
+          <t>Grindavik</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.89</v>
+        <v>2.22</v>
       </c>
       <c r="G10" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="H10" t="n">
-        <v>4.9</v>
+        <v>2.88</v>
       </c>
       <c r="I10" t="n">
-        <v>5.9</v>
+        <v>3.1</v>
       </c>
       <c r="J10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="P10" t="n">
         <v>3</v>
       </c>
-      <c r="K10" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.46</v>
-      </c>
       <c r="Q10" t="n">
-        <v>2.74</v>
+        <v>1.4</v>
       </c>
       <c r="R10" t="n">
-        <v>1.16</v>
+        <v>1.81</v>
       </c>
       <c r="S10" t="n">
-        <v>5.8</v>
+        <v>2.06</v>
       </c>
       <c r="T10" t="n">
-        <v>2.3</v>
+        <v>1.41</v>
       </c>
       <c r="U10" t="n">
-        <v>1.63</v>
+        <v>2.96</v>
       </c>
       <c r="V10" t="n">
-        <v>1.2</v>
+        <v>1.47</v>
       </c>
       <c r="W10" t="n">
-        <v>1.91</v>
+        <v>1.72</v>
       </c>
       <c r="X10" t="n">
-        <v>9.6</v>
+        <v>36</v>
       </c>
       <c r="Y10" t="n">
-        <v>15.5</v>
+        <v>24</v>
       </c>
       <c r="Z10" t="n">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="AA10" t="n">
-        <v>700</v>
+        <v>160</v>
       </c>
       <c r="AB10" t="n">
-        <v>6.2</v>
+        <v>21</v>
       </c>
       <c r="AC10" t="n">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>25</v>
+        <v>14.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>140</v>
+        <v>27</v>
       </c>
       <c r="AF10" t="n">
-        <v>12.5</v>
+        <v>23</v>
       </c>
       <c r="AG10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH10" t="n">
         <v>14</v>
       </c>
-      <c r="AH10" t="n">
-        <v>30</v>
-      </c>
       <c r="AI10" t="n">
-        <v>540</v>
+        <v>28</v>
       </c>
       <c r="AJ10" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL10" t="n">
         <v>26</v>
       </c>
-      <c r="AK10" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>75</v>
-      </c>
       <c r="AM10" t="n">
-        <v>500</v>
+        <v>44</v>
       </c>
       <c r="AN10" t="n">
-        <v>29</v>
+        <v>9.4</v>
       </c>
       <c r="AO10" t="n">
-        <v>700</v>
+        <v>14</v>
       </c>
       <c r="AP10" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AQ10" t="n">
-        <v>6.2</v>
+        <v>19.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>5.1</v>
+        <v>20</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.6</v>
+        <v>8.6</v>
       </c>
       <c r="AT10" t="n">
-        <v>5.2</v>
+        <v>17</v>
       </c>
       <c r="AU10" t="n">
-        <v>5.8</v>
+        <v>9.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="AW10" t="n">
-        <v>5.5</v>
+        <v>7.4</v>
       </c>
       <c r="AX10" t="n">
-        <v>7.6</v>
+        <v>18.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AZ10" t="n">
-        <v>4.8</v>
+        <v>10</v>
       </c>
       <c r="BA10" t="n">
-        <v>5.5</v>
+        <v>20</v>
       </c>
       <c r="BB10" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="BC10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BD10" t="n">
         <v>21</v>
       </c>
-      <c r="BD10" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BE10" t="n">
-        <v>5.6</v>
+        <v>34</v>
       </c>
       <c r="BF10" t="n">
-        <v>19.5</v>
+        <v>7.8</v>
       </c>
       <c r="BG10" t="n">
-        <v>5.6</v>
+        <v>12</v>
       </c>
       <c r="BH10" t="n">
-        <v>2.7</v>
+        <v>5.4</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.18</v>
+        <v>4.1</v>
       </c>
       <c r="BJ10" t="n">
-        <v>13</v>
+        <v>8.4</v>
       </c>
       <c r="BK10" t="n">
         <v>6</v>
@@ -3066,53 +3054,53 @@
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN10" t="n">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="BP10" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BQ10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>21</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>7</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BW10" t="n">
         <v>6.8</v>
       </c>
-      <c r="BR10" t="n">
-        <v>46</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>5</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW10" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BX10" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BY10" t="n">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="BZ10" t="n">
-        <v>50</v>
+        <v>12.5</v>
       </c>
       <c r="CA10" t="n">
-        <v>9.4</v>
+        <v>5.8</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-13 18:58:03</t>
+          <t>2026-07-13 22:40:56</t>
         </is>
       </c>
     </row>
@@ -3143,13 +3131,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="G11" t="n">
         <v>3.55</v>
       </c>
       <c r="H11" t="n">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="I11" t="n">
         <v>3.15</v>
@@ -3158,25 +3146,25 @@
         <v>2.68</v>
       </c>
       <c r="K11" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="L11" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="M11" t="n">
         <v>1.14</v>
       </c>
       <c r="N11" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="O11" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="P11" t="n">
         <v>1.42</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="R11" t="n">
         <v>1.15</v>
@@ -3200,7 +3188,7 @@
         <v>8</v>
       </c>
       <c r="Y11" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z11" t="n">
         <v>18.5</v>
@@ -3209,13 +3197,13 @@
         <v>60</v>
       </c>
       <c r="AB11" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AC11" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AE11" t="n">
         <v>50</v>
@@ -3230,10 +3218,10 @@
         <v>27</v>
       </c>
       <c r="AI11" t="n">
-        <v>540</v>
+        <v>200</v>
       </c>
       <c r="AJ11" t="n">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AK11" t="n">
         <v>60</v>
@@ -3248,19 +3236,19 @@
         <v>95</v>
       </c>
       <c r="AO11" t="n">
-        <v>65</v>
+        <v>210</v>
       </c>
       <c r="AP11" t="n">
         <v>6.2</v>
       </c>
       <c r="AQ11" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="AR11" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AS11" t="n">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="AT11" t="n">
         <v>7</v>
@@ -3272,43 +3260,43 @@
         <v>10</v>
       </c>
       <c r="AW11" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="AX11" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AY11" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AZ11" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BA11" t="n">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="BB11" t="n">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="BC11" t="n">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="BD11" t="n">
-        <v>5.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE11" t="n">
-        <v>5.4</v>
+        <v>7.8</v>
       </c>
       <c r="BF11" t="n">
-        <v>5.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG11" t="n">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="BH11" t="n">
         <v>2.66</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="BJ11" t="n">
         <v>12.5</v>
@@ -3320,13 +3308,13 @@
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>2.06</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN11" t="n">
         <v>6.4</v>
       </c>
       <c r="BO11" t="n">
-        <v>3.85</v>
+        <v>5.1</v>
       </c>
       <c r="BP11" t="n">
         <v>34</v>
@@ -3338,35 +3326,35 @@
         <v>65</v>
       </c>
       <c r="BS11" t="n">
-        <v>2.02</v>
+        <v>8.4</v>
       </c>
       <c r="BT11" t="n">
         <v>5.9</v>
       </c>
       <c r="BU11" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="BV11" t="n">
         <v>29</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.95</v>
+        <v>7.2</v>
       </c>
       <c r="BX11" t="n">
         <v>60</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.02</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ11" t="n">
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>2.02</v>
+        <v>8.4</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-13 18:58:03</t>
+          <t>2026-07-13 22:40:56</t>
         </is>
       </c>
     </row>
@@ -3400,10 +3388,10 @@
         <v>2.06</v>
       </c>
       <c r="G12" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="H12" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="I12" t="n">
         <v>4.4</v>
@@ -3418,106 +3406,106 @@
         <v>1.45</v>
       </c>
       <c r="M12" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N12" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O12" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="P12" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="R12" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="S12" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="T12" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="U12" t="n">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="V12" t="n">
         <v>1.31</v>
       </c>
       <c r="W12" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="X12" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="Y12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Z12" t="n">
         <v>30</v>
       </c>
       <c r="AA12" t="n">
-        <v>110</v>
+        <v>900</v>
       </c>
       <c r="AB12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>160</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP12" t="n">
         <v>10</v>
       </c>
-      <c r="AC12" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>450</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>85</v>
-      </c>
-      <c r="AP12" t="n">
+      <c r="AQ12" t="n">
         <v>10.5</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>11.5</v>
       </c>
       <c r="AR12" t="n">
         <v>22</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.1</v>
+        <v>9.6</v>
       </c>
       <c r="AT12" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AU12" t="n">
         <v>6.8</v>
@@ -3526,55 +3514,55 @@
         <v>14.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AX12" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AY12" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ12" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BA12" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="BB12" t="n">
         <v>19</v>
       </c>
       <c r="BC12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BE12" t="n">
-        <v>5.2</v>
+        <v>9.6</v>
       </c>
       <c r="BF12" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="BH12" t="n">
         <v>3.2</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="BJ12" t="n">
         <v>10.5</v>
       </c>
       <c r="BK12" t="n">
-        <v>5.7</v>
+        <v>7.4</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BN12" t="n">
         <v>4.9</v>
@@ -3592,35 +3580,35 @@
         <v>34</v>
       </c>
       <c r="BS12" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BT12" t="n">
         <v>7.4</v>
       </c>
       <c r="BU12" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BV12" t="n">
         <v>38</v>
       </c>
       <c r="BW12" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="CA12" t="n">
         <v>9</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-13 18:58:03</t>
+          <t>2026-07-13 22:40:56</t>
         </is>
       </c>
     </row>
@@ -3651,100 +3639,100 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="G13" t="n">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="H13" t="n">
-        <v>2.76</v>
+        <v>3.05</v>
       </c>
       <c r="I13" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="J13" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="K13" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L13" t="n">
-        <v>1.51</v>
+        <v>1.67</v>
       </c>
       <c r="M13" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N13" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="O13" t="n">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="P13" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.46</v>
+        <v>3.05</v>
       </c>
       <c r="R13" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="S13" t="n">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="T13" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="U13" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="V13" t="n">
         <v>1.4</v>
       </c>
       <c r="W13" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="X13" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y13" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Z13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA13" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AB13" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC13" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AE13" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>330</v>
+      </c>
+      <c r="AJ13" t="n">
         <v>55</v>
       </c>
-      <c r="AF13" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>60</v>
-      </c>
       <c r="AK13" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AL13" t="n">
         <v>80</v>
@@ -3756,125 +3744,125 @@
         <v>60</v>
       </c>
       <c r="AO13" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AP13" t="n">
-        <v>3.85</v>
+        <v>6</v>
       </c>
       <c r="AQ13" t="n">
-        <v>4.4</v>
+        <v>7.4</v>
       </c>
       <c r="AR13" t="n">
-        <v>4.9</v>
+        <v>17.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.7</v>
+        <v>20</v>
       </c>
       <c r="AT13" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="AU13" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="AV13" t="n">
-        <v>4.5</v>
+        <v>13</v>
       </c>
       <c r="AW13" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX13" t="n">
-        <v>4.7</v>
+        <v>12.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>4.4</v>
+        <v>10</v>
       </c>
       <c r="AZ13" t="n">
-        <v>5</v>
+        <v>18.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="BB13" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BC13" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="BD13" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="BE13" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BF13" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BG13" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="BH13" t="n">
-        <v>2.86</v>
+        <v>2.68</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="BJ13" t="n">
         <v>12.5</v>
       </c>
       <c r="BK13" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BN13" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BP13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BQ13" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BR13" t="n">
         <v>55</v>
       </c>
       <c r="BS13" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT13" t="n">
         <v>6.4</v>
       </c>
       <c r="BU13" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BV13" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BW13" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BX13" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BZ13" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="CA13" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-13 18:58:03</t>
+          <t>2026-07-13 22:40:56</t>
         </is>
       </c>
     </row>
@@ -3905,112 +3893,112 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.72</v>
+        <v>3.2</v>
       </c>
       <c r="G14" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="H14" t="n">
         <v>2.68</v>
       </c>
       <c r="I14" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="J14" t="n">
-        <v>2.66</v>
+        <v>2.46</v>
       </c>
       <c r="K14" t="n">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="L14" t="n">
-        <v>1.54</v>
+        <v>1.68</v>
       </c>
       <c r="M14" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N14" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="O14" t="n">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="P14" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="R14" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="S14" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="T14" t="n">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="U14" t="n">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="W14" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="X14" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="Y14" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z14" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AA14" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AB14" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE14" t="n">
         <v>55</v>
       </c>
       <c r="AF14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG14" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AI14" t="n">
-        <v>90</v>
+        <v>460</v>
       </c>
       <c r="AJ14" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AK14" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AL14" t="n">
-        <v>90</v>
+        <v>460</v>
       </c>
       <c r="AM14" t="n">
         <v>500</v>
       </c>
       <c r="AN14" t="n">
+        <v>500</v>
+      </c>
+      <c r="AO14" t="n">
         <v>180</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>70</v>
       </c>
       <c r="AP14" t="n">
         <v>3.85</v>
@@ -4019,10 +4007,10 @@
         <v>4.4</v>
       </c>
       <c r="AR14" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AS14" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AT14" t="n">
         <v>4.4</v>
@@ -4031,104 +4019,104 @@
         <v>4.2</v>
       </c>
       <c r="AV14" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AW14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AZ14" t="n">
         <v>5.9</v>
       </c>
-      <c r="AX14" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BA14" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BB14" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BC14" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="BD14" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BE14" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BF14" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BG14" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BH14" t="n">
-        <v>2.76</v>
+        <v>2.62</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="BJ14" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN14" t="n">
         <v>6.4</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BP14" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BQ14" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BR14" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT14" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="BU14" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BV14" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BX14" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ14" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="CA14" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-13 18:58:03</t>
+          <t>2026-07-13 22:40:56</t>
         </is>
       </c>
     </row>
@@ -4159,230 +4147,230 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.94</v>
+        <v>2.28</v>
       </c>
       <c r="G15" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="H15" t="n">
-        <v>2.74</v>
+        <v>3.95</v>
       </c>
       <c r="I15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="K15" t="n">
         <v>3.25</v>
       </c>
-      <c r="J15" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="K15" t="n">
-        <v>3.1</v>
-      </c>
       <c r="L15" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="M15" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="N15" t="n">
-        <v>2.02</v>
+        <v>2.44</v>
       </c>
       <c r="O15" t="n">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="P15" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="R15" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="S15" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="T15" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="U15" t="n">
         <v>1.62</v>
       </c>
       <c r="V15" t="n">
-        <v>1.45</v>
+        <v>1.26</v>
       </c>
       <c r="W15" t="n">
-        <v>1.4</v>
+        <v>1.69</v>
       </c>
       <c r="X15" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y15" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC15" t="n">
         <v>8</v>
       </c>
-      <c r="Z15" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AA15" t="n">
+      <c r="AD15" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE15" t="n">
         <v>500</v>
       </c>
-      <c r="AB15" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>75</v>
-      </c>
       <c r="AF15" t="n">
-        <v>21</v>
+        <v>13.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>17</v>
+        <v>13.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="AI15" t="n">
         <v>500</v>
       </c>
       <c r="AJ15" t="n">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AK15" t="n">
-        <v>290</v>
+        <v>38</v>
       </c>
       <c r="AL15" t="n">
-        <v>500</v>
+        <v>240</v>
       </c>
       <c r="AM15" t="n">
         <v>500</v>
       </c>
       <c r="AN15" t="n">
-        <v>500</v>
+        <v>48</v>
       </c>
       <c r="AO15" t="n">
         <v>500</v>
       </c>
       <c r="AP15" t="n">
-        <v>3.9</v>
+        <v>5.6</v>
       </c>
       <c r="AQ15" t="n">
         <v>4.4</v>
       </c>
       <c r="AR15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BB15" t="n">
         <v>5.8</v>
       </c>
-      <c r="AS15" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AV15" t="n">
+      <c r="BC15" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>21</v>
+      </c>
+      <c r="BQ15" t="n">
         <v>5.6</v>
       </c>
-      <c r="AW15" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>8</v>
-      </c>
-      <c r="BE15" t="n">
+      <c r="BR15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BT15" t="n">
         <v>8.4</v>
       </c>
-      <c r="BF15" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>13</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>36</v>
-      </c>
-      <c r="BQ15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT15" t="n">
-        <v>6</v>
-      </c>
       <c r="BU15" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-13 18:58:03</t>
+          <t>2026-07-13 22:40:56</t>
         </is>
       </c>
     </row>
@@ -4413,230 +4401,230 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.76</v>
+        <v>3.65</v>
       </c>
       <c r="G16" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="H16" t="n">
-        <v>2.6</v>
+        <v>2.24</v>
       </c>
       <c r="I16" t="n">
-        <v>3.25</v>
+        <v>2.48</v>
       </c>
       <c r="J16" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="K16" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L16" t="n">
-        <v>1.49</v>
+        <v>1.64</v>
       </c>
       <c r="M16" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N16" t="n">
-        <v>2.26</v>
+        <v>2.44</v>
       </c>
       <c r="O16" t="n">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="P16" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.5</v>
+        <v>2.94</v>
       </c>
       <c r="R16" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="S16" t="n">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
       <c r="T16" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="U16" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="V16" t="n">
-        <v>1.44</v>
+        <v>1.68</v>
       </c>
       <c r="W16" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="X16" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="Y16" t="n">
-        <v>9.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="Z16" t="n">
-        <v>19.5</v>
+        <v>14.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="AB16" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD16" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AE16" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AF16" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="AG16" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AH16" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AI16" t="n">
-        <v>540</v>
+        <v>170</v>
       </c>
       <c r="AJ16" t="n">
-        <v>420</v>
+        <v>900</v>
       </c>
       <c r="AK16" t="n">
+        <v>500</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>140</v>
+      </c>
+      <c r="AO16" t="n">
         <v>55</v>
       </c>
-      <c r="AL16" t="n">
-        <v>540</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>230</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>70</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>60</v>
-      </c>
       <c r="AP16" t="n">
-        <v>3.7</v>
+        <v>6</v>
       </c>
       <c r="AQ16" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="AR16" t="n">
-        <v>4.5</v>
+        <v>10.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="AT16" t="n">
-        <v>4.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU16" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="AV16" t="n">
-        <v>4.3</v>
+        <v>9</v>
       </c>
       <c r="AW16" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="AX16" t="n">
-        <v>4.7</v>
+        <v>21</v>
       </c>
       <c r="AY16" t="n">
-        <v>4.3</v>
+        <v>14.5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>4.8</v>
+        <v>20</v>
       </c>
       <c r="BA16" t="n">
         <v>5.5</v>
       </c>
       <c r="BB16" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BC16" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BE16" t="n">
         <v>5.8</v>
       </c>
       <c r="BF16" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BG16" t="n">
+        <v>30</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>13</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>7</v>
+      </c>
+      <c r="BT16" t="n">
         <v>5.4</v>
       </c>
-      <c r="BH16" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>32</v>
-      </c>
-      <c r="BQ16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT16" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BU16" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BV16" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BZ16" t="n">
         <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-13 18:58:03</t>
+          <t>2026-07-13 22:40:56</t>
         </is>
       </c>
     </row>
@@ -4667,22 +4655,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.2</v>
+        <v>3.65</v>
       </c>
       <c r="G17" t="n">
         <v>1000</v>
       </c>
       <c r="H17" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="I17" t="n">
-        <v>1000</v>
+        <v>1.81</v>
       </c>
       <c r="J17" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="K17" t="n">
-        <v>500</v>
+        <v>7.6</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
@@ -4691,34 +4679,34 @@
         <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>1.34</v>
+        <v>1.02</v>
       </c>
       <c r="O17" t="n">
         <v>1.12</v>
       </c>
       <c r="P17" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="Q17" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V17" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="W17" t="n">
         <v>1.12</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.21</v>
       </c>
       <c r="X17" t="n">
         <v>500</v>
@@ -4766,7 +4754,7 @@
         <v>500</v>
       </c>
       <c r="AM17" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN17" t="n">
         <v>500</v>
@@ -4775,58 +4763,58 @@
         <v>500</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.07</v>
+        <v>1.21</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.07</v>
+        <v>1.21</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.07</v>
+        <v>1.21</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.07</v>
+        <v>1.21</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.05</v>
+        <v>1.19</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.07</v>
+        <v>1.21</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.07</v>
+        <v>1.21</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.07</v>
+        <v>1.21</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.07</v>
+        <v>1.21</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.07</v>
+        <v>1.55</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.07</v>
+        <v>1.55</v>
       </c>
       <c r="BH17" t="n">
         <v>1000</v>
@@ -4890,14 +4878,14 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-13 18:58:03</t>
+          <t>2026-07-13 22:40:56</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4912,246 +4900,246 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Blooming Santa Cruz</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Delfin</t>
+          <t>CD Gualberto Villarroel</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.1</v>
+        <v>1.21</v>
       </c>
       <c r="G18" t="n">
-        <v>3.3</v>
+        <v>1.59</v>
       </c>
       <c r="H18" t="n">
-        <v>2.84</v>
+        <v>2.7</v>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>1000</v>
       </c>
       <c r="J18" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="K18" t="n">
-        <v>2.94</v>
+        <v>1000</v>
       </c>
       <c r="L18" t="n">
-        <v>1.66</v>
+        <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>2.28</v>
+        <v>1.36</v>
       </c>
       <c r="O18" t="n">
-        <v>1.64</v>
+        <v>1.14</v>
       </c>
       <c r="P18" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.96</v>
+        <v>1.14</v>
       </c>
       <c r="R18" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="S18" t="n">
-        <v>6.8</v>
+        <v>1.14</v>
       </c>
       <c r="T18" t="n">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="U18" t="n">
-        <v>1.68</v>
+        <v>1.01</v>
       </c>
       <c r="V18" t="n">
-        <v>1.5</v>
+        <v>1.11</v>
       </c>
       <c r="W18" t="n">
-        <v>1.44</v>
+        <v>2.62</v>
       </c>
       <c r="X18" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="Y18" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="Z18" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AA18" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AC18" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AD18" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AE18" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AG18" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AH18" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AI18" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AK18" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AL18" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AM18" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AO18" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AQ18" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AR18" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AS18" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT18" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU18" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV18" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AW18" t="n">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="AX18" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AY18" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AZ18" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BA18" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BB18" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BC18" t="n">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BD18" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BE18" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BF18" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BG18" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BH18" t="n">
-        <v>2.58</v>
+        <v>1000</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="BJ18" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK18" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN18" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BO18" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BP18" t="n">
         <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BT18" t="n">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="BU18" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BV18" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BZ18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA18" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-13 18:58:03</t>
+          <t>2026-07-13 22:40:56</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5161,244 +5149,244 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Blooming Santa Cruz</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CD Gualberto Villarroel</t>
+          <t>Delfin</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.21</v>
+        <v>3.15</v>
       </c>
       <c r="G19" t="n">
-        <v>1.6</v>
+        <v>3.25</v>
       </c>
       <c r="H19" t="n">
-        <v>1.04</v>
+        <v>2.86</v>
       </c>
       <c r="I19" t="n">
-        <v>1000</v>
+        <v>2.98</v>
       </c>
       <c r="J19" t="n">
-        <v>1.03</v>
+        <v>2.88</v>
       </c>
       <c r="K19" t="n">
-        <v>1000</v>
+        <v>2.94</v>
       </c>
       <c r="L19" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="M19" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="N19" t="n">
-        <v>1.34</v>
+        <v>2.34</v>
       </c>
       <c r="O19" t="n">
-        <v>1.14</v>
+        <v>1.64</v>
       </c>
       <c r="P19" t="n">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.14</v>
+        <v>3.1</v>
       </c>
       <c r="R19" t="n">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="S19" t="n">
-        <v>2.12</v>
+        <v>6.8</v>
       </c>
       <c r="T19" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="U19" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="V19" t="n">
-        <v>1.11</v>
+        <v>1.51</v>
       </c>
       <c r="W19" t="n">
-        <v>2.44</v>
+        <v>1.44</v>
       </c>
       <c r="X19" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="Y19" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="Z19" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AA19" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB19" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC19" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE19" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF19" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AG19" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI19" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK19" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL19" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AM19" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AN19" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AO19" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.01</v>
+        <v>46</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BH19" t="n">
-        <v>1000</v>
+        <v>2.58</v>
       </c>
       <c r="BI19" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="BJ19" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK19" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BN19" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BP19" t="n">
         <v>1000</v>
       </c>
       <c r="BQ19" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR19" t="n">
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BT19" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BU19" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BV19" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW19" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BZ19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA19" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-13 18:58:03</t>
+          <t>2026-07-13 22:40:56</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-14.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,402 +429,402 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>League</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Home</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Away</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Odd_H_Back</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Odd_H_Lay</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Odd_A_Back</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Odd_A_Lay</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Odd_D_Back</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Odd_D_Lay</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Odd_Over05_HT_Back</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Odd_Over05_FT_Back</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Odd_Under15_FT_Back</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Odd_Over15_FT_Back</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Odd_Under25_FT_Back</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Odd_Over25_FT_Back</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Odd_Under35_FT_Back</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Odd_Over35_FT_Back</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Odd_BTTS_Yes_Back</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Odd_BTTS_No_Back</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Double_Chance_Home_or_Draw_Back</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Double_Chance_Draw_or_Away_Back</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_0x0_Lay</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_0x1_Lay</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_0x2_Lay</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_0x3_Lay</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_1x0_Lay</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_1x1_Lay</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_1x2_Lay</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_1x3_Lay</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_2x0_Lay</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_2x1_Lay</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_2x2_Lay</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_2x3_Lay</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_3x0_Lay</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_3x1_Lay</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_3x2_Lay</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_3x3_Lay</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_Goleada_H_Lay</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_Goleada_A_Lay</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_0x0_Back</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_0x1_Back</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_0x2_Back</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_0x3_Back</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_1x0_Back</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_1x1_Back</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_1x2_Back</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_1x3_Back</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_2x0_Back</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_2x1_Back</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_2x2_Back</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_2x3_Back</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_3x0_Back</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_3x1_Back</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_3x2_Back</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_3x3_Back</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_Goleada_H_Back</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_Goleada_A_Back</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Odd_HTS_0x0_Lay</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>Odd_HTS_0x0_Back</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>Odd_HTS_1x1_Lay</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>Odd_HTS_1x1_Back</t>
         </is>
       </c>
-      <c r="BL1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Odd_HTS_2x2_Lay</t>
         </is>
       </c>
-      <c r="BM1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>Odd_HTS_2x2_Back</t>
         </is>
       </c>
-      <c r="BN1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>Odd_HTS_1x0_Lay</t>
         </is>
       </c>
-      <c r="BO1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>Odd_HTS_1x0_Back</t>
         </is>
       </c>
-      <c r="BP1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>Odd_HTS_2x0_Lay</t>
         </is>
       </c>
-      <c r="BQ1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>Odd_HTS_2x0_Back</t>
         </is>
       </c>
-      <c r="BR1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>Odd_HTS_2x1_Lay</t>
         </is>
       </c>
-      <c r="BS1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>Odd_HTS_2x1_Back</t>
         </is>
       </c>
-      <c r="BT1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>Odd_HTS_0x1_Lay</t>
         </is>
       </c>
-      <c r="BU1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>Odd_HTS_0x1_Back</t>
         </is>
       </c>
-      <c r="BV1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>Odd_HTS_0x2_Lay</t>
         </is>
       </c>
-      <c r="BW1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>Odd_HTS_0x2_Back</t>
         </is>
       </c>
-      <c r="BX1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>Odd_HTS_1x2_Lay</t>
         </is>
       </c>
-      <c r="BY1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>Odd_HTS_1x2_Back</t>
         </is>
       </c>
-      <c r="BZ1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>Odd_HTS_Outros_Lay</t>
         </is>
       </c>
-      <c r="CA1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>Odd_HTS_Outros_Back</t>
         </is>
       </c>
-      <c r="CB1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>SnapshotTS</t>
         </is>
@@ -845,148 +857,148 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="G2" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="H2" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="I2" t="n">
         <v>7</v>
       </c>
       <c r="J2" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="K2" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="L2" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="M2" t="n">
         <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="O2" t="n">
         <v>1.13</v>
       </c>
       <c r="P2" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="R2" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="S2" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="U2" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="V2" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W2" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="X2" t="n">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="Y2" t="n">
-        <v>100</v>
+        <v>44</v>
       </c>
       <c r="Z2" t="n">
-        <v>450</v>
+        <v>160</v>
       </c>
       <c r="AA2" t="n">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="AB2" t="n">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="AC2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AE2" t="n">
-        <v>400</v>
+        <v>130</v>
       </c>
       <c r="AF2" t="n">
         <v>13</v>
       </c>
       <c r="AG2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH2" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI2" t="n">
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="AJ2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK2" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AL2" t="n">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="AM2" t="n">
-        <v>260</v>
+        <v>65</v>
       </c>
       <c r="AN2" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AO2" t="n">
         <v>170</v>
       </c>
       <c r="AP2" t="n">
-        <v>18.5</v>
+        <v>32</v>
       </c>
       <c r="AQ2" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AR2" t="n">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="AS2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AT2" t="n">
         <v>14</v>
       </c>
       <c r="AU2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AV2" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AW2" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="AX2" t="n">
         <v>11.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AZ2" t="n">
         <v>15.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="BB2" t="n">
         <v>14</v>
@@ -995,80 +1007,80 @@
         <v>12</v>
       </c>
       <c r="BD2" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="BE2" t="n">
         <v>28</v>
       </c>
       <c r="BF2" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="BG2" t="n">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="BH2" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="BI2" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="BJ2" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.8</v>
+        <v>7.6</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="BN2" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BP2" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.5</v>
+        <v>7.6</v>
       </c>
       <c r="BR2" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>8</v>
+        <v>2.26</v>
       </c>
       <c r="BT2" t="n">
-        <v>11</v>
+        <v>17.5</v>
       </c>
       <c r="BU2" t="n">
-        <v>6.2</v>
+        <v>9.4</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>10.5</v>
+        <v>2.26</v>
       </c>
       <c r="BZ2" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>5.8</v>
+        <v>2.26</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-13 22:40:56</t>
+          <t>2026-07-14 07:32:00</t>
         </is>
       </c>
     </row>
@@ -1099,64 +1111,64 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="G3" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="H3" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J3" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="K3" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="L3" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="M3" t="n">
         <v>1.02</v>
       </c>
       <c r="N3" t="n">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="O3" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="P3" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="R3" t="n">
-        <v>1.92</v>
+        <v>2.16</v>
       </c>
       <c r="S3" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="T3" t="n">
-        <v>1.43</v>
+        <v>1.2</v>
       </c>
       <c r="U3" t="n">
-        <v>2.88</v>
+        <v>2.14</v>
       </c>
       <c r="V3" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W3" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="X3" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="Y3" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="Z3" t="n">
         <v>140</v>
@@ -1165,112 +1177,112 @@
         <v>500</v>
       </c>
       <c r="AB3" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AC3" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AD3" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AE3" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="AF3" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AG3" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AH3" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AI3" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AJ3" t="n">
-        <v>24</v>
+        <v>120</v>
       </c>
       <c r="AK3" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AL3" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="AM3" t="n">
-        <v>200</v>
+        <v>580</v>
       </c>
       <c r="AN3" t="n">
-        <v>6.2</v>
+        <v>29</v>
       </c>
       <c r="AO3" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
+        <v>29</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC3" t="n">
         <v>7.6</v>
       </c>
-      <c r="AQ3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>16</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>19</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>14</v>
-      </c>
       <c r="BD3" t="n">
-        <v>18</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE3" t="n">
-        <v>7.6</v>
+        <v>1.72</v>
       </c>
       <c r="BF3" t="n">
-        <v>5.1</v>
+        <v>1.78</v>
       </c>
       <c r="BG3" t="n">
-        <v>17</v>
+        <v>1.74</v>
       </c>
       <c r="BH3" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BI3" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BJ3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BK3" t="n">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
@@ -1279,50 +1291,50 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BN3" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BP3" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>8.4</v>
+        <v>5.3</v>
       </c>
       <c r="BR3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BS3" t="n">
         <v>6.2</v>
       </c>
       <c r="BT3" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BU3" t="n">
-        <v>6.2</v>
+        <v>4.7</v>
       </c>
       <c r="BV3" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="BW3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>26</v>
+      </c>
+      <c r="BY3" t="n">
         <v>7</v>
       </c>
-      <c r="BX3" t="n">
-        <v>28</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BZ3" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="CA3" t="n">
-        <v>7.2</v>
+        <v>4.8</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-13 22:40:56</t>
+          <t>2026-07-14 07:32:00</t>
         </is>
       </c>
     </row>
@@ -1344,76 +1356,76 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CS Dock Sud</t>
+          <t>Camioneros</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Uai Urquiza</t>
+          <t>CSD Liniers de Ciudad Evita</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="G4" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="H4" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="I4" t="n">
-        <v>5.4</v>
+        <v>7.2</v>
       </c>
       <c r="J4" t="n">
-        <v>2.58</v>
+        <v>2.88</v>
       </c>
       <c r="K4" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="L4" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="M4" t="n">
         <v>1.13</v>
       </c>
       <c r="N4" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="O4" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="P4" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="R4" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="S4" t="n">
-        <v>2.92</v>
+        <v>5.8</v>
       </c>
       <c r="T4" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="U4" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="V4" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W4" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="X4" t="n">
         <v>970</v>
       </c>
       <c r="Y4" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AA4" t="n">
         <v>900</v>
@@ -1425,10 +1437,10 @@
         <v>42</v>
       </c>
       <c r="AD4" t="n">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="AE4" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="AF4" t="n">
         <v>970</v>
@@ -1437,146 +1449,146 @@
         <v>970</v>
       </c>
       <c r="AH4" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AI4" t="n">
-        <v>540</v>
+        <v>700</v>
       </c>
       <c r="AJ4" t="n">
         <v>900</v>
       </c>
       <c r="AK4" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AL4" t="n">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="AM4" t="n">
         <v>500</v>
       </c>
       <c r="AN4" t="n">
-        <v>90</v>
+        <v>600</v>
       </c>
       <c r="AO4" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.56</v>
+        <v>2.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.63</v>
+        <v>3.1</v>
       </c>
       <c r="AU4" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.56</v>
+        <v>5.5</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.57</v>
+        <v>5.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.69</v>
+        <v>1.78</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.69</v>
+        <v>1.78</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.66</v>
+        <v>1.78</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="BH4" t="n">
-        <v>2.68</v>
+        <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.22</v>
+        <v>1.01</v>
       </c>
       <c r="BJ4" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BN4" t="n">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BP4" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BR4" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BT4" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-13 22:40:56</t>
+          <t>2026-07-14 07:32:00</t>
         </is>
       </c>
     </row>
@@ -1598,175 +1610,175 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Flandria</t>
+          <t>Argentino de Quilmes</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Argentino de Merlo</t>
+          <t>Arsenal de Sarandi</t>
         </is>
       </c>
       <c r="F5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="G5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>4</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N5" t="n">
         <v>2.56</v>
       </c>
-      <c r="G5" t="n">
+      <c r="O5" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="V5" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X5" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>42</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>110</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>65</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>500</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AQ5" t="n">
         <v>2.86</v>
       </c>
-      <c r="H5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="I5" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="S5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W5" t="n">
+      <c r="AR5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BB5" t="n">
         <v>1.54</v>
       </c>
-      <c r="X5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>23</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>250</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>160</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>340</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>120</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>48</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>210</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>390</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>500</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>7</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>9</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>6</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BC5" t="n">
-        <v>8.4</v>
+        <v>1.54</v>
       </c>
       <c r="BD5" t="n">
-        <v>9.199999999999999</v>
+        <v>1.54</v>
       </c>
       <c r="BE5" t="n">
-        <v>9.800000000000001</v>
+        <v>1.54</v>
       </c>
       <c r="BF5" t="n">
-        <v>8.800000000000001</v>
+        <v>1.55</v>
       </c>
       <c r="BG5" t="n">
-        <v>9.199999999999999</v>
+        <v>1.55</v>
       </c>
       <c r="BH5" t="n">
         <v>1000</v>
@@ -1830,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-13 22:40:56</t>
+          <t>2026-07-14 07:32:00</t>
         </is>
       </c>
     </row>
@@ -1852,246 +1864,246 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Sportivo Italiano</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Villa San Carlos</t>
+          <t>Excursionistas</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.89</v>
+        <v>3.45</v>
       </c>
       <c r="G6" t="n">
-        <v>2.08</v>
+        <v>4.2</v>
       </c>
       <c r="H6" t="n">
-        <v>4.9</v>
+        <v>2.26</v>
       </c>
       <c r="I6" t="n">
-        <v>5.9</v>
+        <v>2.5</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="K6" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L6" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="M6" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="N6" t="n">
-        <v>2.46</v>
+        <v>2.68</v>
       </c>
       <c r="O6" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="P6" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.86</v>
+        <v>2.56</v>
       </c>
       <c r="R6" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="S6" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="T6" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>1.63</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>1.2</v>
+        <v>1.67</v>
       </c>
       <c r="W6" t="n">
-        <v>1.94</v>
+        <v>1.33</v>
       </c>
       <c r="X6" t="n">
-        <v>8.4</v>
+        <v>970</v>
       </c>
       <c r="Y6" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="Z6" t="n">
-        <v>42</v>
+        <v>970</v>
       </c>
       <c r="AA6" t="n">
         <v>900</v>
       </c>
       <c r="AB6" t="n">
-        <v>6.4</v>
+        <v>970</v>
       </c>
       <c r="AC6" t="n">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="AD6" t="n">
-        <v>25</v>
+        <v>970</v>
       </c>
       <c r="AE6" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="AF6" t="n">
-        <v>11</v>
+        <v>120</v>
       </c>
       <c r="AG6" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AH6" t="n">
-        <v>30</v>
+        <v>85</v>
       </c>
       <c r="AI6" t="n">
-        <v>700</v>
+        <v>450</v>
       </c>
       <c r="AJ6" t="n">
-        <v>26</v>
+        <v>900</v>
       </c>
       <c r="AK6" t="n">
-        <v>32</v>
+        <v>160</v>
       </c>
       <c r="AL6" t="n">
-        <v>75</v>
+        <v>540</v>
       </c>
       <c r="AM6" t="n">
         <v>500</v>
       </c>
       <c r="AN6" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="AP6" t="n">
-        <v>7</v>
+        <v>4.4</v>
       </c>
       <c r="AQ6" t="n">
-        <v>10.5</v>
+        <v>3.4</v>
       </c>
       <c r="AR6" t="n">
-        <v>7.4</v>
+        <v>5.8</v>
       </c>
       <c r="AS6" t="n">
-        <v>8.6</v>
+        <v>1.69</v>
       </c>
       <c r="AT6" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.6</v>
+        <v>4.4</v>
       </c>
       <c r="AV6" t="n">
-        <v>19.5</v>
+        <v>5.3</v>
       </c>
       <c r="AW6" t="n">
-        <v>8.4</v>
+        <v>1.68</v>
       </c>
       <c r="AX6" t="n">
-        <v>8.800000000000001</v>
+        <v>1.7</v>
       </c>
       <c r="AY6" t="n">
-        <v>9.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AZ6" t="n">
-        <v>20</v>
+        <v>1.66</v>
       </c>
       <c r="BA6" t="n">
-        <v>8.4</v>
+        <v>1.71</v>
       </c>
       <c r="BB6" t="n">
-        <v>20</v>
+        <v>1.72</v>
       </c>
       <c r="BC6" t="n">
-        <v>14.5</v>
+        <v>1.71</v>
       </c>
       <c r="BD6" t="n">
-        <v>8</v>
+        <v>1.71</v>
       </c>
       <c r="BE6" t="n">
-        <v>8.800000000000001</v>
+        <v>1.72</v>
       </c>
       <c r="BF6" t="n">
-        <v>6.8</v>
+        <v>1.73</v>
       </c>
       <c r="BG6" t="n">
-        <v>8.6</v>
+        <v>1.69</v>
       </c>
       <c r="BH6" t="n">
-        <v>2.7</v>
+        <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.18</v>
+        <v>1.01</v>
       </c>
       <c r="BJ6" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BN6" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="BP6" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BR6" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BT6" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BV6" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-13 22:40:56</t>
+          <t>2026-07-14 07:32:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2106,239 +2118,239 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Grotta</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Excursionistas</t>
+          <t>Grindavik</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.6</v>
+        <v>2.24</v>
       </c>
       <c r="G7" t="n">
-        <v>4.3</v>
+        <v>2.32</v>
       </c>
       <c r="H7" t="n">
-        <v>2.24</v>
+        <v>2.96</v>
       </c>
       <c r="I7" t="n">
-        <v>2.5</v>
+        <v>3.15</v>
       </c>
       <c r="J7" t="n">
-        <v>2.86</v>
+        <v>4.2</v>
       </c>
       <c r="K7" t="n">
-        <v>3.35</v>
+        <v>4.6</v>
       </c>
       <c r="L7" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>70</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>90</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>470</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>60</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>160</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>220</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>970</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BF7" t="n">
         <v>1.55</v>
       </c>
-      <c r="M7" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N7" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S7" t="n">
-        <v>5</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="X7" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>38</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>36</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>28</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>18</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>250</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>70</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>200</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>110</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>36</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>24</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>23</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>21</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>28</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>28</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>7</v>
-      </c>
       <c r="BG7" t="n">
-        <v>6.2</v>
+        <v>1.55</v>
       </c>
       <c r="BH7" t="n">
-        <v>2.88</v>
+        <v>1000</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.44</v>
+        <v>1.01</v>
       </c>
       <c r="BJ7" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BN7" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BP7" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BR7" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BT7" t="n">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="BV7" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BX7" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-13 22:40:56</t>
+          <t>2026-07-14 07:32:00</t>
         </is>
       </c>
     </row>
@@ -2360,239 +2372,239 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Argentino de Quilmes</t>
+          <t>Flandria</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandi</t>
+          <t>Argentino de Merlo</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.85</v>
+        <v>2.4</v>
       </c>
       <c r="G8" t="n">
-        <v>4.6</v>
+        <v>2.7</v>
       </c>
       <c r="H8" t="n">
-        <v>2.18</v>
+        <v>3.3</v>
       </c>
       <c r="I8" t="n">
-        <v>2.4</v>
+        <v>3.9</v>
       </c>
       <c r="J8" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="K8" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="L8" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="M8" t="n">
         <v>1.13</v>
       </c>
       <c r="N8" t="n">
-        <v>2.56</v>
+        <v>2.44</v>
       </c>
       <c r="O8" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="P8" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.68</v>
+        <v>2.82</v>
       </c>
       <c r="R8" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="S8" t="n">
         <v>5.7</v>
       </c>
       <c r="T8" t="n">
-        <v>2.18</v>
+        <v>1.75</v>
       </c>
       <c r="U8" t="n">
-        <v>1.71</v>
+        <v>1.38</v>
       </c>
       <c r="V8" t="n">
-        <v>1.72</v>
+        <v>1.35</v>
       </c>
       <c r="W8" t="n">
-        <v>1.28</v>
+        <v>1.6</v>
       </c>
       <c r="X8" t="n">
-        <v>8.4</v>
+        <v>500</v>
       </c>
       <c r="Y8" t="n">
-        <v>7.2</v>
+        <v>970</v>
       </c>
       <c r="Z8" t="n">
-        <v>13.5</v>
+        <v>500</v>
       </c>
       <c r="AA8" t="n">
-        <v>38</v>
+        <v>500</v>
       </c>
       <c r="AB8" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AC8" t="n">
+        <v>42</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>500</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>500</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>500</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AR8" t="n">
         <v>7.6</v>
       </c>
-      <c r="AD8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>42</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>65</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>160</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>440</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>540</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>500</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>44</v>
-      </c>
-      <c r="AP8" t="n">
+      <c r="AS8" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AX8" t="n">
         <v>7</v>
       </c>
-      <c r="AQ8" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>24</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU8" t="n">
+      <c r="AY8" t="n">
         <v>6.2</v>
       </c>
-      <c r="AV8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>24</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>15.5</v>
-      </c>
       <c r="AZ8" t="n">
-        <v>20</v>
+        <v>1.65</v>
       </c>
       <c r="BA8" t="n">
-        <v>28</v>
+        <v>1.67</v>
       </c>
       <c r="BB8" t="n">
-        <v>9</v>
+        <v>1.66</v>
       </c>
       <c r="BC8" t="n">
-        <v>8.6</v>
+        <v>1.66</v>
       </c>
       <c r="BD8" t="n">
-        <v>9</v>
+        <v>1.67</v>
       </c>
       <c r="BE8" t="n">
-        <v>9.4</v>
+        <v>1.67</v>
       </c>
       <c r="BF8" t="n">
-        <v>9.199999999999999</v>
+        <v>1.68</v>
       </c>
       <c r="BG8" t="n">
-        <v>24</v>
+        <v>1.68</v>
       </c>
       <c r="BH8" t="n">
-        <v>2.72</v>
+        <v>1000</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.38</v>
+        <v>1.01</v>
       </c>
       <c r="BJ8" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BN8" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BO8" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BP8" t="n">
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BT8" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BV8" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-13 22:40:56</t>
+          <t>2026-07-14 07:32:00</t>
         </is>
       </c>
     </row>
@@ -2614,246 +2626,246 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Camioneros</t>
+          <t>CS Dock Sud</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CSD Liniers de Ciudad Evita</t>
+          <t>Uai Urquiza</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.08</v>
+        <v>1.85</v>
       </c>
       <c r="G9" t="n">
-        <v>2.28</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="I9" t="n">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="J9" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="K9" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="L9" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="M9" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="N9" t="n">
-        <v>2.46</v>
+        <v>2.58</v>
       </c>
       <c r="O9" t="n">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="P9" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.88</v>
+        <v>2.68</v>
       </c>
       <c r="R9" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>2.72</v>
       </c>
       <c r="T9" t="n">
-        <v>2.24</v>
+        <v>1.11</v>
       </c>
       <c r="U9" t="n">
-        <v>1.65</v>
+        <v>1.11</v>
       </c>
       <c r="V9" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="W9" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="X9" t="n">
-        <v>8</v>
+        <v>970</v>
       </c>
       <c r="Y9" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="Z9" t="n">
-        <v>95</v>
+        <v>170</v>
       </c>
       <c r="AA9" t="n">
         <v>900</v>
       </c>
       <c r="AB9" t="n">
-        <v>6.8</v>
+        <v>970</v>
       </c>
       <c r="AC9" t="n">
-        <v>7.6</v>
+        <v>42</v>
       </c>
       <c r="AD9" t="n">
-        <v>22</v>
+        <v>120</v>
       </c>
       <c r="AE9" t="n">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="AF9" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AG9" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AH9" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AI9" t="n">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="AJ9" t="n">
-        <v>36</v>
+        <v>900</v>
       </c>
       <c r="AK9" t="n">
-        <v>65</v>
+        <v>110</v>
       </c>
       <c r="AL9" t="n">
-        <v>170</v>
+        <v>450</v>
       </c>
       <c r="AM9" t="n">
         <v>500</v>
       </c>
       <c r="AN9" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>6.6</v>
+        <v>4.2</v>
       </c>
       <c r="AQ9" t="n">
-        <v>9.6</v>
+        <v>5.7</v>
       </c>
       <c r="AR9" t="n">
-        <v>7.6</v>
+        <v>1.53</v>
       </c>
       <c r="AS9" t="n">
-        <v>9.199999999999999</v>
+        <v>1.54</v>
       </c>
       <c r="AT9" t="n">
-        <v>5.1</v>
+        <v>3</v>
       </c>
       <c r="AU9" t="n">
-        <v>6.2</v>
+        <v>4.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>15.5</v>
+        <v>1.52</v>
       </c>
       <c r="AW9" t="n">
-        <v>8.800000000000001</v>
+        <v>1.54</v>
       </c>
       <c r="AX9" t="n">
-        <v>9</v>
+        <v>5.6</v>
       </c>
       <c r="AY9" t="n">
-        <v>9.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="AZ9" t="n">
-        <v>7.2</v>
+        <v>1.51</v>
       </c>
       <c r="BA9" t="n">
-        <v>9</v>
+        <v>1.54</v>
       </c>
       <c r="BB9" t="n">
-        <v>7.4</v>
+        <v>2.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>7.6</v>
+        <v>1.51</v>
       </c>
       <c r="BD9" t="n">
-        <v>8.6</v>
+        <v>1.53</v>
       </c>
       <c r="BE9" t="n">
-        <v>9.4</v>
+        <v>1.54</v>
       </c>
       <c r="BF9" t="n">
-        <v>7.6</v>
+        <v>1.55</v>
       </c>
       <c r="BG9" t="n">
-        <v>9.4</v>
+        <v>1.55</v>
       </c>
       <c r="BH9" t="n">
-        <v>2.66</v>
+        <v>1000</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="BJ9" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN9" t="n">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BP9" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BR9" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BT9" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-13 22:40:56</t>
+          <t>2026-07-14 07:32:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2868,239 +2880,239 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Grotta</t>
+          <t>Sportivo Italiano</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Grindavik</t>
+          <t>Villa San Carlos</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.22</v>
+        <v>1.8</v>
       </c>
       <c r="G10" t="n">
-        <v>2.4</v>
+        <v>1.96</v>
       </c>
       <c r="H10" t="n">
-        <v>2.88</v>
+        <v>4.8</v>
       </c>
       <c r="I10" t="n">
-        <v>3.1</v>
+        <v>7.4</v>
       </c>
       <c r="J10" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="K10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="X10" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>120</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>42</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>70</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>110</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>700</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>110</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>460</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AU10" t="n">
         <v>4.4</v>
       </c>
-      <c r="L10" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N10" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="P10" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="X10" t="n">
-        <v>36</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>24</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>85</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>160</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>21</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>27</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>14</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>28</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>26</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>44</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>14</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>8</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>17</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>9.4</v>
-      </c>
       <c r="AV10" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BB10" t="n">
         <v>10</v>
       </c>
-      <c r="AW10" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>10</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>20</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>13</v>
-      </c>
       <c r="BC10" t="n">
-        <v>17.5</v>
+        <v>1.68</v>
       </c>
       <c r="BD10" t="n">
-        <v>21</v>
+        <v>1.71</v>
       </c>
       <c r="BE10" t="n">
-        <v>34</v>
+        <v>1.73</v>
       </c>
       <c r="BF10" t="n">
-        <v>7.8</v>
+        <v>1.73</v>
       </c>
       <c r="BG10" t="n">
-        <v>12</v>
+        <v>1.73</v>
       </c>
       <c r="BH10" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BI10" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BJ10" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BN10" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BO10" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BP10" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BR10" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BT10" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BU10" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BV10" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BX10" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BZ10" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-13 22:40:56</t>
+          <t>2026-07-14 07:32:00</t>
         </is>
       </c>
     </row>
@@ -3131,230 +3143,230 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="G11" t="n">
-        <v>3.55</v>
+        <v>4.4</v>
       </c>
       <c r="H11" t="n">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="I11" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="J11" t="n">
-        <v>2.68</v>
+        <v>2.46</v>
       </c>
       <c r="K11" t="n">
-        <v>3.15</v>
+        <v>2.7</v>
       </c>
       <c r="L11" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="M11" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="N11" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="O11" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="P11" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="Q11" t="n">
         <v>3.05</v>
       </c>
       <c r="R11" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="S11" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="T11" t="n">
-        <v>2.14</v>
+        <v>1.11</v>
       </c>
       <c r="U11" t="n">
-        <v>1.66</v>
+        <v>1.11</v>
       </c>
       <c r="V11" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="X11" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y11" t="n">
-        <v>8.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="Z11" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AA11" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AB11" t="n">
-        <v>9</v>
+        <v>970</v>
       </c>
       <c r="AC11" t="n">
-        <v>7.4</v>
+        <v>970</v>
       </c>
       <c r="AD11" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AE11" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AF11" t="n">
-        <v>22</v>
+        <v>500</v>
       </c>
       <c r="AG11" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AH11" t="n">
-        <v>27</v>
+        <v>500</v>
       </c>
       <c r="AI11" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="AJ11" t="n">
-        <v>170</v>
+        <v>500</v>
       </c>
       <c r="AK11" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AL11" t="n">
-        <v>540</v>
+        <v>500</v>
       </c>
       <c r="AM11" t="n">
         <v>500</v>
       </c>
       <c r="AN11" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>6.2</v>
+        <v>3.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>5.8</v>
+        <v>1.21</v>
       </c>
       <c r="AR11" t="n">
-        <v>14</v>
+        <v>1.2</v>
       </c>
       <c r="AS11" t="n">
-        <v>7</v>
+        <v>1.2</v>
       </c>
       <c r="AT11" t="n">
-        <v>7</v>
+        <v>4.4</v>
       </c>
       <c r="AU11" t="n">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="AV11" t="n">
-        <v>10</v>
+        <v>1.21</v>
       </c>
       <c r="AW11" t="n">
-        <v>6.8</v>
+        <v>1.2</v>
       </c>
       <c r="AX11" t="n">
-        <v>16.5</v>
+        <v>1.2</v>
       </c>
       <c r="AY11" t="n">
-        <v>12.5</v>
+        <v>1.19</v>
       </c>
       <c r="AZ11" t="n">
-        <v>20</v>
+        <v>1.21</v>
       </c>
       <c r="BA11" t="n">
-        <v>7.2</v>
+        <v>1.21</v>
       </c>
       <c r="BB11" t="n">
-        <v>7.2</v>
+        <v>1.21</v>
       </c>
       <c r="BC11" t="n">
-        <v>7</v>
+        <v>1.21</v>
       </c>
       <c r="BD11" t="n">
-        <v>7.4</v>
+        <v>1.21</v>
       </c>
       <c r="BE11" t="n">
-        <v>7.8</v>
+        <v>1.21</v>
       </c>
       <c r="BF11" t="n">
-        <v>7.4</v>
+        <v>1.55</v>
       </c>
       <c r="BG11" t="n">
-        <v>7</v>
+        <v>1.55</v>
       </c>
       <c r="BH11" t="n">
-        <v>2.66</v>
+        <v>1000</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="BJ11" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK11" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BN11" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BO11" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BP11" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BR11" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BT11" t="n">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="BU11" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BV11" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BX11" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BZ11" t="n">
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-13 22:40:56</t>
+          <t>2026-07-14 07:32:00</t>
         </is>
       </c>
     </row>
@@ -3385,230 +3397,230 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="G12" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="H12" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="I12" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J12" t="n">
         <v>3.35</v>
       </c>
       <c r="K12" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L12" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="M12" t="n">
         <v>1.09</v>
       </c>
       <c r="N12" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O12" t="n">
         <v>1.4</v>
       </c>
       <c r="P12" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R12" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="S12" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T12" t="n">
-        <v>1.92</v>
+        <v>1.57</v>
       </c>
       <c r="U12" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="V12" t="n">
         <v>1.31</v>
       </c>
       <c r="W12" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="X12" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="Z12" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="AA12" t="n">
         <v>900</v>
       </c>
       <c r="AB12" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC12" t="n">
-        <v>8.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AD12" t="n">
+        <v>90</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>370</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AG12" t="n">
         <v>18</v>
       </c>
-      <c r="AE12" t="n">
-        <v>70</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AH12" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="AI12" t="n">
-        <v>160</v>
+        <v>370</v>
       </c>
       <c r="AJ12" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="AK12" t="n">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="AL12" t="n">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="AM12" t="n">
         <v>580</v>
       </c>
       <c r="AN12" t="n">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="AO12" t="n">
-        <v>75</v>
+        <v>600</v>
       </c>
       <c r="AP12" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AQ12" t="n">
         <v>10</v>
       </c>
-      <c r="AQ12" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AR12" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AS12" t="n">
+        <v>55</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>34</v>
+      </c>
+      <c r="AX12" t="n">
         <v>9.6</v>
       </c>
-      <c r="AT12" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>42</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AY12" t="n">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ12" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="BB12" t="n">
         <v>19</v>
       </c>
       <c r="BC12" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="BD12" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BE12" t="n">
-        <v>9.6</v>
+        <v>2.82</v>
       </c>
       <c r="BF12" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="BH12" t="n">
-        <v>3.2</v>
+        <v>1000</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.8</v>
+        <v>1.01</v>
       </c>
       <c r="BJ12" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BN12" t="n">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="BO12" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BP12" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BR12" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BT12" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BU12" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BV12" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BZ12" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-13 22:40:56</t>
+          <t>2026-07-14 07:32:00</t>
         </is>
       </c>
     </row>
@@ -3639,230 +3651,230 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="G13" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="H13" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I13" t="n">
         <v>3.5</v>
       </c>
       <c r="J13" t="n">
-        <v>2.74</v>
+        <v>2.86</v>
       </c>
       <c r="K13" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="L13" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="M13" t="n">
         <v>1.13</v>
       </c>
       <c r="N13" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="O13" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="P13" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="R13" t="n">
         <v>1.16</v>
       </c>
       <c r="S13" t="n">
-        <v>6.4</v>
+        <v>4.1</v>
       </c>
       <c r="T13" t="n">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="U13" t="n">
-        <v>1.69</v>
+        <v>1.42</v>
       </c>
       <c r="V13" t="n">
         <v>1.4</v>
       </c>
       <c r="W13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X13" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>500</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>500</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>500</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>500</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>500</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>540</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BE13" t="n">
         <v>1.51</v>
       </c>
-      <c r="X13" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>23</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>80</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>330</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>46</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>80</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>60</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>500</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>6</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>20</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BF13" t="n">
-        <v>6.8</v>
+        <v>1.55</v>
       </c>
       <c r="BG13" t="n">
-        <v>7</v>
+        <v>1.55</v>
       </c>
       <c r="BH13" t="n">
-        <v>2.68</v>
+        <v>1000</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.18</v>
+        <v>1.01</v>
       </c>
       <c r="BJ13" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK13" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BN13" t="n">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="BO13" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BP13" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BR13" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BT13" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BU13" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BV13" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BX13" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BZ13" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-13 22:40:56</t>
+          <t>2026-07-14 07:32:00</t>
         </is>
       </c>
     </row>
@@ -3893,112 +3905,112 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="G14" t="n">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="H14" t="n">
-        <v>2.68</v>
+        <v>3.45</v>
       </c>
       <c r="I14" t="n">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="J14" t="n">
         <v>2.46</v>
       </c>
       <c r="K14" t="n">
-        <v>3.05</v>
+        <v>2.68</v>
       </c>
       <c r="L14" t="n">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="M14" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="N14" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="O14" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="P14" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="R14" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="S14" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="T14" t="n">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="V14" t="n">
-        <v>1.51</v>
+        <v>1.35</v>
       </c>
       <c r="W14" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="X14" t="n">
-        <v>7.6</v>
+        <v>970</v>
       </c>
       <c r="Y14" t="n">
-        <v>8.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="Z14" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AA14" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AB14" t="n">
-        <v>8.800000000000001</v>
+        <v>970</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.4</v>
+        <v>970</v>
       </c>
       <c r="AD14" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AE14" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AF14" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AG14" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AH14" t="n">
-        <v>28</v>
+        <v>500</v>
       </c>
       <c r="AI14" t="n">
-        <v>460</v>
+        <v>500</v>
       </c>
       <c r="AJ14" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AK14" t="n">
         <v>500</v>
       </c>
       <c r="AL14" t="n">
-        <v>460</v>
+        <v>500</v>
       </c>
       <c r="AM14" t="n">
         <v>500</v>
       </c>
       <c r="AN14" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
         <v>3.85</v>
@@ -4007,10 +4019,10 @@
         <v>4.4</v>
       </c>
       <c r="AR14" t="n">
-        <v>5.2</v>
+        <v>1.32</v>
       </c>
       <c r="AS14" t="n">
-        <v>6.6</v>
+        <v>1.36</v>
       </c>
       <c r="AT14" t="n">
         <v>4.4</v>
@@ -4019,104 +4031,104 @@
         <v>4.2</v>
       </c>
       <c r="AV14" t="n">
-        <v>5</v>
+        <v>8.4</v>
       </c>
       <c r="AW14" t="n">
-        <v>6.6</v>
+        <v>1.36</v>
       </c>
       <c r="AX14" t="n">
-        <v>5.5</v>
+        <v>8.4</v>
       </c>
       <c r="AY14" t="n">
-        <v>5.1</v>
+        <v>8.4</v>
       </c>
       <c r="AZ14" t="n">
-        <v>5.9</v>
+        <v>1.37</v>
       </c>
       <c r="BA14" t="n">
-        <v>6.8</v>
+        <v>1.36</v>
       </c>
       <c r="BB14" t="n">
-        <v>6.8</v>
+        <v>1.36</v>
       </c>
       <c r="BC14" t="n">
-        <v>7</v>
+        <v>1.36</v>
       </c>
       <c r="BD14" t="n">
-        <v>6.8</v>
+        <v>1.36</v>
       </c>
       <c r="BE14" t="n">
-        <v>7.2</v>
+        <v>1.37</v>
       </c>
       <c r="BF14" t="n">
-        <v>7.2</v>
+        <v>1.55</v>
       </c>
       <c r="BG14" t="n">
-        <v>6.6</v>
+        <v>1.55</v>
       </c>
       <c r="BH14" t="n">
-        <v>2.62</v>
+        <v>1000</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.14</v>
+        <v>1.02</v>
       </c>
       <c r="BJ14" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>5.5</v>
+        <v>1.02</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>9.199999999999999</v>
+        <v>1.02</v>
       </c>
       <c r="BN14" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BO14" t="n">
-        <v>4.7</v>
+        <v>1.02</v>
       </c>
       <c r="BP14" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BT14" t="n">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="BU14" t="n">
-        <v>4.4</v>
+        <v>1.02</v>
       </c>
       <c r="BV14" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BZ14" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-13 22:40:56</t>
+          <t>2026-07-14 07:32:00</t>
         </is>
       </c>
     </row>
@@ -4147,34 +4159,34 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.28</v>
+        <v>2.68</v>
       </c>
       <c r="G15" t="n">
-        <v>2.3</v>
+        <v>3.05</v>
       </c>
       <c r="H15" t="n">
-        <v>3.95</v>
+        <v>2.94</v>
       </c>
       <c r="I15" t="n">
-        <v>4.9</v>
+        <v>3.4</v>
       </c>
       <c r="J15" t="n">
         <v>2.82</v>
       </c>
       <c r="K15" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="L15" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="M15" t="n">
         <v>1.14</v>
       </c>
       <c r="N15" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="O15" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="P15" t="n">
         <v>1.43</v>
@@ -4183,194 +4195,194 @@
         <v>2.88</v>
       </c>
       <c r="R15" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="S15" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="T15" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="U15" t="n">
-        <v>1.62</v>
+        <v>1.37</v>
       </c>
       <c r="V15" t="n">
-        <v>1.26</v>
+        <v>1.42</v>
       </c>
       <c r="W15" t="n">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="X15" t="n">
-        <v>8.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="Y15" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="Z15" t="n">
-        <v>34</v>
+        <v>970</v>
       </c>
       <c r="AA15" t="n">
         <v>900</v>
       </c>
       <c r="AB15" t="n">
-        <v>7</v>
+        <v>970</v>
       </c>
       <c r="AC15" t="n">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="AD15" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AE15" t="n">
         <v>500</v>
       </c>
       <c r="AF15" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AG15" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AH15" t="n">
-        <v>30</v>
+        <v>500</v>
       </c>
       <c r="AI15" t="n">
         <v>500</v>
       </c>
       <c r="AJ15" t="n">
-        <v>36</v>
+        <v>900</v>
       </c>
       <c r="AK15" t="n">
-        <v>38</v>
+        <v>500</v>
       </c>
       <c r="AL15" t="n">
-        <v>240</v>
+        <v>500</v>
       </c>
       <c r="AM15" t="n">
         <v>500</v>
       </c>
       <c r="AN15" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AO15" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>5.6</v>
+        <v>1.39</v>
       </c>
       <c r="AQ15" t="n">
         <v>4.4</v>
       </c>
       <c r="AR15" t="n">
-        <v>8.4</v>
+        <v>1.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>6.6</v>
+        <v>1.5</v>
       </c>
       <c r="AT15" t="n">
-        <v>4.9</v>
+        <v>1.37</v>
       </c>
       <c r="AU15" t="n">
-        <v>5.3</v>
+        <v>1.37</v>
       </c>
       <c r="AV15" t="n">
-        <v>8.4</v>
+        <v>1.49</v>
       </c>
       <c r="AW15" t="n">
-        <v>6.4</v>
+        <v>1.51</v>
       </c>
       <c r="AX15" t="n">
-        <v>4.6</v>
+        <v>1.47</v>
       </c>
       <c r="AY15" t="n">
-        <v>4.6</v>
+        <v>1.46</v>
       </c>
       <c r="AZ15" t="n">
-        <v>5.6</v>
+        <v>1.48</v>
       </c>
       <c r="BA15" t="n">
-        <v>6.6</v>
+        <v>1.51</v>
       </c>
       <c r="BB15" t="n">
-        <v>5.8</v>
+        <v>1.5</v>
       </c>
       <c r="BC15" t="n">
-        <v>5.8</v>
+        <v>1.48</v>
       </c>
       <c r="BD15" t="n">
-        <v>6.4</v>
+        <v>1.51</v>
       </c>
       <c r="BE15" t="n">
-        <v>6.8</v>
+        <v>1.51</v>
       </c>
       <c r="BF15" t="n">
-        <v>5.8</v>
+        <v>1.55</v>
       </c>
       <c r="BG15" t="n">
-        <v>6.6</v>
+        <v>1.55</v>
       </c>
       <c r="BH15" t="n">
-        <v>2.74</v>
+        <v>1000</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="BJ15" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BK15" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="BN15" t="n">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="BO15" t="n">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="BP15" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>1.95</v>
+        <v>1.01</v>
       </c>
       <c r="BT15" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="BU15" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>1.95</v>
+        <v>1.01</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.97</v>
+        <v>1.01</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-13 22:40:56</t>
+          <t>2026-07-14 07:32:00</t>
         </is>
       </c>
     </row>
@@ -4401,94 +4413,94 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="G16" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="H16" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="I16" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="J16" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="K16" t="n">
         <v>3.45</v>
       </c>
       <c r="L16" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="M16" t="n">
         <v>1.13</v>
       </c>
       <c r="N16" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="O16" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="P16" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.94</v>
+        <v>2.8</v>
       </c>
       <c r="R16" t="n">
         <v>1.15</v>
       </c>
       <c r="S16" t="n">
-        <v>5.6</v>
+        <v>2.84</v>
       </c>
       <c r="T16" t="n">
-        <v>2.12</v>
+        <v>1.78</v>
       </c>
       <c r="U16" t="n">
-        <v>1.64</v>
+        <v>1.37</v>
       </c>
       <c r="V16" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="W16" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="X16" t="n">
-        <v>9.6</v>
+        <v>970</v>
       </c>
       <c r="Y16" t="n">
-        <v>7.6</v>
+        <v>970</v>
       </c>
       <c r="Z16" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AA16" t="n">
-        <v>40</v>
+        <v>900</v>
       </c>
       <c r="AB16" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AC16" t="n">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="AD16" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AE16" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AF16" t="n">
-        <v>30</v>
+        <v>500</v>
       </c>
       <c r="AG16" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AH16" t="n">
-        <v>29</v>
+        <v>500</v>
       </c>
       <c r="AI16" t="n">
-        <v>170</v>
+        <v>540</v>
       </c>
       <c r="AJ16" t="n">
         <v>900</v>
@@ -4503,128 +4515,128 @@
         <v>500</v>
       </c>
       <c r="AN16" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AO16" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>6</v>
+        <v>1.47</v>
       </c>
       <c r="AQ16" t="n">
-        <v>5.1</v>
+        <v>1.36</v>
       </c>
       <c r="AR16" t="n">
-        <v>10.5</v>
+        <v>1.43</v>
       </c>
       <c r="AS16" t="n">
-        <v>5.1</v>
+        <v>1.46</v>
       </c>
       <c r="AT16" t="n">
-        <v>8.199999999999999</v>
+        <v>4.4</v>
       </c>
       <c r="AU16" t="n">
-        <v>5.5</v>
+        <v>1.33</v>
       </c>
       <c r="AV16" t="n">
-        <v>9</v>
+        <v>1.4</v>
       </c>
       <c r="AW16" t="n">
-        <v>5.1</v>
+        <v>1.46</v>
       </c>
       <c r="AX16" t="n">
-        <v>21</v>
+        <v>1.46</v>
       </c>
       <c r="AY16" t="n">
-        <v>14.5</v>
+        <v>1.45</v>
       </c>
       <c r="AZ16" t="n">
-        <v>20</v>
+        <v>1.44</v>
       </c>
       <c r="BA16" t="n">
-        <v>5.5</v>
+        <v>1.46</v>
       </c>
       <c r="BB16" t="n">
-        <v>5.6</v>
+        <v>1.47</v>
       </c>
       <c r="BC16" t="n">
-        <v>5.5</v>
+        <v>1.47</v>
       </c>
       <c r="BD16" t="n">
-        <v>5.6</v>
+        <v>1.47</v>
       </c>
       <c r="BE16" t="n">
-        <v>5.8</v>
+        <v>1.47</v>
       </c>
       <c r="BF16" t="n">
-        <v>5.7</v>
+        <v>1.55</v>
       </c>
       <c r="BG16" t="n">
-        <v>30</v>
+        <v>1.55</v>
       </c>
       <c r="BH16" t="n">
-        <v>2.76</v>
+        <v>1000</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="BJ16" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK16" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BN16" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BO16" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BP16" t="n">
         <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BT16" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BU16" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="BV16" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BZ16" t="n">
         <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-13 22:40:56</t>
+          <t>2026-07-14 07:32:00</t>
         </is>
       </c>
     </row>
@@ -4655,46 +4667,46 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="G17" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="H17" t="n">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="I17" t="n">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="J17" t="n">
-        <v>3.15</v>
+        <v>4.2</v>
       </c>
       <c r="K17" t="n">
-        <v>7.6</v>
+        <v>4.8</v>
       </c>
       <c r="L17" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N17" t="n">
-        <v>1.02</v>
+        <v>6.8</v>
       </c>
       <c r="O17" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="P17" t="n">
-        <v>1.32</v>
+        <v>3</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="R17" t="n">
-        <v>1.32</v>
+        <v>1.84</v>
       </c>
       <c r="S17" t="n">
-        <v>1.33</v>
+        <v>2.08</v>
       </c>
       <c r="T17" t="n">
         <v>1.01</v>
@@ -4703,19 +4715,19 @@
         <v>1.01</v>
       </c>
       <c r="V17" t="n">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="W17" t="n">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="X17" t="n">
         <v>500</v>
       </c>
       <c r="Y17" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="Z17" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AA17" t="n">
         <v>500</v>
@@ -4724,22 +4736,22 @@
         <v>500</v>
       </c>
       <c r="AC17" t="n">
-        <v>500</v>
+        <v>95</v>
       </c>
       <c r="AD17" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AE17" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AF17" t="n">
         <v>500</v>
       </c>
       <c r="AG17" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AH17" t="n">
-        <v>500</v>
+        <v>130</v>
       </c>
       <c r="AI17" t="n">
         <v>500</v>
@@ -4757,64 +4769,64 @@
         <v>580</v>
       </c>
       <c r="AN17" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.21</v>
+        <v>1.82</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.17</v>
+        <v>1.74</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.18</v>
+        <v>1.75</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.2</v>
+        <v>1.78</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.21</v>
+        <v>1.82</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.18</v>
+        <v>6.2</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.17</v>
+        <v>6.2</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.2</v>
+        <v>1.75</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.21</v>
+        <v>1.83</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.21</v>
+        <v>1.78</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.19</v>
+        <v>1.73</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.2</v>
+        <v>1.79</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.21</v>
+        <v>1.85</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.21</v>
+        <v>1.84</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.21</v>
+        <v>1.83</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.21</v>
+        <v>1.85</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.55</v>
+        <v>1.93</v>
       </c>
       <c r="BH17" t="n">
         <v>1000</v>
@@ -4878,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-13 22:40:56</t>
+          <t>2026-07-14 07:32:00</t>
         </is>
       </c>
     </row>
@@ -4909,58 +4921,58 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.21</v>
+        <v>1.46</v>
       </c>
       <c r="G18" t="n">
-        <v>1.59</v>
+        <v>1.48</v>
       </c>
       <c r="H18" t="n">
-        <v>2.7</v>
+        <v>6.8</v>
       </c>
       <c r="I18" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>2.7</v>
+        <v>4.8</v>
       </c>
       <c r="K18" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N18" t="n">
-        <v>1.36</v>
+        <v>6</v>
       </c>
       <c r="O18" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="P18" t="n">
-        <v>1.36</v>
+        <v>2.74</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.14</v>
+        <v>1.52</v>
       </c>
       <c r="R18" t="n">
-        <v>1.28</v>
+        <v>1.7</v>
       </c>
       <c r="S18" t="n">
-        <v>1.14</v>
+        <v>2.3</v>
       </c>
       <c r="T18" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="U18" t="n">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="V18" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="W18" t="n">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="X18" t="n">
         <v>1000</v>
@@ -5132,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-13 22:40:56</t>
+          <t>2026-07-14 07:32:00</t>
         </is>
       </c>
     </row>
@@ -5163,40 +5175,40 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="G19" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="H19" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="K19" t="n">
         <v>2.86</v>
       </c>
-      <c r="I19" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="J19" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="K19" t="n">
-        <v>2.94</v>
-      </c>
       <c r="L19" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="M19" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="N19" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="O19" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="P19" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="R19" t="n">
         <v>1.16</v>
@@ -5205,85 +5217,85 @@
         <v>6.8</v>
       </c>
       <c r="T19" t="n">
-        <v>2.26</v>
+        <v>1.88</v>
       </c>
       <c r="U19" t="n">
-        <v>1.68</v>
+        <v>1.56</v>
       </c>
       <c r="V19" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="W19" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="X19" t="n">
         <v>7.2</v>
       </c>
       <c r="Y19" t="n">
-        <v>7.8</v>
+        <v>970</v>
       </c>
       <c r="Z19" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AA19" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE19" t="n">
         <v>55</v>
       </c>
-      <c r="AB19" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>50</v>
-      </c>
       <c r="AF19" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AG19" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AH19" t="n">
         <v>29</v>
       </c>
       <c r="AI19" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AJ19" t="n">
         <v>65</v>
       </c>
       <c r="AK19" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AL19" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AM19" t="n">
-        <v>250</v>
+        <v>320</v>
       </c>
       <c r="AN19" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AO19" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AP19" t="n">
-        <v>6.4</v>
+        <v>4.6</v>
       </c>
       <c r="AQ19" t="n">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="AR19" t="n">
-        <v>15</v>
+        <v>2.4</v>
       </c>
       <c r="AS19" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AT19" t="n">
-        <v>7.6</v>
+        <v>4.3</v>
       </c>
       <c r="AU19" t="n">
         <v>6.2</v>
@@ -5292,101 +5304,101 @@
         <v>13</v>
       </c>
       <c r="AW19" t="n">
-        <v>42</v>
+        <v>2.68</v>
       </c>
       <c r="AX19" t="n">
         <v>16.5</v>
       </c>
       <c r="AY19" t="n">
-        <v>14.5</v>
+        <v>7</v>
       </c>
       <c r="AZ19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA19" t="n">
-        <v>9.4</v>
+        <v>2.74</v>
       </c>
       <c r="BB19" t="n">
-        <v>9</v>
+        <v>2.7</v>
       </c>
       <c r="BC19" t="n">
-        <v>46</v>
+        <v>2.68</v>
       </c>
       <c r="BD19" t="n">
-        <v>9.4</v>
+        <v>2.74</v>
       </c>
       <c r="BE19" t="n">
-        <v>10</v>
+        <v>2.78</v>
       </c>
       <c r="BF19" t="n">
-        <v>9.199999999999999</v>
+        <v>2.72</v>
       </c>
       <c r="BG19" t="n">
-        <v>12</v>
+        <v>2.7</v>
       </c>
       <c r="BH19" t="n">
-        <v>2.58</v>
+        <v>1000</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="BJ19" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK19" t="n">
-        <v>5.9</v>
+        <v>4.5</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>10.5</v>
+        <v>7.6</v>
       </c>
       <c r="BN19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ19" t="n">
         <v>6.2</v>
       </c>
-      <c r="BO19" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BP19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ19" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BR19" t="n">
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>9.4</v>
+        <v>7</v>
       </c>
       <c r="BT19" t="n">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="BU19" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="BV19" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>8.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BZ19" t="n">
         <v>1000</v>
       </c>
       <c r="CA19" t="n">
-        <v>9.6</v>
+        <v>7.2</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-13 22:40:56</t>
+          <t>2026-07-14 07:32:00</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-14.xlsx
@@ -857,230 +857,230 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.48</v>
+        <v>1.25</v>
       </c>
       <c r="G2" t="n">
-        <v>1.5</v>
+        <v>1.26</v>
       </c>
       <c r="H2" t="n">
-        <v>6.6</v>
+        <v>19.5</v>
       </c>
       <c r="I2" t="n">
+        <v>20</v>
+      </c>
+      <c r="J2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="K2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB2" t="n">
         <v>7</v>
       </c>
-      <c r="J2" t="n">
+      <c r="AC2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>190</v>
+      </c>
+      <c r="AF2" t="n">
         <v>5.5</v>
       </c>
-      <c r="K2" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N2" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="P2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W2" t="n">
-        <v>3</v>
-      </c>
-      <c r="X2" t="n">
-        <v>55</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>44</v>
-      </c>
-      <c r="Z2" t="n">
+      <c r="AG2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI2" t="n">
         <v>160</v>
       </c>
-      <c r="AA2" t="n">
-        <v>210</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>19</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AD2" t="n">
+      <c r="AJ2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>14</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>220</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>420</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV2" t="n">
         <v>28</v>
       </c>
-      <c r="AE2" t="n">
+      <c r="AW2" t="n">
         <v>130</v>
       </c>
-      <c r="AF2" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>17</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AL2" t="n">
+      <c r="AX2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AZ2" t="n">
         <v>23</v>
       </c>
-      <c r="AM2" t="n">
-        <v>65</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>170</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>32</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>34</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>60</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>15</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>14</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>23</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>42</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>15.5</v>
-      </c>
       <c r="BA2" t="n">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="BB2" t="n">
-        <v>14</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC2" t="n">
         <v>12</v>
       </c>
       <c r="BD2" t="n">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="BE2" t="n">
-        <v>28</v>
+        <v>200</v>
       </c>
       <c r="BF2" t="n">
-        <v>3.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG2" t="n">
-        <v>38</v>
+        <v>110</v>
       </c>
       <c r="BH2" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK2" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="BN2" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BP2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ2" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="BR2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="BT2" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="BU2" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="BV2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA2" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-14 07:32:00</t>
+          <t>2026-07-14 09:40:53</t>
         </is>
       </c>
     </row>
@@ -1111,230 +1111,230 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="G3" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="H3" t="n">
         <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J3" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="K3" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="M3" t="n">
         <v>1.02</v>
       </c>
       <c r="N3" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="O3" t="n">
         <v>1.09</v>
       </c>
       <c r="P3" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="R3" t="n">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="S3" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="U3" t="n">
-        <v>2.14</v>
+        <v>3.25</v>
       </c>
       <c r="V3" t="n">
         <v>1.29</v>
       </c>
       <c r="W3" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="X3" t="n">
-        <v>140</v>
+        <v>90</v>
       </c>
       <c r="Y3" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="Z3" t="n">
-        <v>140</v>
+        <v>70</v>
       </c>
       <c r="AA3" t="n">
-        <v>500</v>
+        <v>470</v>
       </c>
       <c r="AB3" t="n">
-        <v>970</v>
+        <v>25</v>
       </c>
       <c r="AC3" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AD3" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="AE3" t="n">
-        <v>120</v>
+        <v>48</v>
       </c>
       <c r="AF3" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="AG3" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="AJ3" t="n">
-        <v>120</v>
+        <v>24</v>
       </c>
       <c r="AK3" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AL3" t="n">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="AM3" t="n">
-        <v>580</v>
+        <v>55</v>
       </c>
       <c r="AN3" t="n">
-        <v>29</v>
+        <v>4.7</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AP3" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.7</v>
+        <v>32</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.71</v>
+        <v>40</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.72</v>
+        <v>55</v>
       </c>
       <c r="AT3" t="n">
-        <v>8.4</v>
+        <v>20</v>
       </c>
       <c r="AU3" t="n">
-        <v>6.4</v>
+        <v>13</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.71</v>
+        <v>17.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.71</v>
+        <v>30</v>
       </c>
       <c r="AX3" t="n">
-        <v>8.4</v>
+        <v>18</v>
       </c>
       <c r="AY3" t="n">
-        <v>6.4</v>
+        <v>11</v>
       </c>
       <c r="AZ3" t="n">
-        <v>6.8</v>
+        <v>12.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.69</v>
+        <v>24</v>
       </c>
       <c r="BB3" t="n">
-        <v>10</v>
+        <v>16.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>7.6</v>
+        <v>13.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>9.800000000000001</v>
+        <v>17</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.72</v>
+        <v>20</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.78</v>
+        <v>4.1</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.74</v>
+        <v>14.5</v>
       </c>
       <c r="BH3" t="n">
         <v>6.4</v>
       </c>
       <c r="BI3" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BJ3" t="n">
         <v>8.6</v>
       </c>
       <c r="BK3" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BL3" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BM3" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BN3" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BP3" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.3</v>
+        <v>7.8</v>
       </c>
       <c r="BR3" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BS3" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BT3" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU3" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BV3" t="n">
         <v>27</v>
       </c>
       <c r="BW3" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BX3" t="n">
         <v>26</v>
       </c>
       <c r="BY3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BZ3" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-14 07:32:00</t>
+          <t>2026-07-14 09:40:53</t>
         </is>
       </c>
     </row>
@@ -1368,61 +1368,61 @@
         <v>2.1</v>
       </c>
       <c r="G4" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="H4" t="n">
         <v>4.7</v>
       </c>
       <c r="I4" t="n">
-        <v>7.2</v>
+        <v>5.1</v>
       </c>
       <c r="J4" t="n">
         <v>2.88</v>
       </c>
       <c r="K4" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L4" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="M4" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N4" t="n">
         <v>2.46</v>
       </c>
       <c r="O4" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="P4" t="n">
         <v>1.46</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="R4" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="S4" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="U4" t="n">
-        <v>1.04</v>
+        <v>1.66</v>
       </c>
       <c r="V4" t="n">
         <v>1.25</v>
       </c>
       <c r="W4" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="X4" t="n">
-        <v>970</v>
+        <v>8</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z4" t="n">
         <v>500</v>
@@ -1431,22 +1431,22 @@
         <v>900</v>
       </c>
       <c r="AB4" t="n">
-        <v>970</v>
+        <v>6.8</v>
       </c>
       <c r="AC4" t="n">
-        <v>42</v>
+        <v>7.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="AE4" t="n">
         <v>700</v>
       </c>
       <c r="AF4" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AG4" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AH4" t="n">
         <v>75</v>
@@ -1455,13 +1455,13 @@
         <v>700</v>
       </c>
       <c r="AJ4" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK4" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AL4" t="n">
-        <v>500</v>
+        <v>210</v>
       </c>
       <c r="AM4" t="n">
         <v>500</v>
@@ -1470,125 +1470,125 @@
         <v>600</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.6</v>
+        <v>6.6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.75</v>
+        <v>13.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.79</v>
+        <v>9.4</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.1</v>
+        <v>5.7</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.71</v>
+        <v>17.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.78</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX4" t="n">
-        <v>5.5</v>
+        <v>10</v>
       </c>
       <c r="AY4" t="n">
-        <v>5.5</v>
+        <v>10</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.75</v>
+        <v>12</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.78</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.75</v>
+        <v>12</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.74</v>
+        <v>13</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.77</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.78</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.78</v>
+        <v>7.8</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.79</v>
+        <v>9.6</v>
       </c>
       <c r="BH4" t="n">
-        <v>1000</v>
+        <v>2.66</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BN4" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BP4" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BR4" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT4" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-14 07:32:00</t>
+          <t>2026-07-14 09:40:53</t>
         </is>
       </c>
     </row>
@@ -1619,13 +1619,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="G5" t="n">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="H5" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="I5" t="n">
         <v>1.92</v>
@@ -1634,25 +1634,25 @@
         <v>3.2</v>
       </c>
       <c r="K5" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="L5" t="n">
         <v>1.62</v>
       </c>
       <c r="M5" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N5" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="O5" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="P5" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="R5" t="n">
         <v>1.17</v>
@@ -1661,10 +1661,10 @@
         <v>5.7</v>
       </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="U5" t="n">
-        <v>1.03</v>
+        <v>1.6</v>
       </c>
       <c r="V5" t="n">
         <v>2.08</v>
@@ -1673,40 +1673,40 @@
         <v>1.18</v>
       </c>
       <c r="X5" t="n">
-        <v>970</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y5" t="n">
-        <v>970</v>
+        <v>6.2</v>
       </c>
       <c r="Z5" t="n">
-        <v>970</v>
+        <v>9.6</v>
       </c>
       <c r="AA5" t="n">
-        <v>900</v>
+        <v>23</v>
       </c>
       <c r="AB5" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AC5" t="n">
-        <v>42</v>
+        <v>8.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AE5" t="n">
-        <v>500</v>
+        <v>29</v>
       </c>
       <c r="AF5" t="n">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="AG5" t="n">
-        <v>970</v>
+        <v>32</v>
       </c>
       <c r="AH5" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AI5" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AJ5" t="n">
         <v>900</v>
@@ -1721,128 +1721,128 @@
         <v>500</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.6</v>
+        <v>7.2</v>
       </c>
       <c r="AQ5" t="n">
-        <v>2.86</v>
+        <v>5.1</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.8</v>
+        <v>7.8</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.51</v>
+        <v>17.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>5.7</v>
+        <v>12</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.7</v>
+        <v>7</v>
       </c>
       <c r="AV5" t="n">
-        <v>5.2</v>
+        <v>9.4</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.5</v>
+        <v>20</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.52</v>
+        <v>30</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.52</v>
+        <v>17.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.5</v>
+        <v>19</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.53</v>
+        <v>34</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.54</v>
+        <v>8.6</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.54</v>
+        <v>8.4</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.54</v>
+        <v>8.4</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.54</v>
+        <v>8.6</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.55</v>
+        <v>8.6</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.55</v>
+        <v>18.5</v>
       </c>
       <c r="BH5" t="n">
-        <v>1000</v>
+        <v>2.74</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BN5" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BT5" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BV5" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-14 07:32:00</t>
+          <t>2026-07-14 09:40:53</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="G6" t="n">
         <v>4.2</v>
@@ -1885,10 +1885,10 @@
         <v>2.5</v>
       </c>
       <c r="J6" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="K6" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="L6" t="n">
         <v>1.55</v>
@@ -1903,7 +1903,7 @@
         <v>1.5</v>
       </c>
       <c r="P6" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Q6" t="n">
         <v>2.56</v>
@@ -1912,13 +1912,13 @@
         <v>1.19</v>
       </c>
       <c r="S6" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="V6" t="n">
         <v>1.67</v>
@@ -1927,176 +1927,176 @@
         <v>1.33</v>
       </c>
       <c r="X6" t="n">
-        <v>970</v>
+        <v>9.6</v>
       </c>
       <c r="Y6" t="n">
-        <v>970</v>
+        <v>8</v>
       </c>
       <c r="Z6" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>900</v>
+        <v>38</v>
       </c>
       <c r="AB6" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>42</v>
+        <v>7.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AE6" t="n">
-        <v>110</v>
+        <v>36</v>
       </c>
       <c r="AF6" t="n">
-        <v>120</v>
+        <v>28</v>
       </c>
       <c r="AG6" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AH6" t="n">
-        <v>85</v>
+        <v>25</v>
       </c>
       <c r="AI6" t="n">
-        <v>450</v>
+        <v>65</v>
       </c>
       <c r="AJ6" t="n">
-        <v>900</v>
+        <v>250</v>
       </c>
       <c r="AK6" t="n">
-        <v>160</v>
+        <v>70</v>
       </c>
       <c r="AL6" t="n">
-        <v>540</v>
+        <v>200</v>
       </c>
       <c r="AM6" t="n">
         <v>500</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AO6" t="n">
-        <v>600</v>
+        <v>36</v>
       </c>
       <c r="AP6" t="n">
-        <v>4.4</v>
+        <v>7.4</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.4</v>
+        <v>6.2</v>
       </c>
       <c r="AR6" t="n">
-        <v>5.8</v>
+        <v>11</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.69</v>
+        <v>24</v>
       </c>
       <c r="AT6" t="n">
-        <v>4.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU6" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="AV6" t="n">
-        <v>5.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.68</v>
+        <v>24</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.7</v>
+        <v>21</v>
       </c>
       <c r="AY6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>28</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>24</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>9</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>40</v>
+      </c>
+      <c r="BQ6" t="n">
         <v>7.6</v>
       </c>
-      <c r="AZ6" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BR6" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT6" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BV6" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BX6" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-14 07:32:00</t>
+          <t>2026-07-14 09:40:53</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="G7" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H7" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="I7" t="n">
         <v>3.15</v>
       </c>
       <c r="J7" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="K7" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L7" t="n">
         <v>1.24</v>
@@ -2154,203 +2154,203 @@
         <v>7.2</v>
       </c>
       <c r="O7" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="P7" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="Q7" t="n">
         <v>1.44</v>
       </c>
       <c r="R7" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="S7" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="T7" t="n">
-        <v>1.11</v>
+        <v>1.42</v>
       </c>
       <c r="U7" t="n">
-        <v>1.11</v>
+        <v>3</v>
       </c>
       <c r="V7" t="n">
         <v>1.46</v>
       </c>
       <c r="W7" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Y7" t="n">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="Z7" t="n">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="AA7" t="n">
-        <v>470</v>
+        <v>55</v>
       </c>
       <c r="AB7" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AC7" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AE7" t="n">
-        <v>85</v>
+        <v>27</v>
       </c>
       <c r="AF7" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="AG7" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AH7" t="n">
-        <v>60</v>
+        <v>14.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>85</v>
+        <v>28</v>
       </c>
       <c r="AJ7" t="n">
-        <v>160</v>
+        <v>34</v>
       </c>
       <c r="AK7" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AL7" t="n">
-        <v>220</v>
+        <v>25</v>
       </c>
       <c r="AM7" t="n">
-        <v>580</v>
+        <v>44</v>
       </c>
       <c r="AN7" t="n">
-        <v>970</v>
+        <v>9.4</v>
       </c>
       <c r="AO7" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.37</v>
+        <v>15.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.33</v>
+        <v>19.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.35</v>
+        <v>13</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.36</v>
+        <v>22</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.32</v>
+        <v>16.5</v>
       </c>
       <c r="AU7" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>17</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>34</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>12</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BK7" t="n">
         <v>5.1</v>
       </c>
-      <c r="AV7" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BN7" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BP7" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BR7" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BT7" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BV7" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BX7" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-14 07:32:00</t>
+          <t>2026-07-14 09:40:53</t>
         </is>
       </c>
     </row>
@@ -2381,230 +2381,230 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="G8" t="n">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="H8" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="I8" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="J8" t="n">
-        <v>2.76</v>
+        <v>2.86</v>
       </c>
       <c r="K8" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="L8" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="M8" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N8" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="O8" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="P8" t="n">
         <v>1.46</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="R8" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="S8" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="T8" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="U8" t="n">
-        <v>1.38</v>
+        <v>1.7</v>
       </c>
       <c r="V8" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W8" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="X8" t="n">
-        <v>500</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y8" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>500</v>
+        <v>27</v>
       </c>
       <c r="AA8" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="AB8" t="n">
-        <v>970</v>
+        <v>7.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>42</v>
+        <v>7.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AE8" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AF8" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AG8" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AH8" t="n">
-        <v>500</v>
+        <v>26</v>
       </c>
       <c r="AI8" t="n">
-        <v>500</v>
+        <v>340</v>
       </c>
       <c r="AJ8" t="n">
-        <v>500</v>
+        <v>38</v>
       </c>
       <c r="AK8" t="n">
-        <v>500</v>
+        <v>38</v>
       </c>
       <c r="AL8" t="n">
-        <v>500</v>
+        <v>210</v>
       </c>
       <c r="AM8" t="n">
         <v>500</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AP8" t="n">
-        <v>3.85</v>
+        <v>6.6</v>
       </c>
       <c r="AQ8" t="n">
-        <v>4.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR8" t="n">
-        <v>7.6</v>
+        <v>21</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.66</v>
+        <v>9</v>
       </c>
       <c r="AT8" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="AU8" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="AV8" t="n">
-        <v>7.6</v>
+        <v>14.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.66</v>
+        <v>20</v>
       </c>
       <c r="AX8" t="n">
-        <v>7</v>
+        <v>11.5</v>
       </c>
       <c r="AY8" t="n">
-        <v>6.2</v>
+        <v>10.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.65</v>
+        <v>21</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.67</v>
+        <v>9</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.66</v>
+        <v>11</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.66</v>
+        <v>11</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.67</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.67</v>
+        <v>9.6</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.68</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.68</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH8" t="n">
-        <v>1000</v>
+        <v>2.66</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BN8" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BP8" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BT8" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BV8" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BX8" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="CA8" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-14 07:32:00</t>
+          <t>2026-07-14 09:40:53</t>
         </is>
       </c>
     </row>
@@ -2635,230 +2635,230 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="H9" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="I9" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="J9" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="K9" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L9" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="M9" t="n">
         <v>1.13</v>
       </c>
       <c r="N9" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="O9" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="P9" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="R9" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S9" t="n">
-        <v>2.72</v>
+        <v>5.3</v>
       </c>
       <c r="T9" t="n">
-        <v>1.11</v>
+        <v>2.28</v>
       </c>
       <c r="U9" t="n">
-        <v>1.11</v>
+        <v>1.64</v>
       </c>
       <c r="V9" t="n">
         <v>1.19</v>
       </c>
       <c r="W9" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="X9" t="n">
-        <v>970</v>
+        <v>9</v>
       </c>
       <c r="Y9" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>170</v>
+        <v>55</v>
       </c>
       <c r="AA9" t="n">
         <v>900</v>
       </c>
       <c r="AB9" t="n">
-        <v>970</v>
+        <v>6.4</v>
       </c>
       <c r="AC9" t="n">
-        <v>42</v>
+        <v>8.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>120</v>
+        <v>27</v>
       </c>
       <c r="AE9" t="n">
         <v>500</v>
       </c>
       <c r="AF9" t="n">
-        <v>970</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG9" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="AI9" t="n">
         <v>500</v>
       </c>
       <c r="AJ9" t="n">
-        <v>900</v>
+        <v>21</v>
       </c>
       <c r="AK9" t="n">
-        <v>110</v>
+        <v>27</v>
       </c>
       <c r="AL9" t="n">
-        <v>450</v>
+        <v>160</v>
       </c>
       <c r="AM9" t="n">
         <v>500</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AP9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>17</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>13</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>13</v>
+      </c>
+      <c r="BN9" t="n">
         <v>4.2</v>
       </c>
-      <c r="AQ9" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>1000</v>
-      </c>
       <c r="BO9" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BP9" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BR9" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BT9" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BV9" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-14 07:32:00</t>
+          <t>2026-07-14 09:40:53</t>
         </is>
       </c>
     </row>
@@ -2889,13 +2889,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="G10" t="n">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="H10" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="I10" t="n">
         <v>7.4</v>
@@ -2904,7 +2904,7 @@
         <v>3.4</v>
       </c>
       <c r="K10" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L10" t="n">
         <v>1.6</v>
@@ -2913,206 +2913,206 @@
         <v>1.13</v>
       </c>
       <c r="N10" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="O10" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="P10" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="R10" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="S10" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="T10" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="U10" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="V10" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W10" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="X10" t="n">
-        <v>970</v>
+        <v>9</v>
       </c>
       <c r="Y10" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="Z10" t="n">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AA10" t="n">
         <v>900</v>
       </c>
       <c r="AB10" t="n">
-        <v>970</v>
+        <v>6.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>42</v>
+        <v>8.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AF10" t="n">
-        <v>970</v>
+        <v>9.6</v>
       </c>
       <c r="AG10" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AH10" t="n">
-        <v>110</v>
+        <v>32</v>
       </c>
       <c r="AI10" t="n">
         <v>700</v>
       </c>
       <c r="AJ10" t="n">
-        <v>900</v>
+        <v>22</v>
       </c>
       <c r="AK10" t="n">
-        <v>110</v>
+        <v>28</v>
       </c>
       <c r="AL10" t="n">
-        <v>460</v>
+        <v>160</v>
       </c>
       <c r="AM10" t="n">
         <v>500</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>860</v>
       </c>
       <c r="AP10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>30</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>19</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>24</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>28</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN10" t="n">
         <v>4.2</v>
       </c>
-      <c r="AQ10" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AT10" t="n">
+      <c r="BO10" t="n">
         <v>3.5</v>
       </c>
-      <c r="AU10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>7</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BP10" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BR10" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BT10" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-14 07:32:00</t>
+          <t>2026-07-14 09:40:53</t>
         </is>
       </c>
     </row>
@@ -3143,19 +3143,19 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="G11" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="H11" t="n">
         <v>2.66</v>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="J11" t="n">
-        <v>2.46</v>
+        <v>2.58</v>
       </c>
       <c r="K11" t="n">
         <v>2.7</v>
@@ -3164,13 +3164,13 @@
         <v>1.69</v>
       </c>
       <c r="M11" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="N11" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="O11" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="P11" t="n">
         <v>1.4</v>
@@ -3182,7 +3182,7 @@
         <v>1.14</v>
       </c>
       <c r="S11" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="T11" t="n">
         <v>1.11</v>
@@ -3191,10 +3191,10 @@
         <v>1.11</v>
       </c>
       <c r="V11" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="W11" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="X11" t="n">
         <v>16</v>
@@ -3251,7 +3251,7 @@
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>3.5</v>
+        <v>5.7</v>
       </c>
       <c r="AQ11" t="n">
         <v>1.21</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-14 07:32:00</t>
+          <t>2026-07-14 09:40:53</t>
         </is>
       </c>
     </row>
@@ -3397,40 +3397,40 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="G12" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H12" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="I12" t="n">
         <v>4.3</v>
       </c>
       <c r="J12" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K12" t="n">
         <v>3.6</v>
       </c>
       <c r="L12" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M12" t="n">
         <v>1.09</v>
       </c>
       <c r="N12" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O12" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="P12" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="R12" t="n">
         <v>1.28</v>
@@ -3439,188 +3439,188 @@
         <v>4.2</v>
       </c>
       <c r="T12" t="n">
-        <v>1.57</v>
+        <v>1.96</v>
       </c>
       <c r="U12" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="V12" t="n">
         <v>1.31</v>
       </c>
       <c r="W12" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="X12" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="Z12" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="AA12" t="n">
         <v>900</v>
       </c>
       <c r="AB12" t="n">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AC12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG12" t="n">
         <v>11.5</v>
       </c>
-      <c r="AD12" t="n">
+      <c r="AH12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI12" t="n">
         <v>90</v>
       </c>
-      <c r="AE12" t="n">
-        <v>370</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>18</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>36</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>370</v>
-      </c>
       <c r="AJ12" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="AK12" t="n">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="AL12" t="n">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="AM12" t="n">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN12" t="n">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="AO12" t="n">
-        <v>600</v>
+        <v>230</v>
       </c>
       <c r="AP12" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AQ12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR12" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AS12" t="n">
         <v>55</v>
       </c>
       <c r="AT12" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AU12" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="AV12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AW12" t="n">
+        <v>36</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>46</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>29</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>18</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>44</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>16</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BR12" t="n">
         <v>34</v>
       </c>
-      <c r="AX12" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>44</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>19</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>18</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>30</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>40</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>1000</v>
-      </c>
       <c r="BS12" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BT12" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BU12" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BV12" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BX12" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BZ12" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="CA12" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-14 07:32:00</t>
+          <t>2026-07-14 09:40:53</t>
         </is>
       </c>
     </row>
@@ -3654,16 +3654,16 @@
         <v>2.62</v>
       </c>
       <c r="G13" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="H13" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I13" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="J13" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="K13" t="n">
         <v>3.05</v>
@@ -3681,7 +3681,7 @@
         <v>1.57</v>
       </c>
       <c r="P13" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="Q13" t="n">
         <v>2.78</v>
@@ -3690,191 +3690,191 @@
         <v>1.16</v>
       </c>
       <c r="S13" t="n">
-        <v>4.1</v>
+        <v>5.7</v>
       </c>
       <c r="T13" t="n">
-        <v>1.78</v>
+        <v>2.12</v>
       </c>
       <c r="U13" t="n">
-        <v>1.42</v>
+        <v>1.69</v>
       </c>
       <c r="V13" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W13" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="X13" t="n">
-        <v>970</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y13" t="n">
-        <v>970</v>
+        <v>9.6</v>
       </c>
       <c r="Z13" t="n">
-        <v>500</v>
+        <v>23</v>
       </c>
       <c r="AA13" t="n">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="AB13" t="n">
-        <v>970</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC13" t="n">
-        <v>970</v>
+        <v>7.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AE13" t="n">
-        <v>500</v>
+        <v>170</v>
       </c>
       <c r="AF13" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>500</v>
+        <v>26</v>
       </c>
       <c r="AI13" t="n">
-        <v>500</v>
+        <v>330</v>
       </c>
       <c r="AJ13" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="AK13" t="n">
-        <v>500</v>
+        <v>46</v>
       </c>
       <c r="AL13" t="n">
-        <v>540</v>
+        <v>80</v>
       </c>
       <c r="AM13" t="n">
         <v>500</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.38</v>
+        <v>6.4</v>
       </c>
       <c r="AQ13" t="n">
-        <v>4.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.49</v>
+        <v>17.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.5</v>
+        <v>20</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.38</v>
+        <v>6.4</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.46</v>
+        <v>5.9</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.48</v>
+        <v>13</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.5</v>
+        <v>7</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.46</v>
+        <v>12</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.42</v>
+        <v>11</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.47</v>
+        <v>20</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.5</v>
+        <v>7.4</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.49</v>
+        <v>34</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.49</v>
+        <v>6.8</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.5</v>
+        <v>27</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.51</v>
+        <v>7.8</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.55</v>
+        <v>7</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.55</v>
+        <v>7.2</v>
       </c>
       <c r="BH13" t="n">
-        <v>1000</v>
+        <v>2.68</v>
       </c>
       <c r="BI13" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="BJ13" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK13" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN13" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BP13" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BQ13" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BR13" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS13" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT13" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU13" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BV13" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW13" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BX13" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BZ13" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="CA13" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-14 07:32:00</t>
+          <t>2026-07-14 09:40:53</t>
         </is>
       </c>
     </row>
@@ -3917,10 +3917,10 @@
         <v>4</v>
       </c>
       <c r="J14" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="K14" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="L14" t="n">
         <v>1.74</v>
@@ -3938,197 +3938,197 @@
         <v>1.37</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="R14" t="n">
         <v>1.13</v>
       </c>
       <c r="S14" t="n">
+        <v>7</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X14" t="n">
         <v>6.8</v>
       </c>
-      <c r="T14" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="X14" t="n">
-        <v>970</v>
-      </c>
       <c r="Y14" t="n">
-        <v>970</v>
+        <v>9.6</v>
       </c>
       <c r="Z14" t="n">
-        <v>970</v>
+        <v>24</v>
       </c>
       <c r="AA14" t="n">
-        <v>500</v>
+        <v>90</v>
       </c>
       <c r="AB14" t="n">
-        <v>970</v>
+        <v>8</v>
       </c>
       <c r="AC14" t="n">
-        <v>970</v>
+        <v>6.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AF14" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AG14" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>500</v>
+        <v>29</v>
       </c>
       <c r="AI14" t="n">
         <v>500</v>
       </c>
       <c r="AJ14" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AK14" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AL14" t="n">
-        <v>500</v>
+        <v>240</v>
       </c>
       <c r="AM14" t="n">
         <v>500</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AP14" t="n">
-        <v>3.85</v>
+        <v>5.3</v>
       </c>
       <c r="AQ14" t="n">
-        <v>4.4</v>
+        <v>7.4</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.32</v>
+        <v>18</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.36</v>
+        <v>22</v>
       </c>
       <c r="AT14" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="AU14" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="AV14" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA14" t="n">
         <v>8.4</v>
       </c>
-      <c r="AW14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AX14" t="n">
+      <c r="BB14" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD14" t="n">
         <v>8.4</v>
       </c>
-      <c r="AY14" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>1.36</v>
-      </c>
       <c r="BE14" t="n">
-        <v>1.37</v>
+        <v>7.4</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.55</v>
+        <v>8</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.55</v>
+        <v>7.2</v>
       </c>
       <c r="BH14" t="n">
-        <v>1000</v>
+        <v>2.54</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.02</v>
+        <v>2.14</v>
       </c>
       <c r="BJ14" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.02</v>
+        <v>5.4</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.02</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN14" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.02</v>
+        <v>4.6</v>
       </c>
       <c r="BP14" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BQ14" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BT14" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU14" t="n">
-        <v>1.02</v>
+        <v>5.2</v>
       </c>
       <c r="BV14" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ14" t="n">
         <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-14 07:32:00</t>
+          <t>2026-07-14 09:40:53</t>
         </is>
       </c>
     </row>
@@ -4159,28 +4159,28 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="G15" t="n">
         <v>3.05</v>
       </c>
       <c r="H15" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="I15" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="J15" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="K15" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="L15" t="n">
         <v>1.64</v>
       </c>
       <c r="M15" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N15" t="n">
         <v>2.5</v>
@@ -4189,200 +4189,200 @@
         <v>1.62</v>
       </c>
       <c r="P15" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="R15" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="S15" t="n">
         <v>6.2</v>
       </c>
       <c r="T15" t="n">
-        <v>1.83</v>
+        <v>2.18</v>
       </c>
       <c r="U15" t="n">
-        <v>1.37</v>
+        <v>1.69</v>
       </c>
       <c r="V15" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W15" t="n">
         <v>1.5</v>
       </c>
       <c r="X15" t="n">
-        <v>970</v>
+        <v>7.8</v>
       </c>
       <c r="Y15" t="n">
-        <v>970</v>
+        <v>8.4</v>
       </c>
       <c r="Z15" t="n">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>900</v>
+        <v>270</v>
       </c>
       <c r="AB15" t="n">
-        <v>970</v>
+        <v>8</v>
       </c>
       <c r="AC15" t="n">
-        <v>42</v>
+        <v>7.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>500</v>
+        <v>220</v>
       </c>
       <c r="AF15" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AG15" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AH15" t="n">
-        <v>500</v>
+        <v>38</v>
       </c>
       <c r="AI15" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="AJ15" t="n">
-        <v>900</v>
+        <v>160</v>
       </c>
       <c r="AK15" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AL15" t="n">
-        <v>500</v>
+        <v>460</v>
       </c>
       <c r="AM15" t="n">
         <v>500</v>
       </c>
       <c r="AN15" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AO15" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.39</v>
+        <v>6.6</v>
       </c>
       <c r="AQ15" t="n">
-        <v>4.4</v>
+        <v>7</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.5</v>
+        <v>16.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.5</v>
+        <v>36</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.37</v>
+        <v>5.8</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.37</v>
+        <v>6</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.49</v>
+        <v>13</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.51</v>
+        <v>24</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.47</v>
+        <v>12.5</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.46</v>
+        <v>10.5</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.48</v>
+        <v>19</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.51</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.5</v>
+        <v>32</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.48</v>
+        <v>30</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.51</v>
+        <v>30</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.51</v>
+        <v>10.5</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.55</v>
+        <v>9.4</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.55</v>
+        <v>9.6</v>
       </c>
       <c r="BH15" t="n">
-        <v>1000</v>
+        <v>2.6</v>
       </c>
       <c r="BI15" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="BJ15" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK15" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BN15" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BP15" t="n">
         <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BT15" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU15" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-14 07:32:00</t>
+          <t>2026-07-14 09:40:53</t>
         </is>
       </c>
     </row>
@@ -4413,37 +4413,37 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="G16" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="H16" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="I16" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="J16" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="K16" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="L16" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="M16" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N16" t="n">
         <v>2.42</v>
       </c>
       <c r="O16" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="P16" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="Q16" t="n">
         <v>2.8</v>
@@ -4452,52 +4452,52 @@
         <v>1.15</v>
       </c>
       <c r="S16" t="n">
-        <v>2.84</v>
+        <v>5.9</v>
       </c>
       <c r="T16" t="n">
-        <v>1.78</v>
+        <v>2.18</v>
       </c>
       <c r="U16" t="n">
-        <v>1.37</v>
+        <v>1.65</v>
       </c>
       <c r="V16" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W16" t="n">
         <v>1.31</v>
       </c>
       <c r="X16" t="n">
-        <v>970</v>
+        <v>9.4</v>
       </c>
       <c r="Y16" t="n">
-        <v>970</v>
+        <v>7.2</v>
       </c>
       <c r="Z16" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AA16" t="n">
-        <v>900</v>
+        <v>130</v>
       </c>
       <c r="AB16" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AC16" t="n">
-        <v>42</v>
+        <v>7.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="AF16" t="n">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="AG16" t="n">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>500</v>
+        <v>29</v>
       </c>
       <c r="AI16" t="n">
         <v>540</v>
@@ -4515,128 +4515,128 @@
         <v>500</v>
       </c>
       <c r="AN16" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AO16" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.47</v>
+        <v>6.4</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.36</v>
+        <v>5.6</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.43</v>
+        <v>9.6</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.46</v>
+        <v>15</v>
       </c>
       <c r="AT16" t="n">
-        <v>4.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.33</v>
+        <v>6</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.4</v>
+        <v>10</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.46</v>
+        <v>6</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.46</v>
+        <v>8.4</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.45</v>
+        <v>14.5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.44</v>
+        <v>21</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.46</v>
+        <v>6.4</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.47</v>
+        <v>6.6</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.47</v>
+        <v>6.4</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.47</v>
+        <v>6.6</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.47</v>
+        <v>6.8</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.55</v>
+        <v>6.6</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.55</v>
+        <v>6</v>
       </c>
       <c r="BH16" t="n">
-        <v>1000</v>
+        <v>2.7</v>
       </c>
       <c r="BI16" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="BJ16" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK16" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BN16" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BP16" t="n">
         <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BT16" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BU16" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BV16" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BZ16" t="n">
         <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-14 07:32:00</t>
+          <t>2026-07-14 09:40:53</t>
         </is>
       </c>
     </row>
@@ -4667,220 +4667,220 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="G17" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="H17" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="I17" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="J17" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="K17" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L17" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="M17" t="n">
         <v>1.02</v>
       </c>
       <c r="N17" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="O17" t="n">
         <v>1.14</v>
       </c>
       <c r="P17" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="R17" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="S17" t="n">
         <v>2.08</v>
       </c>
       <c r="T17" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="U17" t="n">
-        <v>1.01</v>
+        <v>2.9</v>
       </c>
       <c r="V17" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="W17" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="X17" t="n">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="Y17" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>500</v>
+        <v>24</v>
       </c>
       <c r="AB17" t="n">
-        <v>500</v>
+        <v>27</v>
       </c>
       <c r="AC17" t="n">
-        <v>95</v>
+        <v>12</v>
       </c>
       <c r="AD17" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AF17" t="n">
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="AG17" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AH17" t="n">
-        <v>130</v>
+        <v>16</v>
       </c>
       <c r="AI17" t="n">
-        <v>500</v>
+        <v>24</v>
       </c>
       <c r="AJ17" t="n">
-        <v>500</v>
+        <v>170</v>
       </c>
       <c r="AK17" t="n">
-        <v>500</v>
+        <v>38</v>
       </c>
       <c r="AL17" t="n">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AM17" t="n">
-        <v>580</v>
+        <v>50</v>
       </c>
       <c r="AN17" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AO17" t="n">
-        <v>85</v>
+        <v>6.8</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.82</v>
+        <v>28</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.74</v>
+        <v>14</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.75</v>
+        <v>13.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.78</v>
+        <v>18</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.82</v>
+        <v>22</v>
       </c>
       <c r="AU17" t="n">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="AV17" t="n">
-        <v>6.2</v>
+        <v>9.4</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.75</v>
+        <v>13.5</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.83</v>
+        <v>17.5</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.78</v>
+        <v>15</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.73</v>
+        <v>13</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.79</v>
+        <v>19.5</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.85</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.84</v>
+        <v>32</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.83</v>
+        <v>16.5</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.85</v>
+        <v>36</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.87</v>
+        <v>18.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.93</v>
+        <v>5.5</v>
       </c>
       <c r="BH17" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BI17" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BJ17" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK17" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BL17" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BM17" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BN17" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BP17" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BQ17" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR17" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BS17" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BT17" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BU17" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BV17" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BW17" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX17" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BZ17" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-14 07:32:00</t>
+          <t>2026-07-14 09:40:53</t>
         </is>
       </c>
     </row>
@@ -4921,220 +4921,220 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="G18" t="n">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="H18" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="I18" t="n">
-        <v>8.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="J18" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="K18" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="L18" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M18" t="n">
         <v>1.03</v>
       </c>
       <c r="N18" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W18" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="X18" t="n">
+        <v>27</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>28</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>170</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>16</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>28</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN18" t="n">
         <v>6</v>
       </c>
-      <c r="O18" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W18" t="n">
-        <v>3</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1000</v>
-      </c>
       <c r="AO18" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BH18" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BI18" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BJ18" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BK18" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BN18" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BP18" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BQ18" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BR18" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BS18" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BT18" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BU18" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BV18" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BW18" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BX18" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BZ18" t="n">
         <v>0</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-14 07:32:00</t>
+          <t>2026-07-14 09:40:53</t>
         </is>
       </c>
     </row>
@@ -5178,227 +5178,227 @@
         <v>3.1</v>
       </c>
       <c r="G19" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H19" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="I19" t="n">
         <v>3.1</v>
       </c>
       <c r="J19" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="K19" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="L19" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="M19" t="n">
         <v>1.18</v>
       </c>
       <c r="N19" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="O19" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="P19" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="Q19" t="n">
         <v>3.2</v>
       </c>
       <c r="R19" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="S19" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="T19" t="n">
-        <v>1.88</v>
+        <v>2.32</v>
       </c>
       <c r="U19" t="n">
-        <v>1.56</v>
+        <v>1.68</v>
       </c>
       <c r="V19" t="n">
         <v>1.48</v>
       </c>
       <c r="W19" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X19" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="Y19" t="n">
-        <v>970</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z19" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AA19" t="n">
         <v>60</v>
       </c>
       <c r="AB19" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC19" t="n">
-        <v>970</v>
+        <v>6.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AE19" t="n">
         <v>55</v>
       </c>
       <c r="AF19" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AG19" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AH19" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI19" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AJ19" t="n">
         <v>65</v>
       </c>
       <c r="AK19" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AL19" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AM19" t="n">
-        <v>320</v>
+        <v>260</v>
       </c>
       <c r="AN19" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AO19" t="n">
         <v>75</v>
       </c>
       <c r="AP19" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="AQ19" t="n">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="AR19" t="n">
-        <v>2.4</v>
+        <v>15</v>
       </c>
       <c r="AS19" t="n">
-        <v>10.5</v>
+        <v>48</v>
       </c>
       <c r="AT19" t="n">
-        <v>4.3</v>
+        <v>7.4</v>
       </c>
       <c r="AU19" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW19" t="n">
-        <v>2.68</v>
+        <v>46</v>
       </c>
       <c r="AX19" t="n">
         <v>16.5</v>
       </c>
       <c r="AY19" t="n">
-        <v>7</v>
+        <v>14.5</v>
       </c>
       <c r="AZ19" t="n">
         <v>23</v>
       </c>
       <c r="BA19" t="n">
-        <v>2.74</v>
+        <v>13</v>
       </c>
       <c r="BB19" t="n">
-        <v>2.7</v>
+        <v>50</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.68</v>
+        <v>48</v>
       </c>
       <c r="BD19" t="n">
-        <v>2.74</v>
+        <v>36</v>
       </c>
       <c r="BE19" t="n">
-        <v>2.78</v>
+        <v>13.5</v>
       </c>
       <c r="BF19" t="n">
-        <v>2.72</v>
+        <v>12.5</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.7</v>
+        <v>60</v>
       </c>
       <c r="BH19" t="n">
-        <v>1000</v>
+        <v>2.56</v>
       </c>
       <c r="BI19" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="BJ19" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK19" t="n">
-        <v>4.5</v>
+        <v>5.9</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="BN19" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BO19" t="n">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="BP19" t="n">
         <v>1000</v>
       </c>
       <c r="BQ19" t="n">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="BR19" t="n">
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>7</v>
+        <v>9.4</v>
       </c>
       <c r="BT19" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BU19" t="n">
-        <v>3</v>
+        <v>4.9</v>
       </c>
       <c r="BV19" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW19" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX19" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY19" t="n">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BZ19" t="n">
         <v>1000</v>
       </c>
       <c r="CA19" t="n">
-        <v>7.2</v>
+        <v>9.6</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-14 07:32:00</t>
+          <t>2026-07-14 09:40:53</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB19"/>
+  <dimension ref="A1:CB18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Chinese Super League</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,251 +843,251 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>08:35:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Zhejiang Greentown</t>
+          <t>HK Kopavogur</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Qingdao Hainiu</t>
+          <t>IR Reykjavik</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.25</v>
+        <v>1.68</v>
       </c>
       <c r="G2" t="n">
-        <v>1.26</v>
+        <v>1.73</v>
       </c>
       <c r="H2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K2" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N2" t="n">
+        <v>11</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="P2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W2" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="X2" t="n">
+        <v>140</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>80</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>140</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>500</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>22</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AO2" t="n">
         <v>19.5</v>
       </c>
-      <c r="I2" t="n">
+      <c r="AP2" t="n">
+        <v>42</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT2" t="n">
         <v>20</v>
       </c>
-      <c r="J2" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="K2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="P2" t="n">
+      <c r="AU2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>16</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>19</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BF2" t="n">
         <v>2.24</v>
       </c>
-      <c r="Q2" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S2" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>32</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>190</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>160</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>14</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>220</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>420</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>28</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>130</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>23</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>110</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>12</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>40</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>200</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BG2" t="n">
-        <v>110</v>
+        <v>15.5</v>
       </c>
       <c r="BH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BP2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BR2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BV2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BX2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-14 09:40:53</t>
+          <t>2026-07-14 11:49:16</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,244 +1097,244 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>HK Kopavogur</t>
+          <t>CS Dock Sud</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>Uai Urquiza</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="G3" t="n">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>5.7</v>
       </c>
       <c r="I3" t="n">
-        <v>4.4</v>
+        <v>6.6</v>
       </c>
       <c r="J3" t="n">
-        <v>4.8</v>
+        <v>3.15</v>
       </c>
       <c r="K3" t="n">
-        <v>5.4</v>
+        <v>3.65</v>
       </c>
       <c r="L3" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="R3" t="n">
         <v>1.18</v>
       </c>
-      <c r="M3" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N3" t="n">
+      <c r="S3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="X3" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>280</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>38</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW3" t="n">
         <v>10</v>
       </c>
-      <c r="O3" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="P3" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="U3" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W3" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="X3" t="n">
-        <v>90</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>55</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>70</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>470</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>25</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>16</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG3" t="n">
+      <c r="AX3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ3" t="n">
         <v>13.5</v>
       </c>
-      <c r="AH3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>32</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>55</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>40</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>32</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>40</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>55</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>20</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>13</v>
-      </c>
-      <c r="AV3" t="n">
+      <c r="BA3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BB3" t="n">
         <v>17.5</v>
       </c>
-      <c r="AW3" t="n">
-        <v>30</v>
-      </c>
-      <c r="AX3" t="n">
+      <c r="BC3" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF3" t="n">
         <v>18</v>
       </c>
-      <c r="AY3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>24</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>17</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>20</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BG3" t="n">
-        <v>14.5</v>
+        <v>10</v>
       </c>
       <c r="BH3" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BJ3" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BL3" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BN3" t="n">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BP3" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BR3" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BT3" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BV3" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BX3" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BZ3" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-14 09:40:53</t>
+          <t>2026-07-14 11:49:16</t>
         </is>
       </c>
     </row>
@@ -1356,31 +1356,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Camioneros</t>
+          <t>Flandria</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CSD Liniers de Ciudad Evita</t>
+          <t>Argentino de Merlo</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="G4" t="n">
-        <v>2.24</v>
+        <v>2.62</v>
       </c>
       <c r="H4" t="n">
-        <v>4.7</v>
+        <v>3.55</v>
       </c>
       <c r="I4" t="n">
-        <v>5.1</v>
+        <v>4</v>
       </c>
       <c r="J4" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="K4" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="L4" t="n">
         <v>1.62</v>
@@ -1395,7 +1395,7 @@
         <v>1.59</v>
       </c>
       <c r="P4" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="Q4" t="n">
         <v>2.8</v>
@@ -1407,124 +1407,124 @@
         <v>6</v>
       </c>
       <c r="T4" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="U4" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="V4" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="W4" t="n">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="X4" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z4" t="n">
-        <v>500</v>
+        <v>26</v>
       </c>
       <c r="AA4" t="n">
-        <v>900</v>
+        <v>170</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AC4" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AE4" t="n">
-        <v>700</v>
+        <v>250</v>
       </c>
       <c r="AF4" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="AI4" t="n">
-        <v>700</v>
+        <v>340</v>
       </c>
       <c r="AJ4" t="n">
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="AK4" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="AL4" t="n">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="AM4" t="n">
         <v>500</v>
       </c>
       <c r="AN4" t="n">
-        <v>600</v>
+        <v>44</v>
       </c>
       <c r="AO4" t="n">
-        <v>600</v>
+        <v>120</v>
       </c>
       <c r="AP4" t="n">
         <v>6.6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR4" t="n">
-        <v>13.5</v>
+        <v>21</v>
       </c>
       <c r="AS4" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BE4" t="n">
         <v>9.4</v>
       </c>
-      <c r="AT4" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>12</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BF4" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BG4" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BH4" t="n">
         <v>2.66</v>
@@ -1536,59 +1536,59 @@
         <v>12.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BN4" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="BP4" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="BQ4" t="n">
         <v>7.4</v>
       </c>
       <c r="BR4" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BS4" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BT4" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BV4" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BW4" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="BX4" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BY4" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="CA4" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-14 09:40:53</t>
+          <t>2026-07-14 11:49:16</t>
         </is>
       </c>
     </row>
@@ -1610,49 +1610,49 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Argentino de Quilmes</t>
+          <t>Sportivo Italiano</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandi</t>
+          <t>Villa San Carlos</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>5.7</v>
+        <v>1.74</v>
       </c>
       <c r="G5" t="n">
-        <v>7</v>
+        <v>1.86</v>
       </c>
       <c r="H5" t="n">
-        <v>1.8</v>
+        <v>6</v>
       </c>
       <c r="I5" t="n">
-        <v>1.92</v>
+        <v>7.2</v>
       </c>
       <c r="J5" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="K5" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="L5" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="M5" t="n">
         <v>1.13</v>
       </c>
       <c r="N5" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="O5" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="P5" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="R5" t="n">
         <v>1.17</v>
@@ -1667,182 +1667,182 @@
         <v>1.6</v>
       </c>
       <c r="V5" t="n">
-        <v>2.08</v>
+        <v>1.16</v>
       </c>
       <c r="W5" t="n">
-        <v>1.18</v>
+        <v>2.16</v>
       </c>
       <c r="X5" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.2</v>
+        <v>15.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>9.6</v>
+        <v>55</v>
       </c>
       <c r="AA5" t="n">
-        <v>23</v>
+        <v>900</v>
       </c>
       <c r="AB5" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD5" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>700</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AG5" t="n">
         <v>12</v>
       </c>
-      <c r="AE5" t="n">
-        <v>29</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>55</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>32</v>
-      </c>
       <c r="AH5" t="n">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="AI5" t="n">
+        <v>700</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL5" t="n">
         <v>160</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>500</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>500</v>
       </c>
       <c r="AM5" t="n">
         <v>500</v>
       </c>
       <c r="AN5" t="n">
-        <v>330</v>
+        <v>26</v>
       </c>
       <c r="AO5" t="n">
-        <v>24</v>
+        <v>310</v>
       </c>
       <c r="AP5" t="n">
         <v>7.2</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5.1</v>
+        <v>12.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>7.8</v>
+        <v>19.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>17.5</v>
+        <v>9</v>
       </c>
       <c r="AT5" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="AU5" t="n">
         <v>7</v>
       </c>
       <c r="AV5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY5" t="n">
         <v>9.4</v>
       </c>
-      <c r="AW5" t="n">
-        <v>20</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>30</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>17.5</v>
-      </c>
       <c r="AZ5" t="n">
-        <v>19</v>
+        <v>13.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="BB5" t="n">
-        <v>8.6</v>
+        <v>16.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>8.4</v>
+        <v>15</v>
       </c>
       <c r="BD5" t="n">
-        <v>8.4</v>
+        <v>28</v>
       </c>
       <c r="BE5" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF5" t="n">
-        <v>8.6</v>
+        <v>18</v>
       </c>
       <c r="BG5" t="n">
-        <v>18.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="BJ5" t="n">
         <v>13.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>8.4</v>
+        <v>6.2</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
+        <v>11</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>44</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>10</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>8</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>10</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY5" t="n">
         <v>10.5</v>
       </c>
-      <c r="BN5" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>10</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>15</v>
-      </c>
-      <c r="BW5" t="n">
+      <c r="BZ5" t="n">
+        <v>42</v>
+      </c>
+      <c r="CA5" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BX5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>9</v>
-      </c>
-      <c r="BZ5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>9</v>
-      </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-14 09:40:53</t>
+          <t>2026-07-14 11:49:16</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="G6" t="n">
         <v>4.2</v>
       </c>
       <c r="H6" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="I6" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="J6" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="K6" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L6" t="n">
         <v>1.55</v>
@@ -1900,7 +1900,7 @@
         <v>2.68</v>
       </c>
       <c r="O6" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="P6" t="n">
         <v>1.54</v>
@@ -1912,16 +1912,16 @@
         <v>1.19</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="T6" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U6" t="n">
         <v>1.75</v>
       </c>
       <c r="V6" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="W6" t="n">
         <v>1.33</v>
@@ -1936,7 +1936,7 @@
         <v>14.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AB6" t="n">
         <v>11.5</v>
@@ -1954,7 +1954,7 @@
         <v>28</v>
       </c>
       <c r="AG6" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AH6" t="n">
         <v>25</v>
@@ -1963,76 +1963,76 @@
         <v>65</v>
       </c>
       <c r="AJ6" t="n">
-        <v>250</v>
+        <v>140</v>
       </c>
       <c r="AK6" t="n">
         <v>70</v>
       </c>
       <c r="AL6" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="AM6" t="n">
         <v>500</v>
       </c>
       <c r="AN6" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AO6" t="n">
         <v>36</v>
       </c>
       <c r="AP6" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AQ6" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AR6" t="n">
         <v>11</v>
       </c>
       <c r="AS6" t="n">
-        <v>24</v>
+        <v>15.5</v>
       </c>
       <c r="AT6" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AU6" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV6" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AW6" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="AX6" t="n">
         <v>21</v>
       </c>
       <c r="AY6" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AZ6" t="n">
         <v>18.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BB6" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BC6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BD6" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="BE6" t="n">
         <v>7.4</v>
       </c>
       <c r="BF6" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BG6" t="n">
-        <v>24</v>
+        <v>6.8</v>
       </c>
       <c r="BH6" t="n">
         <v>2.88</v>
@@ -2044,19 +2044,19 @@
         <v>12</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN6" t="n">
         <v>7.2</v>
       </c>
       <c r="BO6" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BP6" t="n">
         <v>40</v>
@@ -2077,7 +2077,7 @@
         <v>3.8</v>
       </c>
       <c r="BV6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BW6" t="n">
         <v>6.6</v>
@@ -2092,18 +2092,18 @@
         <v>50</v>
       </c>
       <c r="CA6" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-14 09:40:53</t>
+          <t>2026-07-14 11:49:16</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2118,239 +2118,239 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Grotta</t>
+          <t>Argentino de Quilmes</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Grindavik</t>
+          <t>Arsenal de Sarandi</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.22</v>
+        <v>5.7</v>
       </c>
       <c r="G7" t="n">
-        <v>2.3</v>
+        <v>7</v>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>1.77</v>
       </c>
       <c r="I7" t="n">
-        <v>3.15</v>
+        <v>1.91</v>
       </c>
       <c r="J7" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="K7" t="n">
-        <v>4.5</v>
+        <v>3.65</v>
       </c>
       <c r="L7" t="n">
-        <v>1.24</v>
+        <v>1.61</v>
       </c>
       <c r="M7" t="n">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="N7" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V7" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X7" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>110</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>32</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>160</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>500</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>350</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AU7" t="n">
         <v>7.2</v>
       </c>
-      <c r="O7" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="P7" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="X7" t="n">
-        <v>36</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>23</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>29</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>55</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>20</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>27</v>
-      </c>
-      <c r="AF7" t="n">
+      <c r="AV7" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY7" t="n">
         <v>22</v>
       </c>
-      <c r="AG7" t="n">
+      <c r="AZ7" t="n">
         <v>13</v>
       </c>
-      <c r="AH7" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>28</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>25</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>44</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>14</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>22</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BA7" t="n">
-        <v>13.5</v>
+        <v>8.6</v>
       </c>
       <c r="BB7" t="n">
-        <v>17</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC7" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="BD7" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="BE7" t="n">
-        <v>34</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF7" t="n">
         <v>8</v>
       </c>
       <c r="BG7" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="BH7" t="n">
-        <v>5.2</v>
+        <v>2.78</v>
       </c>
       <c r="BI7" t="n">
-        <v>4.5</v>
+        <v>2.24</v>
       </c>
       <c r="BJ7" t="n">
-        <v>8.4</v>
+        <v>13.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
+        <v>11</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ7" t="n">
         <v>10</v>
       </c>
-      <c r="BN7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BP7" t="n">
+      <c r="BR7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>10</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BV7" t="n">
         <v>14.5</v>
       </c>
-      <c r="BQ7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>20</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>6</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>20</v>
-      </c>
       <c r="BW7" t="n">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="BX7" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ7" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>6.2</v>
+        <v>9</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-14 09:40:53</t>
+          <t>2026-07-14 11:49:16</t>
         </is>
       </c>
     </row>
@@ -2372,31 +2372,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Flandria</t>
+          <t>Camioneros</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Argentino de Merlo</t>
+          <t>CSD Liniers de Ciudad Evita</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.34</v>
+        <v>2.08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.56</v>
+        <v>2.24</v>
       </c>
       <c r="H8" t="n">
-        <v>3.55</v>
+        <v>4.7</v>
       </c>
       <c r="I8" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="J8" t="n">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="K8" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="L8" t="n">
         <v>1.62</v>
@@ -2408,7 +2408,7 @@
         <v>2.46</v>
       </c>
       <c r="O8" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="P8" t="n">
         <v>1.46</v>
@@ -2423,58 +2423,58 @@
         <v>6</v>
       </c>
       <c r="T8" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="U8" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="V8" t="n">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="W8" t="n">
-        <v>1.64</v>
+        <v>1.81</v>
       </c>
       <c r="X8" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="Y8" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="Z8" t="n">
-        <v>27</v>
+        <v>500</v>
       </c>
       <c r="AA8" t="n">
-        <v>250</v>
+        <v>900</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AC8" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AE8" t="n">
-        <v>160</v>
+        <v>700</v>
       </c>
       <c r="AF8" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AG8" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>26</v>
+        <v>75</v>
       </c>
       <c r="AI8" t="n">
-        <v>340</v>
+        <v>700</v>
       </c>
       <c r="AJ8" t="n">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="AK8" t="n">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="AL8" t="n">
         <v>210</v>
@@ -2483,135 +2483,135 @@
         <v>500</v>
       </c>
       <c r="AN8" t="n">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="AO8" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="AP8" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AQ8" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AR8" t="n">
-        <v>21</v>
+        <v>13.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT8" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="AU8" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV8" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>20</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX8" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY8" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ8" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="BA8" t="n">
         <v>9</v>
       </c>
       <c r="BB8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BD8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BE8" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BF8" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BG8" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BH8" t="n">
-        <v>2.66</v>
+        <v>1000</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="BJ8" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN8" t="n">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="BO8" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BP8" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BT8" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BV8" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BX8" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-14 09:40:53</t>
+          <t>2026-07-14 11:49:16</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2626,239 +2626,239 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CS Dock Sud</t>
+          <t>Grotta</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Uai Urquiza</t>
+          <t>Grindavik</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.82</v>
+        <v>2.18</v>
       </c>
       <c r="G9" t="n">
-        <v>1.9</v>
+        <v>2.26</v>
       </c>
       <c r="H9" t="n">
-        <v>5.8</v>
+        <v>3.05</v>
       </c>
       <c r="I9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="X9" t="n">
+        <v>42</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>26</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>28</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>24</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>38</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>18</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>27</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>30</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN9" t="n">
         <v>6.2</v>
       </c>
-      <c r="J9" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="N9" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S9" t="n">
+      <c r="BO9" t="n">
         <v>5.3</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="W9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="X9" t="n">
-        <v>9</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>900</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>27</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>500</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>160</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>22</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>290</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>17</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>32</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>13</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>13</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>3.6</v>
       </c>
       <c r="BP9" t="n">
         <v>14.5</v>
       </c>
       <c r="BQ9" t="n">
-        <v>10</v>
+        <v>7.6</v>
       </c>
       <c r="BR9" t="n">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="BS9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BT9" t="n">
-        <v>9.6</v>
+        <v>7.2</v>
       </c>
       <c r="BU9" t="n">
         <v>6.2</v>
       </c>
       <c r="BV9" t="n">
-        <v>95</v>
+        <v>20</v>
       </c>
       <c r="BW9" t="n">
-        <v>11.5</v>
+        <v>8.4</v>
       </c>
       <c r="BX9" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BY9" t="n">
-        <v>11.5</v>
+        <v>8.6</v>
       </c>
       <c r="BZ9" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="CA9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-14 09:40:53</t>
+          <t>2026-07-14 11:49:16</t>
         </is>
       </c>
     </row>
@@ -2875,251 +2875,251 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Sportivo Italiano</t>
+          <t>Deportivo Armenio</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Villa San Carlos</t>
+          <t>Talleres (RE)</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.75</v>
+        <v>3.95</v>
       </c>
       <c r="G10" t="n">
-        <v>1.86</v>
+        <v>4.4</v>
       </c>
       <c r="H10" t="n">
-        <v>6</v>
+        <v>2.66</v>
       </c>
       <c r="I10" t="n">
-        <v>7.4</v>
+        <v>2.74</v>
       </c>
       <c r="J10" t="n">
-        <v>3.4</v>
+        <v>2.52</v>
       </c>
       <c r="K10" t="n">
-        <v>3.75</v>
+        <v>2.7</v>
       </c>
       <c r="L10" t="n">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="M10" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="N10" t="n">
-        <v>2.56</v>
+        <v>2.34</v>
       </c>
       <c r="O10" t="n">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="P10" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.74</v>
+        <v>3.05</v>
       </c>
       <c r="R10" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="S10" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="T10" t="n">
-        <v>2.34</v>
+        <v>1.11</v>
       </c>
       <c r="U10" t="n">
-        <v>1.59</v>
+        <v>1.11</v>
       </c>
       <c r="V10" t="n">
-        <v>1.17</v>
+        <v>1.57</v>
       </c>
       <c r="W10" t="n">
-        <v>2.16</v>
+        <v>1.31</v>
       </c>
       <c r="X10" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="Y10" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="Z10" t="n">
-        <v>55</v>
+        <v>970</v>
       </c>
       <c r="AA10" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB10" t="n">
-        <v>6.2</v>
+        <v>970</v>
       </c>
       <c r="AC10" t="n">
-        <v>8.6</v>
+        <v>970</v>
       </c>
       <c r="AD10" t="n">
-        <v>30</v>
+        <v>970</v>
       </c>
       <c r="AE10" t="n">
-        <v>220</v>
+        <v>500</v>
       </c>
       <c r="AF10" t="n">
-        <v>9.6</v>
+        <v>500</v>
       </c>
       <c r="AG10" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AH10" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AI10" t="n">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="AJ10" t="n">
-        <v>22</v>
+        <v>500</v>
       </c>
       <c r="AK10" t="n">
-        <v>28</v>
+        <v>500</v>
       </c>
       <c r="AL10" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AM10" t="n">
         <v>500</v>
       </c>
       <c r="AN10" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>860</v>
+        <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>7.2</v>
+        <v>5.4</v>
       </c>
       <c r="AQ10" t="n">
-        <v>12.5</v>
+        <v>3.1</v>
       </c>
       <c r="AR10" t="n">
-        <v>30</v>
+        <v>2.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>8</v>
+        <v>1.2</v>
       </c>
       <c r="AT10" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="AU10" t="n">
-        <v>6.8</v>
+        <v>4.2</v>
       </c>
       <c r="AV10" t="n">
-        <v>19</v>
+        <v>5.1</v>
       </c>
       <c r="AW10" t="n">
-        <v>9.199999999999999</v>
+        <v>1.34</v>
       </c>
       <c r="AX10" t="n">
-        <v>7.6</v>
+        <v>1.2</v>
       </c>
       <c r="AY10" t="n">
-        <v>9.6</v>
+        <v>1.19</v>
       </c>
       <c r="AZ10" t="n">
-        <v>24</v>
+        <v>1.21</v>
       </c>
       <c r="BA10" t="n">
-        <v>9.199999999999999</v>
+        <v>1.21</v>
       </c>
       <c r="BB10" t="n">
-        <v>16.5</v>
+        <v>1.21</v>
       </c>
       <c r="BC10" t="n">
-        <v>21</v>
+        <v>1.21</v>
       </c>
       <c r="BD10" t="n">
-        <v>36</v>
+        <v>1.21</v>
       </c>
       <c r="BE10" t="n">
-        <v>28</v>
+        <v>1.21</v>
       </c>
       <c r="BF10" t="n">
-        <v>17.5</v>
+        <v>1.55</v>
       </c>
       <c r="BG10" t="n">
-        <v>8.199999999999999</v>
+        <v>1.55</v>
       </c>
       <c r="BH10" t="n">
-        <v>2.8</v>
+        <v>1000</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.22</v>
+        <v>2.06</v>
       </c>
       <c r="BJ10" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BN10" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="BP10" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BR10" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BT10" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BU10" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BZ10" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-14 09:40:53</t>
+          <t>2026-07-14 11:49:16</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3129,251 +3129,251 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Deportivo Armenio</t>
+          <t>Macara</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Talleres (RE)</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="F11" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H11" t="n">
         <v>3.85</v>
       </c>
-      <c r="G11" t="n">
+      <c r="I11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="X11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>270</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>100</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>22</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>60</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>40</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>46</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>65</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>17</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>46</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BO11" t="n">
         <v>4.3</v>
       </c>
-      <c r="H11" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="I11" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="J11" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="K11" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="N11" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="S11" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X11" t="n">
-        <v>16</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>970</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>970</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>500</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>500</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>500</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>500</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>500</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>500</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BP11" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR11" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BT11" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BU11" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BV11" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BX11" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA11" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-14 09:40:53</t>
+          <t>2026-07-14 11:49:16</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3383,244 +3383,244 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Macara</t>
+          <t>Brown de Adrogue</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Deportivo Laferrere</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.08</v>
+        <v>2.6</v>
       </c>
       <c r="G12" t="n">
-        <v>2.16</v>
+        <v>2.96</v>
       </c>
       <c r="H12" t="n">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="I12" t="n">
-        <v>4.3</v>
+        <v>3.65</v>
       </c>
       <c r="J12" t="n">
-        <v>3.4</v>
+        <v>2.78</v>
       </c>
       <c r="K12" t="n">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="L12" t="n">
-        <v>1.48</v>
+        <v>1.63</v>
       </c>
       <c r="M12" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="N12" t="n">
-        <v>3.25</v>
+        <v>2.56</v>
       </c>
       <c r="O12" t="n">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="P12" t="n">
-        <v>1.75</v>
+        <v>1.47</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.24</v>
+        <v>2.78</v>
       </c>
       <c r="R12" t="n">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="S12" t="n">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="T12" t="n">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="U12" t="n">
-        <v>1.91</v>
+        <v>1.69</v>
       </c>
       <c r="V12" t="n">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="W12" t="n">
-        <v>1.86</v>
+        <v>1.51</v>
       </c>
       <c r="X12" t="n">
-        <v>11.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y12" t="n">
-        <v>13</v>
+        <v>9.6</v>
       </c>
       <c r="Z12" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AA12" t="n">
-        <v>900</v>
+        <v>75</v>
       </c>
       <c r="AB12" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC12" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD12" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF12" t="n">
         <v>17.5</v>
       </c>
-      <c r="AE12" t="n">
-        <v>70</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AG12" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AI12" t="n">
-        <v>90</v>
+        <v>330</v>
       </c>
       <c r="AJ12" t="n">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="AK12" t="n">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="AL12" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AM12" t="n">
         <v>500</v>
       </c>
       <c r="AN12" t="n">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="AO12" t="n">
-        <v>230</v>
+        <v>80</v>
       </c>
       <c r="AP12" t="n">
-        <v>10</v>
+        <v>6.4</v>
       </c>
       <c r="AQ12" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY12" t="n">
         <v>11</v>
       </c>
-      <c r="AR12" t="n">
-        <v>22</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>55</v>
-      </c>
-      <c r="AT12" t="n">
+      <c r="AZ12" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>38</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BD12" t="n">
         <v>7</v>
       </c>
-      <c r="AU12" t="n">
+      <c r="BE12" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF12" t="n">
         <v>6.8</v>
       </c>
-      <c r="AV12" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW12" t="n">
+      <c r="BG12" t="n">
+        <v>7</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>28</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>7</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>60</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BV12" t="n">
         <v>36</v>
       </c>
-      <c r="AX12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>46</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>38</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>29</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>18</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>44</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>16</v>
-      </c>
-      <c r="BQ12" t="n">
+      <c r="BW12" t="n">
         <v>7.6</v>
       </c>
-      <c r="BR12" t="n">
-        <v>34</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>10</v>
-      </c>
-      <c r="BT12" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BU12" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BV12" t="n">
-        <v>38</v>
-      </c>
-      <c r="BW12" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BX12" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="BY12" t="n">
-        <v>11.5</v>
+        <v>8.4</v>
       </c>
       <c r="BZ12" t="n">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="CA12" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-14 09:40:53</t>
+          <t>2026-07-14 11:49:16</t>
         </is>
       </c>
     </row>
@@ -3642,184 +3642,184 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Brown de Adrogue</t>
+          <t>Deportivo Merlo</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Deportivo Laferrere</t>
+          <t>Real Pilar FC</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.62</v>
+        <v>2.84</v>
       </c>
       <c r="G13" t="n">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="H13" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="I13" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="J13" t="n">
-        <v>2.78</v>
+        <v>2.4</v>
       </c>
       <c r="K13" t="n">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="L13" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="M13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R13" t="n">
         <v>1.13</v>
       </c>
-      <c r="N13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.16</v>
-      </c>
       <c r="S13" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="T13" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="U13" t="n">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="V13" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="W13" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="X13" t="n">
-        <v>8.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="Y13" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z13" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AA13" t="n">
-        <v>75</v>
+        <v>260</v>
       </c>
       <c r="AB13" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC13" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AE13" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AF13" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AG13" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AI13" t="n">
-        <v>330</v>
+        <v>500</v>
       </c>
       <c r="AJ13" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AK13" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AL13" t="n">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="AM13" t="n">
         <v>500</v>
       </c>
       <c r="AN13" t="n">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="AO13" t="n">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="AP13" t="n">
-        <v>6.4</v>
+        <v>5.1</v>
       </c>
       <c r="AQ13" t="n">
         <v>7.6</v>
       </c>
       <c r="AR13" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AS13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW13" t="n">
         <v>20</v>
       </c>
-      <c r="AT13" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>7</v>
-      </c>
       <c r="AX13" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AZ13" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB13" t="n">
         <v>20</v>
       </c>
-      <c r="BA13" t="n">
+      <c r="BC13" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF13" t="n">
         <v>7.4</v>
       </c>
-      <c r="BB13" t="n">
-        <v>34</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>27</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>7</v>
-      </c>
       <c r="BG13" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH13" t="n">
-        <v>2.68</v>
+        <v>2.54</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="BJ13" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BK13" t="n">
         <v>5.4</v>
@@ -3828,53 +3828,53 @@
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN13" t="n">
         <v>5.8</v>
       </c>
       <c r="BO13" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BP13" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BQ13" t="n">
         <v>7</v>
       </c>
       <c r="BR13" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BS13" t="n">
+        <v>8</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>38</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY13" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BT13" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BU13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BV13" t="n">
-        <v>36</v>
-      </c>
-      <c r="BW13" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BX13" t="n">
-        <v>65</v>
-      </c>
-      <c r="BY13" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BZ13" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-14 09:40:53</t>
+          <t>2026-07-14 11:49:16</t>
         </is>
       </c>
     </row>
@@ -3896,239 +3896,239 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Deportivo Merlo</t>
+          <t>Comunicaciones B Aires</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Real Pilar FC</t>
+          <t>Villa Dalmine</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="G14" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="H14" t="n">
-        <v>3.45</v>
+        <v>2.94</v>
       </c>
       <c r="I14" t="n">
-        <v>4</v>
+        <v>3.35</v>
       </c>
       <c r="J14" t="n">
-        <v>2.48</v>
+        <v>2.86</v>
       </c>
       <c r="K14" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="L14" t="n">
-        <v>1.74</v>
+        <v>1.64</v>
       </c>
       <c r="M14" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="N14" t="n">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="O14" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="P14" t="n">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.2</v>
+        <v>2.84</v>
       </c>
       <c r="R14" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T14" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="U14" t="n">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="V14" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="W14" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="X14" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="Y14" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="Z14" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AA14" t="n">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="AB14" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>19.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>160</v>
+        <v>240</v>
       </c>
       <c r="AF14" t="n">
         <v>18</v>
       </c>
       <c r="AG14" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AI14" t="n">
         <v>500</v>
       </c>
       <c r="AJ14" t="n">
-        <v>60</v>
+        <v>160</v>
       </c>
       <c r="AK14" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="AL14" t="n">
-        <v>240</v>
+        <v>460</v>
       </c>
       <c r="AM14" t="n">
         <v>500</v>
       </c>
       <c r="AN14" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AO14" t="n">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="AP14" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="AQ14" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AR14" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AS14" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="AT14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU14" t="n">
         <v>6</v>
       </c>
-      <c r="AU14" t="n">
-        <v>5.4</v>
-      </c>
       <c r="AV14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AX14" t="n">
         <v>14.5</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>21</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>13</v>
       </c>
       <c r="AY14" t="n">
         <v>12</v>
       </c>
       <c r="AZ14" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="BA14" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB14" t="n">
-        <v>20</v>
+        <v>7.8</v>
       </c>
       <c r="BC14" t="n">
-        <v>21</v>
+        <v>7.6</v>
       </c>
       <c r="BD14" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE14" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF14" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG14" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH14" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="BJ14" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BK14" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BN14" t="n">
         <v>5.8</v>
       </c>
       <c r="BO14" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BP14" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BT14" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BU14" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BV14" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BZ14" t="n">
         <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-14 09:40:53</t>
+          <t>2026-07-14 11:49:16</t>
         </is>
       </c>
     </row>
@@ -4150,246 +4150,246 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Comunicaciones B Aires</t>
+          <t>CA Ituzaingo</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Villa Dalmine</t>
+          <t>San Martin de Burzaco</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.72</v>
+        <v>3.65</v>
       </c>
       <c r="G15" t="n">
-        <v>3.05</v>
+        <v>4.4</v>
       </c>
       <c r="H15" t="n">
-        <v>2.92</v>
+        <v>2.28</v>
       </c>
       <c r="I15" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="K15" t="n">
         <v>3.3</v>
       </c>
-      <c r="J15" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="K15" t="n">
-        <v>3.15</v>
-      </c>
       <c r="L15" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="M15" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="N15" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="O15" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="P15" t="n">
         <v>1.45</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="R15" t="n">
         <v>1.15</v>
       </c>
       <c r="S15" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="T15" t="n">
         <v>2.18</v>
       </c>
       <c r="U15" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="V15" t="n">
-        <v>1.44</v>
+        <v>1.66</v>
       </c>
       <c r="W15" t="n">
-        <v>1.5</v>
+        <v>1.31</v>
       </c>
       <c r="X15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC15" t="n">
         <v>7.8</v>
       </c>
-      <c r="Y15" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>270</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>7.4</v>
-      </c>
       <c r="AD15" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>220</v>
+        <v>40</v>
       </c>
       <c r="AF15" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="AG15" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AH15" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="AI15" t="n">
-        <v>300</v>
+        <v>170</v>
       </c>
       <c r="AJ15" t="n">
-        <v>160</v>
+        <v>900</v>
       </c>
       <c r="AK15" t="n">
-        <v>65</v>
+        <v>190</v>
       </c>
       <c r="AL15" t="n">
-        <v>460</v>
+        <v>420</v>
       </c>
       <c r="AM15" t="n">
         <v>500</v>
       </c>
       <c r="AN15" t="n">
-        <v>95</v>
+        <v>150</v>
       </c>
       <c r="AO15" t="n">
-        <v>100</v>
+        <v>44</v>
       </c>
       <c r="AP15" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AQ15" t="n">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="AR15" t="n">
-        <v>16.5</v>
+        <v>10.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="AT15" t="n">
-        <v>5.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU15" t="n">
         <v>6</v>
       </c>
       <c r="AV15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BJ15" t="n">
         <v>13</v>
       </c>
-      <c r="AW15" t="n">
-        <v>24</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>32</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>30</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>30</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>12</v>
-      </c>
       <c r="BK15" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>11</v>
+        <v>8.6</v>
       </c>
       <c r="BN15" t="n">
-        <v>5.9</v>
+        <v>7.6</v>
       </c>
       <c r="BO15" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BP15" t="n">
         <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
       <c r="BT15" t="n">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
       <c r="BU15" t="n">
-        <v>5.1</v>
+        <v>3.75</v>
       </c>
       <c r="BV15" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BW15" t="n">
-        <v>8.6</v>
+        <v>6.4</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>9.6</v>
+        <v>7.6</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>9.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-14 09:40:53</t>
+          <t>2026-07-14 11:49:16</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4404,239 +4404,239 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CA Ituzaingo</t>
+          <t>CDT Real Oruro</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>San Martin de Burzaco</t>
+          <t>Always Ready</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="G16" t="n">
         <v>4.4</v>
       </c>
       <c r="H16" t="n">
-        <v>2.24</v>
+        <v>1.78</v>
       </c>
       <c r="I16" t="n">
-        <v>2.5</v>
+        <v>1.86</v>
       </c>
       <c r="J16" t="n">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="K16" t="n">
-        <v>3.35</v>
+        <v>5</v>
       </c>
       <c r="L16" t="n">
-        <v>1.63</v>
+        <v>1.23</v>
       </c>
       <c r="M16" t="n">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="N16" t="n">
-        <v>2.42</v>
+        <v>7.6</v>
       </c>
       <c r="O16" t="n">
-        <v>1.6</v>
+        <v>1.13</v>
       </c>
       <c r="P16" t="n">
-        <v>1.45</v>
+        <v>3.15</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.8</v>
+        <v>1.43</v>
       </c>
       <c r="R16" t="n">
-        <v>1.15</v>
+        <v>1.9</v>
       </c>
       <c r="S16" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V16" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X16" t="n">
+        <v>42</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>23</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>30</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>42</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>23</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>170</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>48</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>19</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>32</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>30</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>38</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>18</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>28</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>29</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BW16" t="n">
         <v>5.9</v>
       </c>
-      <c r="T16" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="X16" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>130</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>110</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>540</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>500</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>150</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>600</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>15</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>6</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>13</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ16" t="n">
+      <c r="BX16" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BY16" t="n">
         <v>7.4</v>
       </c>
-      <c r="BR16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BT16" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BU16" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BV16" t="n">
-        <v>23</v>
-      </c>
-      <c r="BW16" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BX16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY16" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BZ16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA16" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-14 09:40:53</t>
+          <t>2026-07-14 11:49:16</t>
         </is>
       </c>
     </row>
@@ -4653,234 +4653,234 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>CDT Real Oruro</t>
+          <t>Blooming Santa Cruz</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Always Ready</t>
+          <t>CD Gualberto Villarroel</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.75</v>
+        <v>1.49</v>
       </c>
       <c r="G17" t="n">
-        <v>4</v>
+        <v>1.53</v>
       </c>
       <c r="H17" t="n">
-        <v>1.84</v>
+        <v>6.6</v>
       </c>
       <c r="I17" t="n">
-        <v>1.9</v>
+        <v>7.6</v>
       </c>
       <c r="J17" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="K17" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="L17" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="M17" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N17" t="n">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="O17" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="P17" t="n">
-        <v>3.05</v>
+        <v>2.72</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="R17" t="n">
-        <v>1.85</v>
+        <v>1.69</v>
       </c>
       <c r="S17" t="n">
-        <v>2.08</v>
+        <v>2.32</v>
       </c>
       <c r="T17" t="n">
-        <v>1.46</v>
+        <v>1.71</v>
       </c>
       <c r="U17" t="n">
-        <v>2.9</v>
+        <v>2.24</v>
       </c>
       <c r="V17" t="n">
-        <v>2.1</v>
+        <v>1.15</v>
       </c>
       <c r="W17" t="n">
-        <v>1.33</v>
+        <v>2.88</v>
       </c>
       <c r="X17" t="n">
+        <v>27</v>
+      </c>
+      <c r="Y17" t="n">
         <v>36</v>
       </c>
-      <c r="Y17" t="n">
-        <v>18.5</v>
-      </c>
       <c r="Z17" t="n">
-        <v>17.5</v>
+        <v>65</v>
       </c>
       <c r="AA17" t="n">
-        <v>24</v>
+        <v>170</v>
       </c>
       <c r="AB17" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="AC17" t="n">
         <v>12</v>
       </c>
       <c r="AD17" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF17" t="n">
         <v>11.5</v>
       </c>
-      <c r="AE17" t="n">
-        <v>17</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>40</v>
-      </c>
       <c r="AG17" t="n">
-        <v>18</v>
+        <v>12.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="AI17" t="n">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="AJ17" t="n">
-        <v>170</v>
+        <v>14.5</v>
       </c>
       <c r="AK17" t="n">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="AL17" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="AM17" t="n">
-        <v>50</v>
+        <v>95</v>
       </c>
       <c r="AN17" t="n">
-        <v>23</v>
+        <v>5.6</v>
       </c>
       <c r="AO17" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP17" t="n">
         <v>6.8</v>
       </c>
-      <c r="AP17" t="n">
-        <v>28</v>
-      </c>
       <c r="AQ17" t="n">
-        <v>14</v>
+        <v>7.2</v>
       </c>
       <c r="AR17" t="n">
-        <v>13.5</v>
+        <v>8</v>
       </c>
       <c r="AS17" t="n">
-        <v>18</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT17" t="n">
-        <v>22</v>
+        <v>10.5</v>
       </c>
       <c r="AU17" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>8</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BJ17" t="n">
         <v>10</v>
       </c>
-      <c r="AV17" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>15</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>32</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>36</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BK17" t="n">
-        <v>6.8</v>
+        <v>5.6</v>
       </c>
       <c r="BL17" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BM17" t="n">
+        <v>11</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>21</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW17" t="n">
         <v>10</v>
       </c>
-      <c r="BN17" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BO17" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BP17" t="n">
-        <v>27</v>
-      </c>
-      <c r="BQ17" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BR17" t="n">
-        <v>29</v>
-      </c>
-      <c r="BS17" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BT17" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BU17" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BV17" t="n">
-        <v>12</v>
-      </c>
-      <c r="BW17" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BX17" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="BZ17" t="n">
         <v>0</v>
@@ -4890,14 +4890,14 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-14 09:40:53</t>
+          <t>2026-07-14 11:49:16</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4912,493 +4912,239 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Blooming Santa Cruz</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CD Gualberto Villarroel</t>
+          <t>Delfin</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.54</v>
+        <v>2.86</v>
       </c>
       <c r="G18" t="n">
-        <v>1.58</v>
+        <v>2.92</v>
       </c>
       <c r="H18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>48</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>95</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>260</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>65</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP18" t="n">
         <v>6.2</v>
       </c>
-      <c r="I18" t="n">
+      <c r="AQ18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>55</v>
+      </c>
+      <c r="AT18" t="n">
         <v>6.6</v>
       </c>
-      <c r="J18" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="K18" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N18" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W18" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="X18" t="n">
-        <v>27</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>28</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>65</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>170</v>
-      </c>
-      <c r="AB18" t="n">
+      <c r="AU18" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>46</v>
+      </c>
+      <c r="AX18" t="n">
         <v>14.5</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="AY18" t="n">
         <v>13.5</v>
       </c>
-      <c r="AD18" t="n">
-        <v>25</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>85</v>
-      </c>
-      <c r="AF18" t="n">
+      <c r="AZ18" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>44</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>42</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>40</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>14</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>60</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>15</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>10</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>11</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY18" t="n">
         <v>13</v>
       </c>
-      <c r="AG18" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>16</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>16</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>28</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>6</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>80</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>20</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB18" t="n">
+      <c r="BZ18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA18" t="n">
         <v>13</v>
       </c>
-      <c r="BC18" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>10</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>10</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BO18" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BP18" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BQ18" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BR18" t="n">
-        <v>20</v>
-      </c>
-      <c r="BS18" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BT18" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BU18" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BV18" t="n">
-        <v>48</v>
-      </c>
-      <c r="BW18" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BX18" t="n">
-        <v>46</v>
-      </c>
-      <c r="BY18" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BZ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA18" t="n">
-        <v>0</v>
-      </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-14 09:40:53</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Ecuadorian Serie A</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>21:00:00</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Manta FC</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Delfin</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="G19" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="H19" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="I19" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J19" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K19" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="N19" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="S19" t="n">
-        <v>7</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="X19" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>60</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>95</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>65</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>55</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>100</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>260</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>85</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>75</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>6</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>15</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>48</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>46</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>23</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>13</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>50</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>48</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>36</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>60</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BI19" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BJ19" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BK19" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BO19" t="n">
-        <v>5</v>
-      </c>
-      <c r="BP19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ19" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BR19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS19" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BT19" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BU19" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BV19" t="n">
-        <v>32</v>
-      </c>
-      <c r="BW19" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BX19" t="n">
-        <v>65</v>
-      </c>
-      <c r="BY19" t="n">
-        <v>50</v>
-      </c>
-      <c r="BZ19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA19" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="CB19" t="inlineStr">
-        <is>
-          <t>2026-07-14 09:40:53</t>
+          <t>2026-07-14 11:49:16</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-14.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="G2" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="H2" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I2" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="J2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="K2" t="n">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="L2" t="n">
         <v>1.18</v>
@@ -881,154 +881,154 @@
         <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="O2" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="P2" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="R2" t="n">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="S2" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="T2" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="U2" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="V2" t="n">
         <v>1.28</v>
       </c>
       <c r="W2" t="n">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="X2" t="n">
-        <v>140</v>
+        <v>46</v>
       </c>
       <c r="Y2" t="n">
-        <v>80</v>
+        <v>990</v>
       </c>
       <c r="Z2" t="n">
-        <v>140</v>
+        <v>90</v>
       </c>
       <c r="AA2" t="n">
-        <v>500</v>
+        <v>990</v>
       </c>
       <c r="AB2" t="n">
-        <v>970</v>
+        <v>38</v>
       </c>
       <c r="AC2" t="n">
         <v>970</v>
       </c>
       <c r="AD2" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AE2" t="n">
+        <v>95</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ2" t="n">
         <v>120</v>
       </c>
-      <c r="AF2" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH2" t="n">
+      <c r="AK2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>26</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>600</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>36</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>27</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>30</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>28</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>34</v>
+      </c>
+      <c r="AX2" t="n">
         <v>16.5</v>
       </c>
-      <c r="AI2" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK2" t="n">
+      <c r="AY2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA2" t="n">
         <v>28</v>
       </c>
-      <c r="AL2" t="n">
-        <v>22</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>42</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT2" t="n">
+      <c r="BB2" t="n">
         <v>20</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>13</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>16</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>19</v>
       </c>
       <c r="BC2" t="n">
         <v>13</v>
       </c>
       <c r="BD2" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BE2" t="n">
-        <v>19.5</v>
+        <v>36</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.24</v>
+        <v>4.3</v>
       </c>
       <c r="BG2" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BH2" t="n">
         <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.16</v>
+        <v>6</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
@@ -1040,47 +1040,47 @@
         <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="BT2" t="n">
         <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>3.7</v>
+        <v>1.19</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>6.6</v>
+        <v>1.19</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-14 11:49:16</t>
+          <t>2026-07-14 13:57:32</t>
         </is>
       </c>
     </row>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="G3" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="H3" t="n">
         <v>5.7</v>
@@ -1126,7 +1126,7 @@
         <v>3.15</v>
       </c>
       <c r="K3" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L3" t="n">
         <v>1.58</v>
@@ -1138,13 +1138,13 @@
         <v>2.62</v>
       </c>
       <c r="O3" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="P3" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="R3" t="n">
         <v>1.18</v>
@@ -1153,7 +1153,7 @@
         <v>5.5</v>
       </c>
       <c r="T3" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="U3" t="n">
         <v>1.65</v>
@@ -1162,7 +1162,7 @@
         <v>1.17</v>
       </c>
       <c r="W3" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="X3" t="n">
         <v>9</v>
@@ -1177,7 +1177,7 @@
         <v>900</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AC3" t="n">
         <v>8.199999999999999</v>
@@ -1186,10 +1186,10 @@
         <v>27</v>
       </c>
       <c r="AE3" t="n">
-        <v>500</v>
+        <v>260</v>
       </c>
       <c r="AF3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AG3" t="n">
         <v>11.5</v>
@@ -1201,7 +1201,7 @@
         <v>500</v>
       </c>
       <c r="AJ3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK3" t="n">
         <v>27</v>
@@ -1213,28 +1213,28 @@
         <v>500</v>
       </c>
       <c r="AN3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO3" t="n">
         <v>280</v>
       </c>
       <c r="AP3" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AQ3" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AR3" t="n">
         <v>38</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AT3" t="n">
         <v>5.3</v>
       </c>
       <c r="AU3" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV3" t="n">
         <v>21</v>
@@ -1243,25 +1243,25 @@
         <v>10</v>
       </c>
       <c r="AX3" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY3" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ3" t="n">
-        <v>13.5</v>
+        <v>24</v>
       </c>
       <c r="BA3" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BB3" t="n">
         <v>17.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="BD3" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="BE3" t="n">
         <v>10.5</v>
@@ -1270,71 +1270,71 @@
         <v>18</v>
       </c>
       <c r="BG3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>13</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>13</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>42</v>
+      </c>
+      <c r="BS3" t="n">
         <v>10</v>
       </c>
-      <c r="BH3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BT3" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-14 11:49:16</t>
+          <t>2026-07-14 13:57:32</t>
         </is>
       </c>
     </row>
@@ -1371,46 +1371,46 @@
         <v>2.62</v>
       </c>
       <c r="H4" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="I4" t="n">
         <v>4</v>
       </c>
       <c r="J4" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="K4" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L4" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="M4" t="n">
         <v>1.14</v>
       </c>
       <c r="N4" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="O4" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="P4" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="R4" t="n">
         <v>1.16</v>
       </c>
       <c r="S4" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="T4" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="U4" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="V4" t="n">
         <v>1.35</v>
@@ -1419,16 +1419,16 @@
         <v>1.61</v>
       </c>
       <c r="X4" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="Y4" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z4" t="n">
         <v>26</v>
       </c>
       <c r="AA4" t="n">
-        <v>170</v>
+        <v>250</v>
       </c>
       <c r="AB4" t="n">
         <v>7.4</v>
@@ -1437,16 +1437,16 @@
         <v>7.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE4" t="n">
-        <v>250</v>
+        <v>160</v>
       </c>
       <c r="AF4" t="n">
         <v>14.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH4" t="n">
         <v>27</v>
@@ -1458,7 +1458,7 @@
         <v>40</v>
       </c>
       <c r="AK4" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AL4" t="n">
         <v>230</v>
@@ -1467,13 +1467,13 @@
         <v>500</v>
       </c>
       <c r="AN4" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AO4" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AP4" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AQ4" t="n">
         <v>8.199999999999999</v>
@@ -1482,19 +1482,19 @@
         <v>21</v>
       </c>
       <c r="AS4" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AT4" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AU4" t="n">
         <v>6</v>
       </c>
       <c r="AV4" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>20</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX4" t="n">
         <v>11.5</v>
@@ -1503,10 +1503,10 @@
         <v>10.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA4" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BB4" t="n">
         <v>11</v>
@@ -1515,80 +1515,80 @@
         <v>11</v>
       </c>
       <c r="BD4" t="n">
-        <v>8.6</v>
+        <v>28</v>
       </c>
       <c r="BE4" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BF4" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG4" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH4" t="n">
-        <v>2.66</v>
+        <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="BJ4" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN4" t="n">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BP4" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BR4" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BT4" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BV4" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BX4" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-14 11:49:16</t>
+          <t>2026-07-14 13:57:32</t>
         </is>
       </c>
     </row>
@@ -1622,10 +1622,10 @@
         <v>1.74</v>
       </c>
       <c r="G5" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="H5" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I5" t="n">
         <v>7.2</v>
@@ -1646,13 +1646,13 @@
         <v>2.56</v>
       </c>
       <c r="O5" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="P5" t="n">
         <v>1.49</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="R5" t="n">
         <v>1.17</v>
@@ -1670,7 +1670,7 @@
         <v>1.16</v>
       </c>
       <c r="W5" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="X5" t="n">
         <v>8.800000000000001</v>
@@ -1697,7 +1697,7 @@
         <v>700</v>
       </c>
       <c r="AF5" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG5" t="n">
         <v>12</v>
@@ -1712,7 +1712,7 @@
         <v>21</v>
       </c>
       <c r="AK5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL5" t="n">
         <v>160</v>
@@ -1724,10 +1724,10 @@
         <v>26</v>
       </c>
       <c r="AO5" t="n">
-        <v>310</v>
+        <v>370</v>
       </c>
       <c r="AP5" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AQ5" t="n">
         <v>12.5</v>
@@ -1742,7 +1742,7 @@
         <v>5</v>
       </c>
       <c r="AU5" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV5" t="n">
         <v>13</v>
@@ -1751,7 +1751,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AX5" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AY5" t="n">
         <v>9.4</v>
@@ -1763,22 +1763,22 @@
         <v>9</v>
       </c>
       <c r="BB5" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BC5" t="n">
         <v>15</v>
       </c>
       <c r="BD5" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BE5" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BF5" t="n">
         <v>18</v>
       </c>
       <c r="BG5" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BH5" t="n">
         <v>2.76</v>
@@ -1820,7 +1820,7 @@
         <v>10</v>
       </c>
       <c r="BU5" t="n">
-        <v>8</v>
+        <v>5.4</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-14 11:49:16</t>
+          <t>2026-07-14 13:57:32</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="G6" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="H6" t="n">
-        <v>2.24</v>
+        <v>2.06</v>
       </c>
       <c r="I6" t="n">
-        <v>2.48</v>
+        <v>2.18</v>
       </c>
       <c r="J6" t="n">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="K6" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L6" t="n">
         <v>1.55</v>
@@ -1897,64 +1897,64 @@
         <v>1.11</v>
       </c>
       <c r="N6" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="O6" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="P6" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="Q6" t="n">
         <v>2.56</v>
       </c>
       <c r="R6" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S6" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="T6" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="U6" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="V6" t="n">
-        <v>1.68</v>
+        <v>1.84</v>
       </c>
       <c r="W6" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="X6" t="n">
         <v>9.6</v>
       </c>
       <c r="Y6" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="Z6" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AA6" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="AB6" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC6" t="n">
         <v>7.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE6" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AF6" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AG6" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AH6" t="n">
         <v>25</v>
@@ -1963,140 +1963,140 @@
         <v>65</v>
       </c>
       <c r="AJ6" t="n">
-        <v>140</v>
+        <v>900</v>
       </c>
       <c r="AK6" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="AL6" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="AM6" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN6" t="n">
-        <v>500</v>
+        <v>170</v>
       </c>
       <c r="AO6" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="AP6" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AQ6" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>19</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU6" t="n">
         <v>6.4</v>
       </c>
-      <c r="AR6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>6.2</v>
-      </c>
       <c r="AV6" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>25</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>29</v>
+      </c>
+      <c r="BB6" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AW6" t="n">
-        <v>15</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>21</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>14</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>26</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BC6" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BD6" t="n">
         <v>34</v>
       </c>
       <c r="BE6" t="n">
-        <v>7.4</v>
+        <v>9.6</v>
       </c>
       <c r="BF6" t="n">
-        <v>7.2</v>
+        <v>9.4</v>
       </c>
       <c r="BG6" t="n">
-        <v>6.8</v>
+        <v>17</v>
       </c>
       <c r="BH6" t="n">
         <v>2.88</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="BJ6" t="n">
         <v>12</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.3</v>
+        <v>8.4</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BN6" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO6" t="n">
         <v>5.8</v>
       </c>
       <c r="BP6" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="BQ6" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR6" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BS6" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT6" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="BU6" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BV6" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="BW6" t="n">
-        <v>6.6</v>
+        <v>12</v>
       </c>
       <c r="BX6" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="BY6" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BZ6" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="CA6" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-14 11:49:16</t>
+          <t>2026-07-14 13:57:32</t>
         </is>
       </c>
     </row>
@@ -2130,61 +2130,61 @@
         <v>5.7</v>
       </c>
       <c r="G7" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="H7" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="I7" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="J7" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K7" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L7" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="M7" t="n">
         <v>1.12</v>
       </c>
       <c r="N7" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="O7" t="n">
         <v>1.53</v>
       </c>
       <c r="P7" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="R7" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S7" t="n">
         <v>5.5</v>
       </c>
       <c r="T7" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="U7" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="V7" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="W7" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X7" t="n">
         <v>9</v>
       </c>
       <c r="Y7" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="Z7" t="n">
         <v>9.4</v>
@@ -2193,28 +2193,28 @@
         <v>21</v>
       </c>
       <c r="AB7" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD7" t="n">
         <v>12</v>
       </c>
       <c r="AE7" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AF7" t="n">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="AG7" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AH7" t="n">
         <v>34</v>
       </c>
       <c r="AI7" t="n">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="AJ7" t="n">
         <v>900</v>
@@ -2229,25 +2229,25 @@
         <v>500</v>
       </c>
       <c r="AN7" t="n">
-        <v>350</v>
+        <v>320</v>
       </c>
       <c r="AO7" t="n">
         <v>22</v>
       </c>
       <c r="AP7" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AQ7" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AR7" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AS7" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AT7" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AU7" t="n">
         <v>7.2</v>
@@ -2256,40 +2256,40 @@
         <v>9.4</v>
       </c>
       <c r="AW7" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>36</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ7" t="n">
         <v>13.5</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>22</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>13</v>
       </c>
       <c r="BA7" t="n">
         <v>8.6</v>
       </c>
       <c r="BB7" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BC7" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="BD7" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE7" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BF7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BG7" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BH7" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="BI7" t="n">
         <v>2.24</v>
@@ -2298,59 +2298,59 @@
         <v>13.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>6.2</v>
+        <v>9.4</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BN7" t="n">
         <v>10.5</v>
       </c>
       <c r="BO7" t="n">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT7" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BU7" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="BV7" t="n">
         <v>14.5</v>
       </c>
       <c r="BW7" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-14 11:49:16</t>
+          <t>2026-07-14 13:57:32</t>
         </is>
       </c>
     </row>
@@ -2384,34 +2384,34 @@
         <v>2.08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="H8" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I8" t="n">
         <v>5.1</v>
       </c>
       <c r="J8" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="K8" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L8" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="M8" t="n">
         <v>1.14</v>
       </c>
       <c r="N8" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="O8" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="P8" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="Q8" t="n">
         <v>2.8</v>
@@ -2423,19 +2423,19 @@
         <v>6</v>
       </c>
       <c r="T8" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="U8" t="n">
         <v>1.66</v>
       </c>
       <c r="V8" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W8" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="X8" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Y8" t="n">
         <v>12</v>
@@ -2447,7 +2447,7 @@
         <v>900</v>
       </c>
       <c r="AB8" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AC8" t="n">
         <v>7.6</v>
@@ -2483,7 +2483,7 @@
         <v>500</v>
       </c>
       <c r="AN8" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO8" t="n">
         <v>180</v>
@@ -2498,10 +2498,10 @@
         <v>13.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AT8" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AU8" t="n">
         <v>6.2</v>
@@ -2510,7 +2510,7 @@
         <v>17.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AX8" t="n">
         <v>9.800000000000001</v>
@@ -2522,7 +2522,7 @@
         <v>12</v>
       </c>
       <c r="BA8" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB8" t="n">
         <v>12</v>
@@ -2531,80 +2531,80 @@
         <v>13</v>
       </c>
       <c r="BD8" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BE8" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BF8" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BG8" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BH8" t="n">
-        <v>1000</v>
+        <v>2.64</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BN8" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BP8" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BT8" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-14 11:49:16</t>
+          <t>2026-07-14 13:57:32</t>
         </is>
       </c>
     </row>
@@ -2635,22 +2635,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="G9" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="H9" t="n">
         <v>3.05</v>
       </c>
       <c r="I9" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J9" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="K9" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L9" t="n">
         <v>1.22</v>
@@ -2659,40 +2659,40 @@
         <v>1.02</v>
       </c>
       <c r="N9" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="O9" t="n">
         <v>1.12</v>
       </c>
       <c r="P9" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="R9" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="T9" t="n">
         <v>1.39</v>
       </c>
       <c r="U9" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="V9" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W9" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="X9" t="n">
         <v>42</v>
       </c>
       <c r="Y9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Z9" t="n">
         <v>32</v>
@@ -2713,16 +2713,16 @@
         <v>27</v>
       </c>
       <c r="AF9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG9" t="n">
         <v>13</v>
       </c>
       <c r="AH9" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AI9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AJ9" t="n">
         <v>32</v>
@@ -2740,34 +2740,34 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AO9" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AP9" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AR9" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="AS9" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="AT9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AU9" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AV9" t="n">
         <v>13</v>
       </c>
       <c r="AW9" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="AX9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AY9" t="n">
         <v>11</v>
@@ -2776,19 +2776,19 @@
         <v>12</v>
       </c>
       <c r="BA9" t="n">
-        <v>13.5</v>
+        <v>23</v>
       </c>
       <c r="BB9" t="n">
         <v>27</v>
       </c>
       <c r="BC9" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BD9" t="n">
         <v>20</v>
       </c>
       <c r="BE9" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="BF9" t="n">
         <v>7</v>
@@ -2800,7 +2800,7 @@
         <v>5.7</v>
       </c>
       <c r="BI9" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="BJ9" t="n">
         <v>8.4</v>
@@ -2812,28 +2812,28 @@
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN9" t="n">
         <v>6.2</v>
       </c>
       <c r="BO9" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BP9" t="n">
         <v>14.5</v>
       </c>
       <c r="BQ9" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BR9" t="n">
         <v>19</v>
       </c>
       <c r="BS9" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BT9" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BU9" t="n">
         <v>6.2</v>
@@ -2842,13 +2842,13 @@
         <v>20</v>
       </c>
       <c r="BW9" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BX9" t="n">
         <v>23</v>
       </c>
       <c r="BY9" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="BZ9" t="n">
         <v>11</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-14 11:49:16</t>
+          <t>2026-07-14 13:57:32</t>
         </is>
       </c>
     </row>
@@ -2889,25 +2889,25 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="G10" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="H10" t="n">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="I10" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="J10" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="K10" t="n">
         <v>2.7</v>
       </c>
       <c r="L10" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="M10" t="n">
         <v>1.18</v>
@@ -2916,13 +2916,13 @@
         <v>2.34</v>
       </c>
       <c r="O10" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="P10" t="n">
         <v>1.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="R10" t="n">
         <v>1.14</v>
@@ -2940,10 +2940,10 @@
         <v>1.57</v>
       </c>
       <c r="W10" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="X10" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="Y10" t="n">
         <v>970</v>
@@ -3006,7 +3006,7 @@
         <v>2.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AT10" t="n">
         <v>4.4</v>
@@ -3018,31 +3018,31 @@
         <v>5.1</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.2</v>
+        <v>9</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.19</v>
+        <v>6.6</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="BF10" t="n">
         <v>1.55</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-14 11:49:16</t>
+          <t>2026-07-14 13:57:32</t>
         </is>
       </c>
     </row>
@@ -3143,37 +3143,37 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="G11" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="H11" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="I11" t="n">
         <v>4.2</v>
       </c>
       <c r="J11" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K11" t="n">
         <v>3.55</v>
       </c>
       <c r="L11" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="M11" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N11" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O11" t="n">
         <v>1.44</v>
       </c>
       <c r="P11" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q11" t="n">
         <v>2.34</v>
@@ -3182,34 +3182,34 @@
         <v>1.27</v>
       </c>
       <c r="S11" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="T11" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="U11" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="V11" t="n">
         <v>1.31</v>
       </c>
       <c r="W11" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="X11" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y11" t="n">
         <v>12.5</v>
       </c>
-      <c r="Y11" t="n">
-        <v>15</v>
-      </c>
       <c r="Z11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AA11" t="n">
         <v>270</v>
       </c>
       <c r="AB11" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC11" t="n">
         <v>7.6</v>
@@ -3230,25 +3230,25 @@
         <v>22</v>
       </c>
       <c r="AI11" t="n">
-        <v>80</v>
+        <v>370</v>
       </c>
       <c r="AJ11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL11" t="n">
-        <v>65</v>
+        <v>180</v>
       </c>
       <c r="AM11" t="n">
         <v>580</v>
       </c>
       <c r="AN11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO11" t="n">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="AP11" t="n">
         <v>9.6</v>
@@ -3257,10 +3257,10 @@
         <v>10.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AS11" t="n">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="AT11" t="n">
         <v>6.6</v>
@@ -3275,7 +3275,7 @@
         <v>40</v>
       </c>
       <c r="AX11" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AY11" t="n">
         <v>9.800000000000001</v>
@@ -3284,7 +3284,7 @@
         <v>18.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="BB11" t="n">
         <v>21</v>
@@ -3293,80 +3293,80 @@
         <v>19.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>32</v>
+        <v>6.4</v>
       </c>
       <c r="BE11" t="n">
-        <v>65</v>
+        <v>6.8</v>
       </c>
       <c r="BF11" t="n">
-        <v>17</v>
+        <v>5.7</v>
       </c>
       <c r="BG11" t="n">
-        <v>46</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH11" t="n">
-        <v>3</v>
+        <v>1000</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.7</v>
+        <v>1.01</v>
       </c>
       <c r="BJ11" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK11" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>14.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN11" t="n">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="BO11" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BP11" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BR11" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BT11" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BU11" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BV11" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BX11" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BZ11" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-14 11:49:16</t>
+          <t>2026-07-14 13:57:32</t>
         </is>
       </c>
     </row>
@@ -3400,10 +3400,10 @@
         <v>2.6</v>
       </c>
       <c r="G12" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="H12" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="I12" t="n">
         <v>3.65</v>
@@ -3412,7 +3412,7 @@
         <v>2.78</v>
       </c>
       <c r="K12" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="L12" t="n">
         <v>1.63</v>
@@ -3427,7 +3427,7 @@
         <v>1.57</v>
       </c>
       <c r="P12" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="Q12" t="n">
         <v>2.78</v>
@@ -3544,7 +3544,7 @@
         <v>38</v>
       </c>
       <c r="BC12" t="n">
-        <v>6.6</v>
+        <v>34</v>
       </c>
       <c r="BD12" t="n">
         <v>7</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-14 11:49:16</t>
+          <t>2026-07-14 13:57:32</t>
         </is>
       </c>
     </row>
@@ -3651,25 +3651,25 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.84</v>
+        <v>2.76</v>
       </c>
       <c r="G13" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H13" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="I13" t="n">
         <v>4.1</v>
       </c>
       <c r="J13" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="K13" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="L13" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="M13" t="n">
         <v>1.2</v>
@@ -3678,10 +3678,10 @@
         <v>2.38</v>
       </c>
       <c r="O13" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="P13" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="Q13" t="n">
         <v>3.2</v>
@@ -3690,191 +3690,191 @@
         <v>1.13</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="T13" t="n">
-        <v>2.22</v>
+        <v>1.95</v>
       </c>
       <c r="U13" t="n">
-        <v>1.62</v>
+        <v>1.27</v>
       </c>
       <c r="V13" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W13" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="X13" t="n">
-        <v>6.6</v>
+        <v>970</v>
       </c>
       <c r="Y13" t="n">
-        <v>9.800000000000001</v>
+        <v>970</v>
       </c>
       <c r="Z13" t="n">
-        <v>25</v>
+        <v>970</v>
       </c>
       <c r="AA13" t="n">
-        <v>260</v>
+        <v>500</v>
       </c>
       <c r="AB13" t="n">
-        <v>8</v>
+        <v>970</v>
       </c>
       <c r="AC13" t="n">
-        <v>6.6</v>
+        <v>970</v>
       </c>
       <c r="AD13" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AE13" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AF13" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AG13" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AH13" t="n">
-        <v>28</v>
+        <v>500</v>
       </c>
       <c r="AI13" t="n">
         <v>500</v>
       </c>
       <c r="AJ13" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AK13" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AL13" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AM13" t="n">
         <v>500</v>
       </c>
       <c r="AN13" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>5.1</v>
+        <v>3.85</v>
       </c>
       <c r="AQ13" t="n">
-        <v>7.6</v>
+        <v>4.4</v>
       </c>
       <c r="AR13" t="n">
-        <v>18.5</v>
+        <v>8.4</v>
       </c>
       <c r="AS13" t="n">
-        <v>8.6</v>
+        <v>1.28</v>
       </c>
       <c r="AT13" t="n">
-        <v>6.2</v>
+        <v>4.4</v>
       </c>
       <c r="AU13" t="n">
-        <v>5.4</v>
+        <v>4.2</v>
       </c>
       <c r="AV13" t="n">
-        <v>15</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW13" t="n">
-        <v>20</v>
+        <v>1.28</v>
       </c>
       <c r="AX13" t="n">
-        <v>13.5</v>
+        <v>7.4</v>
       </c>
       <c r="AY13" t="n">
-        <v>12.5</v>
+        <v>6.8</v>
       </c>
       <c r="AZ13" t="n">
-        <v>21</v>
+        <v>1.28</v>
       </c>
       <c r="BA13" t="n">
-        <v>9</v>
+        <v>1.28</v>
       </c>
       <c r="BB13" t="n">
-        <v>20</v>
+        <v>1.28</v>
       </c>
       <c r="BC13" t="n">
-        <v>21</v>
+        <v>1.28</v>
       </c>
       <c r="BD13" t="n">
-        <v>8.800000000000001</v>
+        <v>1.28</v>
       </c>
       <c r="BE13" t="n">
-        <v>8</v>
+        <v>1.28</v>
       </c>
       <c r="BF13" t="n">
-        <v>7.4</v>
+        <v>1.55</v>
       </c>
       <c r="BG13" t="n">
-        <v>7.4</v>
+        <v>1.55</v>
       </c>
       <c r="BH13" t="n">
-        <v>2.54</v>
+        <v>1000</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.16</v>
+        <v>1.02</v>
       </c>
       <c r="BJ13" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BK13" t="n">
-        <v>5.4</v>
+        <v>1.02</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>8.800000000000001</v>
+        <v>1.02</v>
       </c>
       <c r="BN13" t="n">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="BO13" t="n">
-        <v>4.6</v>
+        <v>1.02</v>
       </c>
       <c r="BP13" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>7</v>
+        <v>1.02</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>8</v>
+        <v>1.02</v>
       </c>
       <c r="BT13" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BU13" t="n">
-        <v>5.2</v>
+        <v>1.02</v>
       </c>
       <c r="BV13" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>7.4</v>
+        <v>1.02</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>8.199999999999999</v>
+        <v>1.02</v>
       </c>
       <c r="BZ13" t="n">
         <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>8.199999999999999</v>
+        <v>1.02</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-14 11:49:16</t>
+          <t>2026-07-14 13:57:32</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3905,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="G14" t="n">
         <v>3.05</v>
@@ -3917,7 +3917,7 @@
         <v>3.35</v>
       </c>
       <c r="J14" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="K14" t="n">
         <v>3.2</v>
@@ -3935,13 +3935,13 @@
         <v>1.62</v>
       </c>
       <c r="P14" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="Q14" t="n">
         <v>2.84</v>
       </c>
       <c r="R14" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="S14" t="n">
         <v>6</v>
@@ -3962,7 +3962,7 @@
         <v>8</v>
       </c>
       <c r="Y14" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z14" t="n">
         <v>20</v>
@@ -3971,16 +3971,16 @@
         <v>270</v>
       </c>
       <c r="AB14" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC14" t="n">
         <v>7.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AE14" t="n">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="AF14" t="n">
         <v>18</v>
@@ -3989,28 +3989,28 @@
         <v>14.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AI14" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="AJ14" t="n">
-        <v>160</v>
+        <v>75</v>
       </c>
       <c r="AK14" t="n">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="AL14" t="n">
-        <v>460</v>
+        <v>270</v>
       </c>
       <c r="AM14" t="n">
         <v>500</v>
       </c>
       <c r="AN14" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AO14" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AP14" t="n">
         <v>6.6</v>
@@ -4019,10 +4019,10 @@
         <v>7.2</v>
       </c>
       <c r="AR14" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="AT14" t="n">
         <v>6.6</v>
@@ -4034,7 +4034,7 @@
         <v>12.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>7.8</v>
+        <v>32</v>
       </c>
       <c r="AX14" t="n">
         <v>14.5</v>
@@ -4043,28 +4043,28 @@
         <v>12</v>
       </c>
       <c r="AZ14" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BA14" t="n">
-        <v>8.199999999999999</v>
+        <v>28</v>
       </c>
       <c r="BB14" t="n">
-        <v>7.8</v>
+        <v>34</v>
       </c>
       <c r="BC14" t="n">
-        <v>7.6</v>
+        <v>30</v>
       </c>
       <c r="BD14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE14" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>38</v>
+      </c>
+      <c r="BG14" t="n">
         <v>8.800000000000001</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>8.199999999999999</v>
       </c>
       <c r="BH14" t="n">
         <v>2.6</v>
@@ -4097,7 +4097,7 @@
         <v>8.6</v>
       </c>
       <c r="BR14" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="BS14" t="n">
         <v>10</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-14 11:49:16</t>
+          <t>2026-07-14 13:57:32</t>
         </is>
       </c>
     </row>
@@ -4162,16 +4162,16 @@
         <v>3.65</v>
       </c>
       <c r="G15" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="H15" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="I15" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="J15" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="K15" t="n">
         <v>3.3</v>
@@ -4204,13 +4204,13 @@
         <v>2.18</v>
       </c>
       <c r="U15" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="V15" t="n">
         <v>1.66</v>
       </c>
       <c r="W15" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="X15" t="n">
         <v>9.4</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-14 11:49:16</t>
+          <t>2026-07-14 13:57:32</t>
         </is>
       </c>
     </row>
@@ -4413,130 +4413,130 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="G16" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="H16" t="n">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="I16" t="n">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="J16" t="n">
         <v>4.5</v>
       </c>
       <c r="K16" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L16" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="M16" t="n">
         <v>1.02</v>
       </c>
       <c r="N16" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="P16" t="n">
-        <v>3.15</v>
+        <v>3.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="S16" t="n">
-        <v>2.04</v>
+        <v>1.84</v>
       </c>
       <c r="T16" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="U16" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="V16" t="n">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="W16" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="X16" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="Y16" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="Z16" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AA16" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AB16" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AC16" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD16" t="n">
         <v>13</v>
       </c>
-      <c r="AD16" t="n">
-        <v>12</v>
-      </c>
       <c r="AE16" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AF16" t="n">
         <v>42</v>
       </c>
       <c r="AG16" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AH16" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AJ16" t="n">
-        <v>170</v>
+        <v>90</v>
       </c>
       <c r="AK16" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM16" t="n">
         <v>40</v>
       </c>
-      <c r="AL16" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>48</v>
-      </c>
       <c r="AN16" t="n">
-        <v>23</v>
+        <v>16.5</v>
       </c>
       <c r="AO16" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="AP16" t="n">
         <v>14.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AR16" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AS16" t="n">
         <v>19</v>
       </c>
       <c r="AT16" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="AU16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AV16" t="n">
         <v>9.6</v>
@@ -4554,79 +4554,79 @@
         <v>13</v>
       </c>
       <c r="BA16" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="BB16" t="n">
-        <v>9.4</v>
+        <v>32</v>
       </c>
       <c r="BC16" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="BD16" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BE16" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="BF16" t="n">
-        <v>18</v>
+        <v>13.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="BH16" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="BI16" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BJ16" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM16" t="n">
         <v>8.800000000000001</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>10</v>
       </c>
       <c r="BN16" t="n">
         <v>8.6</v>
       </c>
       <c r="BO16" t="n">
-        <v>6.8</v>
+        <v>4.8</v>
       </c>
       <c r="BP16" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="BQ16" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="BR16" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="BS16" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="BT16" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BU16" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BV16" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BW16" t="n">
-        <v>5.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX16" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="BY16" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="BZ16" t="n">
         <v>0</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-14 11:49:16</t>
+          <t>2026-07-14 13:57:32</t>
         </is>
       </c>
     </row>
@@ -4667,22 +4667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="G17" t="n">
         <v>1.49</v>
       </c>
-      <c r="G17" t="n">
-        <v>1.53</v>
-      </c>
       <c r="H17" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="I17" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="J17" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="K17" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="L17" t="n">
         <v>1.27</v>
@@ -4691,25 +4691,25 @@
         <v>1.03</v>
       </c>
       <c r="N17" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O17" t="n">
         <v>1.17</v>
       </c>
       <c r="P17" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="R17" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="S17" t="n">
         <v>2.32</v>
       </c>
       <c r="T17" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="U17" t="n">
         <v>2.24</v>
@@ -4718,85 +4718,85 @@
         <v>1.15</v>
       </c>
       <c r="W17" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="X17" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="Y17" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Z17" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AA17" t="n">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="AB17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AC17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AD17" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AE17" t="n">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="AF17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG17" t="n">
         <v>11.5</v>
       </c>
-      <c r="AG17" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AH17" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AI17" t="n">
         <v>80</v>
       </c>
       <c r="AJ17" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK17" t="n">
         <v>14.5</v>
       </c>
-      <c r="AK17" t="n">
-        <v>15</v>
-      </c>
       <c r="AL17" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AM17" t="n">
-        <v>95</v>
+        <v>140</v>
       </c>
       <c r="AN17" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="AO17" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AP17" t="n">
-        <v>6.8</v>
+        <v>22</v>
       </c>
       <c r="AQ17" t="n">
-        <v>7.2</v>
+        <v>13</v>
       </c>
       <c r="AR17" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS17" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AT17" t="n">
         <v>10.5</v>
       </c>
       <c r="AU17" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AV17" t="n">
-        <v>20</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW17" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AX17" t="n">
         <v>9.4</v>
@@ -4805,82 +4805,82 @@
         <v>9.4</v>
       </c>
       <c r="AZ17" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA17" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="BB17" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BC17" t="n">
         <v>12</v>
       </c>
       <c r="BD17" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE17" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BF17" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BG17" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="BH17" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BI17" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BJ17" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BK17" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BN17" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BO17" t="n">
         <v>3.85</v>
       </c>
       <c r="BP17" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BQ17" t="n">
         <v>5.3</v>
       </c>
       <c r="BR17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BS17" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BT17" t="n">
+        <v>11</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>55</v>
+      </c>
+      <c r="BW17" t="n">
         <v>10.5</v>
       </c>
-      <c r="BU17" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BV17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW17" t="n">
-        <v>10</v>
-      </c>
       <c r="BX17" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY17" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ17" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-14 11:49:16</t>
+          <t>2026-07-14 13:57:32</t>
         </is>
       </c>
     </row>
@@ -4933,10 +4933,10 @@
         <v>3.4</v>
       </c>
       <c r="J18" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="K18" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="L18" t="n">
         <v>1.68</v>
@@ -4948,10 +4948,10 @@
         <v>2.36</v>
       </c>
       <c r="O18" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="P18" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="Q18" t="n">
         <v>3.15</v>
@@ -4960,7 +4960,7 @@
         <v>1.15</v>
       </c>
       <c r="S18" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="T18" t="n">
         <v>2.32</v>
@@ -4975,10 +4975,10 @@
         <v>1.52</v>
       </c>
       <c r="X18" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="Y18" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="Z18" t="n">
         <v>22</v>
@@ -5005,7 +5005,7 @@
         <v>16</v>
       </c>
       <c r="AH18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI18" t="n">
         <v>110</v>
@@ -5014,22 +5014,22 @@
         <v>55</v>
       </c>
       <c r="AK18" t="n">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="AL18" t="n">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="AM18" t="n">
         <v>260</v>
       </c>
       <c r="AN18" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AO18" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AP18" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AQ18" t="n">
         <v>7.6</v>
@@ -5062,7 +5062,7 @@
         <v>23</v>
       </c>
       <c r="BA18" t="n">
-        <v>44</v>
+        <v>11.5</v>
       </c>
       <c r="BB18" t="n">
         <v>42</v>
@@ -5071,80 +5071,80 @@
         <v>40</v>
       </c>
       <c r="BD18" t="n">
-        <v>36</v>
+        <v>11.5</v>
       </c>
       <c r="BE18" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BF18" t="n">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="BG18" t="n">
         <v>60</v>
       </c>
       <c r="BH18" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="BJ18" t="n">
         <v>12.5</v>
       </c>
       <c r="BK18" t="n">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="BN18" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BO18" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BP18" t="n">
         <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>12.5</v>
+        <v>9.4</v>
       </c>
       <c r="BT18" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BU18" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BV18" t="n">
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>11</v>
+        <v>8.6</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>13</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ18" t="n">
         <v>1000</v>
       </c>
       <c r="CA18" t="n">
-        <v>13</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-14 11:49:16</t>
+          <t>2026-07-14 13:57:32</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-14.xlsx
@@ -857,230 +857,230 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.04</v>
+        <v>1.1</v>
       </c>
       <c r="G2" t="n">
-        <v>2.08</v>
+        <v>1.11</v>
       </c>
       <c r="H2" t="n">
-        <v>4.3</v>
+        <v>34</v>
       </c>
       <c r="I2" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>3.4</v>
+        <v>10</v>
       </c>
       <c r="K2" t="n">
-        <v>3.45</v>
+        <v>12</v>
       </c>
       <c r="L2" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="S2" t="n">
-        <v>4.7</v>
+        <v>3.35</v>
       </c>
       <c r="T2" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>1.94</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="X2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>420</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>970</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>130</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>250</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>250</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>250</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>110</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>250</v>
+      </c>
+      <c r="AU2" t="n">
         <v>11</v>
       </c>
-      <c r="Y2" t="n">
-        <v>14</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>120</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>70</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AG2" t="n">
+      <c r="AV2" t="n">
         <v>11</v>
       </c>
-      <c r="AH2" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>26</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL2" t="n">
+      <c r="AW2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>250</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>140</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>250</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>46</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>13</v>
+      </c>
+      <c r="BF2" t="n">
         <v>50</v>
       </c>
-      <c r="AM2" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>22</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>100</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>27</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>85</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>16</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>60</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>65</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>22</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>22</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>42</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>110</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>19</v>
-      </c>
       <c r="BG2" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="BH2" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BK2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BN2" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BP2" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="BQ2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BR2" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BT2" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="BU2" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BV2" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="BW2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="BY2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BZ2" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="CA2" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-14 18:13:51</t>
+          <t>2026-07-14 20:21:48</t>
         </is>
       </c>
     </row>
@@ -1111,230 +1111,230 @@
         </is>
       </c>
       <c r="F3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>22</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="J3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="S3" t="n">
+        <v>16</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="V3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y3" t="n">
         <v>2.7</v>
       </c>
-      <c r="G3" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="H3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="I3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J3" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="K3" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="N3" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="S3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="X3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="Z3" t="n">
-        <v>22</v>
+        <v>6.4</v>
       </c>
       <c r="AA3" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>24</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>320</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>200</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>450</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>140</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>28</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>44</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>36</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>160</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BC3" t="n">
         <v>100</v>
       </c>
-      <c r="AB3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>260</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>46</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>130</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>17</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>20</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>23</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>34</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>38</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>34</v>
-      </c>
       <c r="BD3" t="n">
-        <v>28</v>
+        <v>150</v>
       </c>
       <c r="BE3" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="BF3" t="n">
-        <v>48</v>
+        <v>18.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>9.800000000000001</v>
+        <v>75</v>
       </c>
       <c r="BH3" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BK3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BN3" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BP3" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="BQ3" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>980</v>
+        <v>0</v>
       </c>
       <c r="BS3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BT3" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BV3" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BW3" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>980</v>
+        <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA3" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-14 18:13:51</t>
+          <t>2026-07-14 20:21:48</t>
         </is>
       </c>
     </row>
@@ -1365,230 +1365,230 @@
         </is>
       </c>
       <c r="F4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="H4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
         <v>2.96</v>
       </c>
-      <c r="G4" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="H4" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="I4" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="K4" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="N4" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.14</v>
-      </c>
       <c r="S4" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>930</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK4" t="n">
         <v>6.6</v>
       </c>
-      <c r="T4" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="X4" t="n">
-        <v>970</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>970</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>970</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>500</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>42</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>500</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>500</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>500</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>500</v>
-      </c>
       <c r="AL4" t="n">
-        <v>500</v>
+        <v>11.5</v>
       </c>
       <c r="AM4" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AO4" t="n">
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.85</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR4" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.58</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT4" t="n">
-        <v>4.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU4" t="n">
-        <v>4.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV4" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AW4" t="n">
-        <v>2.76</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX4" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY4" t="n">
-        <v>6.8</v>
+        <v>2.72</v>
       </c>
       <c r="AZ4" t="n">
-        <v>12</v>
+        <v>4.1</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.52</v>
+        <v>16</v>
       </c>
       <c r="BB4" t="n">
-        <v>2.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.78</v>
+        <v>5.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>2.52</v>
+        <v>10</v>
       </c>
       <c r="BE4" t="n">
-        <v>2.54</v>
+        <v>26</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.46</v>
+        <v>12.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.46</v>
+        <v>14.5</v>
       </c>
       <c r="BH4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="BN4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="BP4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="BT4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="BV4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-14 18:13:51</t>
+          <t>2026-07-14 20:21:48</t>
         </is>
       </c>
     </row>
@@ -1619,230 +1619,230 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.9</v>
+        <v>4.6</v>
       </c>
       <c r="G5" t="n">
-        <v>3.1</v>
+        <v>4.9</v>
       </c>
       <c r="H5" t="n">
-        <v>2.88</v>
+        <v>3.9</v>
       </c>
       <c r="I5" t="n">
-        <v>3.05</v>
+        <v>4.2</v>
       </c>
       <c r="J5" t="n">
-        <v>2.98</v>
+        <v>1.83</v>
       </c>
       <c r="K5" t="n">
-        <v>3.1</v>
+        <v>1.88</v>
       </c>
       <c r="L5" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1.15</v>
+        <v>1.79</v>
       </c>
       <c r="N5" t="n">
-        <v>2.36</v>
+        <v>1.26</v>
       </c>
       <c r="O5" t="n">
-        <v>1.64</v>
+        <v>4.6</v>
       </c>
       <c r="P5" t="n">
-        <v>1.43</v>
+        <v>1.04</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.05</v>
+        <v>21</v>
       </c>
       <c r="R5" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="S5" t="n">
+        <v>100</v>
+      </c>
+      <c r="T5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB5" t="n">
         <v>6.4</v>
       </c>
-      <c r="T5" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="X5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>160</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>8</v>
-      </c>
       <c r="AC5" t="n">
-        <v>7.2</v>
+        <v>13</v>
       </c>
       <c r="AD5" t="n">
-        <v>15.5</v>
+        <v>990</v>
       </c>
       <c r="AE5" t="n">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>15</v>
+        <v>990</v>
       </c>
       <c r="AH5" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.4</v>
+        <v>2.2</v>
       </c>
       <c r="AQ5" t="n">
-        <v>6.8</v>
+        <v>5</v>
       </c>
       <c r="AR5" t="n">
-        <v>15.5</v>
+        <v>19.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>38</v>
+        <v>120</v>
       </c>
       <c r="AT5" t="n">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.2</v>
+        <v>10.5</v>
       </c>
       <c r="AV5" t="n">
-        <v>12.5</v>
+        <v>40</v>
       </c>
       <c r="AW5" t="n">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="AX5" t="n">
-        <v>14.5</v>
+        <v>7</v>
       </c>
       <c r="AY5" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="AZ5" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="BA5" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="BB5" t="n">
-        <v>34</v>
+        <v>200</v>
       </c>
       <c r="BC5" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="BD5" t="n">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="BE5" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="BF5" t="n">
         <v>29</v>
       </c>
       <c r="BG5" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BK5" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BN5" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="BP5" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BQ5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BR5" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="BS5" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BT5" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BV5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY5" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BZ5" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="CA5" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-14 18:13:51</t>
+          <t>2026-07-14 20:21:48</t>
         </is>
       </c>
     </row>
@@ -1873,230 +1873,230 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.75</v>
+        <v>21</v>
       </c>
       <c r="G6" t="n">
-        <v>4.2</v>
+        <v>28</v>
       </c>
       <c r="H6" t="n">
-        <v>2.3</v>
+        <v>1.31</v>
       </c>
       <c r="I6" t="n">
-        <v>2.42</v>
+        <v>1.35</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>4.7</v>
       </c>
       <c r="K6" t="n">
-        <v>3.35</v>
+        <v>5.1</v>
       </c>
       <c r="L6" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="O6" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="P6" t="n">
-        <v>1.45</v>
+        <v>1.26</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.96</v>
+        <v>4.6</v>
       </c>
       <c r="R6" t="n">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="S6" t="n">
-        <v>6.2</v>
+        <v>18.5</v>
       </c>
       <c r="T6" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="U6" t="n">
-        <v>1.66</v>
+        <v>1.54</v>
       </c>
       <c r="V6" t="n">
-        <v>1.7</v>
+        <v>3.9</v>
       </c>
       <c r="W6" t="n">
-        <v>1.32</v>
+        <v>1.04</v>
       </c>
       <c r="X6" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>13.5</v>
+        <v>5.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="AB6" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>7.6</v>
+        <v>5.6</v>
       </c>
       <c r="AD6" t="n">
         <v>13</v>
       </c>
       <c r="AE6" t="n">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="AF6" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>19.5</v>
+        <v>32</v>
       </c>
       <c r="AH6" t="n">
-        <v>48</v>
+        <v>990</v>
       </c>
       <c r="AI6" t="n">
+        <v>410</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>340</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>130</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>21</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>44</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>25</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>46</v>
+      </c>
+      <c r="BA6" t="n">
         <v>170</v>
       </c>
-      <c r="AJ6" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>500</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>130</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>50</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>15</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>40</v>
-      </c>
       <c r="BB6" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BC6" t="n">
-        <v>8</v>
+        <v>170</v>
       </c>
       <c r="BD6" t="n">
-        <v>29</v>
+        <v>230</v>
       </c>
       <c r="BE6" t="n">
-        <v>8.6</v>
+        <v>240</v>
       </c>
       <c r="BF6" t="n">
-        <v>8.6</v>
+        <v>490</v>
       </c>
       <c r="BG6" t="n">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="BH6" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="BJ6" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BK6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BL6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM6" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BN6" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="BO6" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BP6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ6" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BR6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS6" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BT6" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BU6" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BV6" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BW6" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY6" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA6" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-14 18:13:51</t>
+          <t>2026-07-14 20:21:48</t>
         </is>
       </c>
     </row>
@@ -2127,220 +2127,220 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.65</v>
+        <v>1.5</v>
       </c>
       <c r="G7" t="n">
-        <v>3.9</v>
+        <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>1.85</v>
+        <v>1.01</v>
       </c>
       <c r="I7" t="n">
-        <v>1.91</v>
+        <v>1.01</v>
       </c>
       <c r="J7" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="K7" t="n">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="L7" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.16</v>
+        <v>6.6</v>
       </c>
       <c r="S7" t="n">
-        <v>1.8</v>
+        <v>1.16</v>
       </c>
       <c r="T7" t="n">
-        <v>1.35</v>
+        <v>3.25</v>
       </c>
       <c r="U7" t="n">
-        <v>3.3</v>
+        <v>1.34</v>
       </c>
       <c r="V7" t="n">
-        <v>2.1</v>
+        <v>100</v>
       </c>
       <c r="W7" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>27</v>
+        <v>7.8</v>
       </c>
       <c r="AB7" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>5.7</v>
+        <v>1.3</v>
       </c>
       <c r="AP7" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="AQ7" t="n">
-        <v>20</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR7" t="n">
-        <v>18.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS7" t="n">
-        <v>23</v>
+        <v>5.5</v>
       </c>
       <c r="AT7" t="n">
-        <v>30</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU7" t="n">
-        <v>13</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV7" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW7" t="n">
-        <v>14.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX7" t="n">
-        <v>36</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY7" t="n">
-        <v>15.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ7" t="n">
-        <v>13</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BA7" t="n">
-        <v>17.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB7" t="n">
-        <v>55</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC7" t="n">
-        <v>30</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD7" t="n">
-        <v>23</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE7" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="BF7" t="n">
-        <v>13.5</v>
+        <v>10</v>
       </c>
       <c r="BG7" t="n">
-        <v>5.2</v>
+        <v>1.16</v>
       </c>
       <c r="BH7" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BI7" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BK7" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BL7" t="n">
-        <v>980</v>
+        <v>0</v>
       </c>
       <c r="BM7" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BN7" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BP7" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="BQ7" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="BR7" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="BT7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BU7" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BV7" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BW7" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="BY7" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-14 18:13:51</t>
+          <t>2026-07-14 20:21:48</t>
         </is>
       </c>
     </row>
@@ -2381,220 +2381,220 @@
         </is>
       </c>
       <c r="F8" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="G8" t="n">
         <v>1.42</v>
       </c>
-      <c r="G8" t="n">
-        <v>1.45</v>
-      </c>
       <c r="H8" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="J8" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="K8" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="L8" t="n">
         <v>1.24</v>
       </c>
       <c r="M8" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N8" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="O8" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="P8" t="n">
         <v>3.05</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="R8" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="S8" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="T8" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="U8" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="V8" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="W8" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="X8" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="Y8" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="Z8" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AA8" t="n">
-        <v>220</v>
+        <v>290</v>
       </c>
       <c r="AB8" t="n">
         <v>15.5</v>
       </c>
       <c r="AC8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ8" t="n">
         <v>13.5</v>
       </c>
-      <c r="AD8" t="n">
-        <v>29</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>160</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>14</v>
-      </c>
       <c r="AK8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AL8" t="n">
         <v>28</v>
       </c>
       <c r="AM8" t="n">
-        <v>140</v>
+        <v>90</v>
       </c>
       <c r="AN8" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="AO8" t="n">
         <v>85</v>
       </c>
       <c r="AP8" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="AQ8" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="AR8" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="AS8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>27</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>46</v>
+      </c>
+      <c r="AX8" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AT8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>9.4</v>
-      </c>
       <c r="AY8" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ8" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BA8" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BB8" t="n">
         <v>11.5</v>
       </c>
       <c r="BC8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>23</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>23</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BG8" t="n">
         <v>12</v>
       </c>
-      <c r="BD8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>22</v>
-      </c>
       <c r="BH8" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BI8" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BJ8" t="n">
         <v>10.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BL8" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="BN8" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BO8" t="n">
         <v>3.9</v>
       </c>
       <c r="BP8" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="BR8" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BS8" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BT8" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BU8" t="n">
         <v>9</v>
       </c>
       <c r="BV8" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="BW8" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BX8" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-14 18:13:51</t>
+          <t>2026-07-14 20:21:48</t>
         </is>
       </c>
     </row>
@@ -2635,230 +2635,230 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="G9" t="n">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="H9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I9" t="n">
         <v>3.25</v>
       </c>
-      <c r="I9" t="n">
-        <v>3.3</v>
-      </c>
       <c r="J9" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="K9" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="L9" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="M9" t="n">
         <v>1.19</v>
       </c>
       <c r="N9" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="S9" t="n">
+        <v>8</v>
+      </c>
+      <c r="T9" t="n">
         <v>2.28</v>
       </c>
-      <c r="O9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="S9" t="n">
+      <c r="U9" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="X9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="Y9" t="n">
         <v>7.6</v>
       </c>
-      <c r="T9" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X9" t="n">
+      <c r="Z9" t="n">
+        <v>990</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>980</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>50</v>
+      </c>
+      <c r="AC9" t="n">
         <v>6.4</v>
       </c>
-      <c r="Y9" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>20</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>65</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AC9" t="n">
+      <c r="AD9" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>960</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>990</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>980</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>960</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>300</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>990</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA9" t="n">
         <v>6.8</v>
       </c>
-      <c r="AD9" t="n">
-        <v>27</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>80</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>130</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>280</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>80</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>90</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>55</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>50</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>15</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>23</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>40</v>
-      </c>
       <c r="BB9" t="n">
-        <v>44</v>
+        <v>6.6</v>
       </c>
       <c r="BC9" t="n">
-        <v>42</v>
+        <v>5.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>14.5</v>
+        <v>8.4</v>
       </c>
       <c r="BE9" t="n">
-        <v>15</v>
+        <v>230</v>
       </c>
       <c r="BF9" t="n">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="BG9" t="n">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="BH9" t="n">
-        <v>2.46</v>
+        <v>2.8</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.24</v>
+        <v>1.96</v>
       </c>
       <c r="BJ9" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>6.8</v>
+        <v>1.76</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>14</v>
+        <v>300</v>
       </c>
       <c r="BN9" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="BO9" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="BP9" t="n">
-        <v>980</v>
+        <v>32</v>
       </c>
       <c r="BQ9" t="n">
-        <v>9.800000000000001</v>
+        <v>1.66</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>12</v>
+        <v>1.76</v>
       </c>
       <c r="BT9" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.4</v>
+        <v>1.76</v>
       </c>
       <c r="BV9" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW9" t="n">
-        <v>10</v>
+        <v>1.66</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>12</v>
+        <v>1.76</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>12</v>
+        <v>1.76</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-14 18:13:51</t>
+          <t>2026-07-14 20:21:48</t>
         </is>
       </c>
     </row>
